--- a/Management/Finantial Planning.xlsx
+++ b/Management/Finantial Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aciww-my.sharepoint.com/personal/daniel_lozanobarrero_aciworldwide_com/Documents/Documents/My-Notes/Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{9D2CB4AA-B5D0-4EF5-A36A-0DE75FD5CA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49C5000A-68C3-412D-9968-0D3E86E00BEB}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{9D2CB4AA-B5D0-4EF5-A36A-0DE75FD5CA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F355AD36-8492-4F75-B7A4-C61BD189AFFC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F8FCC151-5DC7-4472-A863-0C0A531A258D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{F8FCC151-5DC7-4472-A863-0C0A531A258D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="303">
   <si>
     <t>Wellbeing Lifestyle</t>
   </si>
@@ -1501,7 +1501,7 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1704,9 +1704,6 @@
     <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="26" xfId="5" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1793,6 +1790,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="174" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Check Cell" xfId="5" builtinId="23"/>
@@ -1804,19 +1810,11 @@
   </cellStyles>
   <dxfs count="80">
     <dxf>
-      <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="175" formatCode="mmmm\ yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="175" formatCode="mmmm\ yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1830,10 +1828,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="172" formatCode="#,##0.00\ [$COP]"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="173" formatCode="\+\ #.##0\ \C\O\P;\-\ #.##0\ \C\O\P;0\ \C\O\P"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1843,10 +1837,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="172" formatCode="#,##0.00\ [$COP]"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2203,12 +2193,28 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="175" formatCode="mmmm\ yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <b/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="175" formatCode="mmmm\ yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -5999,36 +6005,36 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}" name="Table7" displayName="Table7" ref="E8:G14" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}" name="Table7" displayName="Table7" ref="E8:G14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="E8:G14" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{05264107-3C50-4DC4-BA66-3C598C57D362}" name="Condition" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{4F494527-B966-4283-AC8D-DDFC53922A3A}" name="Action" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{A8687214-DFD3-4202-A740-25119BF98217}" name="% Adjusted" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{05264107-3C50-4DC4-BA66-3C598C57D362}" name="Condition" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{4F494527-B966-4283-AC8D-DDFC53922A3A}" name="Action" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{A8687214-DFD3-4202-A740-25119BF98217}" name="% Adjusted" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}" name="Table10" displayName="Table10" ref="E23:O32" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}" name="Table10" displayName="Table10" ref="E23:O32" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="E23:O32" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{EF8D02AC-323D-45AB-AE15-91832BDC7B4E}" name="Date Bought" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{712A0457-F103-4A5F-89A3-F38940B6301F}" name="Date Sold" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{8B72E438-7296-4BE9-B114-652C18C0973F}" name="Asset" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{C9EB17C7-CF17-4BB1-8390-4A0AA329B909}" name="Units" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{38A379BB-56A1-4C91-8A79-E09D76997328}" name="Price Buy" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{70D6BA55-3422-446B-A79B-9ED0B67E93BD}" name="Price Sell" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{D264BB00-77B0-482C-925B-C8BD072B81A0}" name="Total Invested (COP)" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{9369D078-2888-4CE1-919F-E9A0C05D615C}" name="Total Value" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{313DF1E8-730D-4C1D-BB28-A01F2D131415}" name="Gain/Loss (COP)" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{EF8D02AC-323D-45AB-AE15-91832BDC7B4E}" name="Date Bought" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{712A0457-F103-4A5F-89A3-F38940B6301F}" name="Date Sold" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{8B72E438-7296-4BE9-B114-652C18C0973F}" name="Asset" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C9EB17C7-CF17-4BB1-8390-4A0AA329B909}" name="Units" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{38A379BB-56A1-4C91-8A79-E09D76997328}" name="Price Buy" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{70D6BA55-3422-446B-A79B-9ED0B67E93BD}" name="Price Sell" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{D264BB00-77B0-482C-925B-C8BD072B81A0}" name="Total Invested (COP)" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{9369D078-2888-4CE1-919F-E9A0C05D615C}" name="Total Value" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{313DF1E8-730D-4C1D-BB28-A01F2D131415}" name="Gain/Loss (COP)" dataDxfId="4">
       <calculatedColumnFormula>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{CD1E921A-1374-4429-89D9-1676BA8642FB}" name="% Return" dataDxfId="6" dataCellStyle="Percent">
+    <tableColumn id="10" xr3:uid="{CD1E921A-1374-4429-89D9-1676BA8642FB}" name="% Return" dataDxfId="0" dataCellStyle="Percent">
       <calculatedColumnFormula>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{36B25BAF-3792-45C1-AE34-3EDA3274070F}" name="Notes" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{36B25BAF-3792-45C1-AE34-3EDA3274070F}" name="Notes" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6098,59 +6104,59 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{1E999F4D-13BA-4961-9CC8-4DF65A7B1CEA}" name="Table11" displayName="Table11" ref="H6:I12" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="H6:I12" xr:uid="{1E999F4D-13BA-4961-9CC8-4DF65A7B1CEA}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5E82BFD3-6D74-43F6-913D-96694AEF7A3E}" name="Date" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{710C1C2F-6F23-4153-86B6-2D191197A156}" name="General Balance" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{5E82BFD3-6D74-43F6-913D-96694AEF7A3E}" name="Date" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{710C1C2F-6F23-4153-86B6-2D191197A156}" name="General Balance" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3DBCF91F-3FBC-4548-AAE4-34CB784C3CED}" name="Table1113" displayName="Table1113" ref="H15:I21" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3DBCF91F-3FBC-4548-AAE4-34CB784C3CED}" name="Table1113" displayName="Table1113" ref="H15:I21" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="H15:I21" xr:uid="{3DBCF91F-3FBC-4548-AAE4-34CB784C3CED}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E16B0B05-832D-453D-BB01-1648C2BB6952}" name="Date" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{1165A24D-75E5-4E1D-A756-DA4346B52F4F}" name="Difference from Expected Net" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E16B0B05-832D-453D-BB01-1648C2BB6952}" name="Date" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{1165A24D-75E5-4E1D-A756-DA4346B52F4F}" name="Difference from Expected Net" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BA8F843C-C6A6-4B02-9256-7DFE12B32092}" name="Table5" displayName="Table5" ref="C7:F27" totalsRowShown="0" headerRowDxfId="43" headerRowBorderDxfId="42" tableBorderDxfId="41" totalsRowBorderDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BA8F843C-C6A6-4B02-9256-7DFE12B32092}" name="Table5" displayName="Table5" ref="C7:F27" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37" totalsRowBorderDxfId="36">
   <autoFilter ref="C7:F27" xr:uid="{BA8F843C-C6A6-4B02-9256-7DFE12B32092}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A7222D0C-F15D-4B37-8493-05007AD6DC97}" name="Description" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{9873BCE0-3AFD-4035-A4F4-DDE3995CE8FF}" name="Incoming" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{73BD4001-1956-4334-A204-BB3321930FA2}" name="Outcoming" dataDxfId="37" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{6189F130-2A64-446B-8A16-FBD00F7771AC}" name="Notes" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{A7222D0C-F15D-4B37-8493-05007AD6DC97}" name="Description" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{9873BCE0-3AFD-4035-A4F4-DDE3995CE8FF}" name="Incoming" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{73BD4001-1956-4334-A204-BB3321930FA2}" name="Outcoming" dataDxfId="33" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{6189F130-2A64-446B-8A16-FBD00F7771AC}" name="Notes" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F7CD279B-A932-4C0F-8D8F-D149C918CAA1}" name="Table6" displayName="Table6" ref="H7:J27" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32" totalsRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F7CD279B-A932-4C0F-8D8F-D149C918CAA1}" name="Table6" displayName="Table6" ref="H7:J27" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <autoFilter ref="H7:J27" xr:uid="{F7CD279B-A932-4C0F-8D8F-D149C918CAA1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{516245D1-012B-4614-97CB-8E191CA93F41}" name="Name" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{41E5D36C-6A21-4BF1-972B-BA27C450EDE2}" name="Amount" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{8ADFD3E1-24FE-45CE-8A72-696379253170}" name="Notes" dataDxfId="28" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{516245D1-012B-4614-97CB-8E191CA93F41}" name="Name" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{41E5D36C-6A21-4BF1-972B-BA27C450EDE2}" name="Amount" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{8ADFD3E1-24FE-45CE-8A72-696379253170}" name="Notes" dataDxfId="24" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}" name="Table3" displayName="Table3" ref="E16:H21" totalsRowShown="0" headerRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}" name="Table3" displayName="Table3" ref="E16:H21" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="E16:H21" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{88178FBB-1C68-4443-9D29-711B96CC8F3C}" name="Investment Type" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{AF13EBFA-AD22-4799-B232-349084129FC2}" name="Percentage" dataDxfId="25" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{06249914-8982-4D40-BF2A-A24479258B7E}" name="Current Amount" dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{88178FBB-1C68-4443-9D29-711B96CC8F3C}" name="Investment Type" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{AF13EBFA-AD22-4799-B232-349084129FC2}" name="Percentage" dataDxfId="21" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{06249914-8982-4D40-BF2A-A24479258B7E}" name="Current Amount" dataDxfId="20">
       <calculatedColumnFormula>Tracker!$C$2*Portfolio!F17</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BE746FA0-4394-410B-BFFB-E4580C3454EF}" name="Notes" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{BE746FA0-4394-410B-BFFB-E4580C3454EF}" name="Notes" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6625,7 +6631,7 @@
       </c>
       <c r="L9" s="30">
         <f ca="1">A1048575+_xlfn.CEILING.MATH((TODAY()-A1048575)/21, 1)*21</f>
-        <v>46279</v>
+        <v>46300</v>
       </c>
       <c r="M9" s="40" t="s">
         <v>210</v>
@@ -6648,7 +6654,7 @@
       <c r="H10" s="5">
         <v>15000</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="107">
         <v>8</v>
       </c>
       <c r="J10" s="5">
@@ -6836,7 +6842,7 @@
       <c r="H16" s="5">
         <v>30000</v>
       </c>
-      <c r="I16" s="109">
+      <c r="I16" s="108">
         <v>1</v>
       </c>
       <c r="J16" s="5">
@@ -7053,10 +7059,10 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="105" t="s">
         <v>299</v>
       </c>
-      <c r="C2" s="107">
+      <c r="C2" s="106">
         <v>50000000</v>
       </c>
     </row>
@@ -7076,20 +7082,20 @@
       <c r="F5" s="40" t="s">
         <v>296</v>
       </c>
-      <c r="H5" s="110" t="s">
+      <c r="H5" s="109" t="s">
         <v>297</v>
       </c>
-      <c r="I5" s="110"/>
+      <c r="I5" s="109"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="87">
         <v>46023</v>
       </c>
-      <c r="C6" s="103">
+      <c r="C6" s="102">
         <f>27037512.04+15400000</f>
         <v>42437512.039999999</v>
       </c>
-      <c r="D6" s="103">
+      <c r="D6" s="102">
         <f>27037512.04</f>
         <v>27037512.039999999</v>
       </c>
@@ -7099,10 +7105,10 @@
       <c r="F6" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="H6" s="105" t="s">
+      <c r="H6" s="104" t="s">
         <v>291</v>
       </c>
-      <c r="I6" s="105" t="s">
+      <c r="I6" s="104" t="s">
         <v>295</v>
       </c>
     </row>
@@ -7111,27 +7117,27 @@
         <f>EDATE(B6,1)</f>
         <v>46054</v>
       </c>
-      <c r="C7" s="103">
+      <c r="C7" s="102">
         <f>30821932.81+15400000</f>
         <v>46221932.810000002</v>
       </c>
-      <c r="D7" s="103">
+      <c r="D7" s="102">
         <f>30821932.81</f>
         <v>30821932.809999999</v>
       </c>
-      <c r="E7" s="103">
+      <c r="E7" s="102">
         <f>Table9[[#This Row],[General Balance]]-C6</f>
         <v>3784420.7700000033</v>
       </c>
-      <c r="F7" s="103">
+      <c r="F7" s="102">
         <f>4520137.94-E7</f>
         <v>735717.16999999713</v>
       </c>
-      <c r="H7" s="104">
+      <c r="H7" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
         <v>46113</v>
       </c>
-      <c r="I7" s="103">
+      <c r="I7" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
         <v>52790636.799999997</v>
       </c>
@@ -7141,27 +7147,27 @@
         <f t="shared" ref="B8:B65" si="0">EDATE(B7,1)</f>
         <v>46082</v>
       </c>
-      <c r="C8" s="103">
+      <c r="C8" s="102">
         <f>34124040.84+15400000</f>
         <v>49524040.840000004</v>
       </c>
-      <c r="D8" s="103">
+      <c r="D8" s="102">
         <f>34124040.84</f>
         <v>34124040.840000004</v>
       </c>
-      <c r="E8" s="103">
+      <c r="E8" s="102">
         <f>Table9[[#This Row],[General Balance]]-C7</f>
         <v>3302108.0300000012</v>
       </c>
-      <c r="F8" s="103">
+      <c r="F8" s="102">
         <f t="shared" ref="F8:F65" si="1">4520137.94-E8</f>
         <v>1218029.9099999992</v>
       </c>
-      <c r="H8" s="104">
+      <c r="H8" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
         <v>46143</v>
       </c>
-      <c r="I8" s="103">
+      <c r="I8" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
         <v>55912013.149999999</v>
       </c>
@@ -7171,27 +7177,27 @@
         <f t="shared" si="0"/>
         <v>46113</v>
       </c>
-      <c r="C9" s="103">
+      <c r="C9" s="102">
         <f>37390636.8+15400000</f>
         <v>52790636.799999997</v>
       </c>
-      <c r="D9" s="103">
+      <c r="D9" s="102">
         <f>37390636.8</f>
         <v>37390636.799999997</v>
       </c>
-      <c r="E9" s="103">
+      <c r="E9" s="102">
         <f>Table9[[#This Row],[General Balance]]-C8</f>
         <v>3266595.9599999934</v>
       </c>
-      <c r="F9" s="103">
+      <c r="F9" s="102">
         <f t="shared" si="1"/>
         <v>1253541.980000007</v>
       </c>
-      <c r="H9" s="104">
+      <c r="H9" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
         <v>46174</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
         <v>61491091.960000001</v>
       </c>
@@ -7201,27 +7207,27 @@
         <f t="shared" si="0"/>
         <v>46143</v>
       </c>
-      <c r="C10" s="103">
+      <c r="C10" s="102">
         <f>40512013.15+15400000</f>
         <v>55912013.149999999</v>
       </c>
-      <c r="D10" s="103">
+      <c r="D10" s="102">
         <f>40512013.15</f>
         <v>40512013.149999999</v>
       </c>
-      <c r="E10" s="103">
+      <c r="E10" s="102">
         <f>Table9[[#This Row],[General Balance]]-C9</f>
         <v>3121376.3500000015</v>
       </c>
-      <c r="F10" s="103">
+      <c r="F10" s="102">
         <f t="shared" si="1"/>
         <v>1398761.5899999989</v>
       </c>
-      <c r="H10" s="104">
+      <c r="H10" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
         <v>46204</v>
       </c>
-      <c r="I10" s="103">
+      <c r="I10" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
         <v>64900000</v>
       </c>
@@ -7231,27 +7237,27 @@
         <f t="shared" si="0"/>
         <v>46174</v>
       </c>
-      <c r="C11" s="103">
+      <c r="C11" s="102">
         <f>46091091.96+15400000</f>
         <v>61491091.960000001</v>
       </c>
-      <c r="D11" s="103">
+      <c r="D11" s="102">
         <f>46091091.96</f>
         <v>46091091.960000001</v>
       </c>
-      <c r="E11" s="103">
+      <c r="E11" s="102">
         <f>Table9[[#This Row],[General Balance]]-C10</f>
         <v>5579078.8100000024</v>
       </c>
-      <c r="F11" s="103">
+      <c r="F11" s="102">
         <f t="shared" si="1"/>
         <v>-1058940.870000002</v>
       </c>
-      <c r="H11" s="104">
+      <c r="H11" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
         <v>46235</v>
       </c>
-      <c r="I11" s="103">
+      <c r="I11" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
         <v>65265421.539999999</v>
       </c>
@@ -7261,27 +7267,27 @@
         <f t="shared" si="0"/>
         <v>46204</v>
       </c>
-      <c r="C12" s="103">
+      <c r="C12" s="102">
         <f>9500000+15400000+37000000+3000000</f>
         <v>64900000</v>
       </c>
-      <c r="D12" s="103">
+      <c r="D12" s="102">
         <f>9500000</f>
         <v>9500000</v>
       </c>
-      <c r="E12" s="103">
+      <c r="E12" s="102">
         <f>Table9[[#This Row],[General Balance]]-C11</f>
         <v>3408908.0399999991</v>
       </c>
-      <c r="F12" s="103">
+      <c r="F12" s="102">
         <f t="shared" si="1"/>
         <v>1111229.9000000013</v>
       </c>
-      <c r="H12" s="104">
+      <c r="H12" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
         <v>46266</v>
       </c>
-      <c r="I12" s="103">
+      <c r="I12" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
         <v>69506976.569999993</v>
       </c>
@@ -7291,18 +7297,18 @@
         <f t="shared" si="0"/>
         <v>46235</v>
       </c>
-      <c r="C13" s="103">
+      <c r="C13" s="102">
         <f>Table9[[#This Row],[Account Balance]]+15400000+37000000+6000000</f>
         <v>65265421.539999999</v>
       </c>
-      <c r="D13" s="103">
+      <c r="D13" s="102">
         <v>6865421.54</v>
       </c>
-      <c r="E13" s="103">
+      <c r="E13" s="102">
         <f>4682407-350000-220000-57030-16500-160000-469769</f>
         <v>3409108</v>
       </c>
-      <c r="F13" s="103">
+      <c r="F13" s="102">
         <f t="shared" si="1"/>
         <v>1111029.9400000004</v>
       </c>
@@ -7312,49 +7318,49 @@
         <f t="shared" si="0"/>
         <v>46266</v>
       </c>
-      <c r="C14" s="103">
+      <c r="C14" s="102">
         <f>C13+(Table9[[#This Row],[Account Balance]]-D13)+Main!D10+Main!D9</f>
         <v>69506976.569999993</v>
       </c>
-      <c r="D14" s="103">
+      <c r="D14" s="102">
         <v>10662877.199999999</v>
       </c>
-      <c r="E14" s="103">
+      <c r="E14" s="102">
         <f>Table9[[#This Row],[General Balance]]-C13</f>
         <v>4241555.0299999937</v>
       </c>
-      <c r="F14" s="103">
+      <c r="F14" s="102">
         <f>Main!D21-E14</f>
         <v>171182.9114285782</v>
       </c>
-      <c r="H14" s="110" t="s">
+      <c r="H14" s="109" t="s">
         <v>298</v>
       </c>
-      <c r="I14" s="110"/>
+      <c r="I14" s="109"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="87">
         <f t="shared" si="0"/>
         <v>46296</v>
       </c>
-      <c r="C15" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E15" s="103" t="e">
+      <c r="C15" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E15" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C14</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F15" s="103" t="e">
+      <c r="F15" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H15" s="105" t="s">
+      <c r="H15" s="104" t="s">
         <v>291</v>
       </c>
-      <c r="I15" s="105" t="s">
+      <c r="I15" s="104" t="s">
         <v>296</v>
       </c>
     </row>
@@ -7363,25 +7369,25 @@
         <f t="shared" si="0"/>
         <v>46327</v>
       </c>
-      <c r="C16" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D16" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" s="103" t="e">
+      <c r="C16" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E16" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F16" s="103" t="e">
+      <c r="F16" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H16" s="104">
+      <c r="H16" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
         <v>46113</v>
       </c>
-      <c r="I16" s="103">
+      <c r="I16" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
         <v>1253541.980000007</v>
       </c>
@@ -7391,25 +7397,25 @@
         <f t="shared" si="0"/>
         <v>46357</v>
       </c>
-      <c r="C17" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D17" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E17" s="103" t="e">
+      <c r="C17" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C16</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F17" s="103" t="e">
+      <c r="F17" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H17" s="104">
+      <c r="H17" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
         <v>46143</v>
       </c>
-      <c r="I17" s="103">
+      <c r="I17" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
         <v>1398761.5899999989</v>
       </c>
@@ -7419,25 +7425,25 @@
         <f t="shared" si="0"/>
         <v>46388</v>
       </c>
-      <c r="C18" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="103" t="e">
+      <c r="C18" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C17</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F18" s="103" t="e">
+      <c r="F18" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H18" s="104">
+      <c r="H18" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
         <v>46174</v>
       </c>
-      <c r="I18" s="103">
+      <c r="I18" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
         <v>-1058940.870000002</v>
       </c>
@@ -7447,25 +7453,25 @@
         <f t="shared" si="0"/>
         <v>46419</v>
       </c>
-      <c r="C19" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D19" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="103" t="e">
+      <c r="C19" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C18</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F19" s="103" t="e">
+      <c r="F19" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H19" s="104">
+      <c r="H19" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
         <v>46204</v>
       </c>
-      <c r="I19" s="103">
+      <c r="I19" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
         <v>1111229.9000000013</v>
       </c>
@@ -7475,25 +7481,25 @@
         <f t="shared" si="0"/>
         <v>46447</v>
       </c>
-      <c r="C20" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D20" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="103" t="e">
+      <c r="C20" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C19</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F20" s="103" t="e">
+      <c r="F20" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H20" s="104">
+      <c r="H20" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
         <v>46235</v>
       </c>
-      <c r="I20" s="103">
+      <c r="I20" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
         <v>1111029.9400000004</v>
       </c>
@@ -7503,25 +7509,25 @@
         <f t="shared" si="0"/>
         <v>46478</v>
       </c>
-      <c r="C21" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D21" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="103" t="e">
+      <c r="C21" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D21" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C20</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F21" s="103" t="e">
+      <c r="F21" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="104">
+      <c r="H21" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
         <v>46266</v>
       </c>
-      <c r="I21" s="103">
+      <c r="I21" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
         <v>171182.9114285782</v>
       </c>
@@ -7531,17 +7537,17 @@
         <f t="shared" si="0"/>
         <v>46508</v>
       </c>
-      <c r="C22" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D22" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E22" s="103" t="e">
+      <c r="C22" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E22" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C21</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F22" s="103" t="e">
+      <c r="F22" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7551,17 +7557,17 @@
         <f t="shared" si="0"/>
         <v>46539</v>
       </c>
-      <c r="C23" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D23" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E23" s="103" t="e">
+      <c r="C23" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D23" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E23" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F23" s="103" t="e">
+      <c r="F23" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7571,17 +7577,17 @@
         <f t="shared" si="0"/>
         <v>46569</v>
       </c>
-      <c r="C24" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D24" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="103" t="e">
+      <c r="C24" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D24" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F24" s="103" t="e">
+      <c r="F24" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7591,17 +7597,17 @@
         <f t="shared" si="0"/>
         <v>46600</v>
       </c>
-      <c r="C25" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D25" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E25" s="103" t="e">
+      <c r="C25" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D25" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E25" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C24</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F25" s="103" t="e">
+      <c r="F25" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7611,17 +7617,17 @@
         <f t="shared" si="0"/>
         <v>46631</v>
       </c>
-      <c r="C26" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D26" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E26" s="103" t="e">
+      <c r="C26" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D26" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E26" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C25</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="103" t="e">
+      <c r="F26" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7631,17 +7637,17 @@
         <f t="shared" si="0"/>
         <v>46661</v>
       </c>
-      <c r="C27" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E27" s="103" t="e">
+      <c r="C27" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D27" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E27" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C26</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F27" s="103" t="e">
+      <c r="F27" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7651,17 +7657,17 @@
         <f t="shared" si="0"/>
         <v>46692</v>
       </c>
-      <c r="C28" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D28" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E28" s="103" t="e">
+      <c r="C28" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D28" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F28" s="103" t="e">
+      <c r="F28" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7671,17 +7677,17 @@
         <f t="shared" si="0"/>
         <v>46722</v>
       </c>
-      <c r="C29" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D29" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E29" s="103" t="e">
+      <c r="C29" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D29" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E29" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C28</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F29" s="103" t="e">
+      <c r="F29" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7691,17 +7697,17 @@
         <f t="shared" si="0"/>
         <v>46753</v>
       </c>
-      <c r="C30" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D30" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E30" s="103" t="e">
+      <c r="C30" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E30" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F30" s="103" t="e">
+      <c r="F30" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7711,17 +7717,17 @@
         <f t="shared" si="0"/>
         <v>46784</v>
       </c>
-      <c r="C31" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D31" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E31" s="103" t="e">
+      <c r="C31" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D31" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F31" s="103" t="e">
+      <c r="F31" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7731,17 +7737,17 @@
         <f t="shared" si="0"/>
         <v>46813</v>
       </c>
-      <c r="C32" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D32" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E32" s="103" t="e">
+      <c r="C32" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C31</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="103" t="e">
+      <c r="F32" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7751,17 +7757,17 @@
         <f t="shared" si="0"/>
         <v>46844</v>
       </c>
-      <c r="C33" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D33" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E33" s="103" t="e">
+      <c r="C33" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D33" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E33" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C32</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F33" s="103" t="e">
+      <c r="F33" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7771,17 +7777,17 @@
         <f t="shared" si="0"/>
         <v>46874</v>
       </c>
-      <c r="C34" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D34" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E34" s="103" t="e">
+      <c r="C34" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E34" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C33</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F34" s="103" t="e">
+      <c r="F34" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7791,17 +7797,17 @@
         <f t="shared" si="0"/>
         <v>46905</v>
       </c>
-      <c r="C35" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D35" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E35" s="103" t="e">
+      <c r="C35" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C34</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F35" s="103" t="e">
+      <c r="F35" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7811,17 +7817,17 @@
         <f t="shared" si="0"/>
         <v>46935</v>
       </c>
-      <c r="C36" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D36" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E36" s="103" t="e">
+      <c r="C36" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D36" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E36" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C35</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F36" s="103" t="e">
+      <c r="F36" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7831,17 +7837,17 @@
         <f t="shared" si="0"/>
         <v>46966</v>
       </c>
-      <c r="C37" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D37" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E37" s="103" t="e">
+      <c r="C37" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D37" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E37" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C36</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F37" s="103" t="e">
+      <c r="F37" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7851,17 +7857,17 @@
         <f t="shared" si="0"/>
         <v>46997</v>
       </c>
-      <c r="C38" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D38" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E38" s="103" t="e">
+      <c r="C38" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E38" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C37</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F38" s="103" t="e">
+      <c r="F38" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7871,17 +7877,17 @@
         <f t="shared" si="0"/>
         <v>47027</v>
       </c>
-      <c r="C39" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D39" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E39" s="103" t="e">
+      <c r="C39" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D39" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E39" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C38</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F39" s="103" t="e">
+      <c r="F39" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7891,17 +7897,17 @@
         <f t="shared" si="0"/>
         <v>47058</v>
       </c>
-      <c r="C40" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D40" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E40" s="103" t="e">
+      <c r="C40" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D40" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E40" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C39</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F40" s="103" t="e">
+      <c r="F40" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7911,17 +7917,17 @@
         <f t="shared" si="0"/>
         <v>47088</v>
       </c>
-      <c r="C41" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D41" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E41" s="103" t="e">
+      <c r="C41" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E41" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C40</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F41" s="103" t="e">
+      <c r="F41" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7931,17 +7937,17 @@
         <f t="shared" si="0"/>
         <v>47119</v>
       </c>
-      <c r="C42" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D42" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E42" s="103" t="e">
+      <c r="C42" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D42" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E42" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C41</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F42" s="103" t="e">
+      <c r="F42" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7951,17 +7957,17 @@
         <f t="shared" si="0"/>
         <v>47150</v>
       </c>
-      <c r="C43" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D43" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E43" s="103" t="e">
+      <c r="C43" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E43" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C42</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F43" s="103" t="e">
+      <c r="F43" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7971,17 +7977,17 @@
         <f t="shared" si="0"/>
         <v>47178</v>
       </c>
-      <c r="C44" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D44" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E44" s="103" t="e">
+      <c r="C44" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D44" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E44" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C43</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F44" s="103" t="e">
+      <c r="F44" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -7991,17 +7997,17 @@
         <f t="shared" si="0"/>
         <v>47209</v>
       </c>
-      <c r="C45" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D45" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E45" s="103" t="e">
+      <c r="C45" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D45" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E45" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C44</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F45" s="103" t="e">
+      <c r="F45" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8011,17 +8017,17 @@
         <f t="shared" si="0"/>
         <v>47239</v>
       </c>
-      <c r="C46" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D46" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E46" s="103" t="e">
+      <c r="C46" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D46" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E46" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C45</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F46" s="103" t="e">
+      <c r="F46" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8031,17 +8037,17 @@
         <f t="shared" si="0"/>
         <v>47270</v>
       </c>
-      <c r="C47" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D47" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E47" s="103" t="e">
+      <c r="C47" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E47" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C46</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F47" s="103" t="e">
+      <c r="F47" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8051,17 +8057,17 @@
         <f t="shared" si="0"/>
         <v>47300</v>
       </c>
-      <c r="C48" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D48" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E48" s="103" t="e">
+      <c r="C48" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D48" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E48" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C47</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F48" s="103" t="e">
+      <c r="F48" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8071,17 +8077,17 @@
         <f t="shared" si="0"/>
         <v>47331</v>
       </c>
-      <c r="C49" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D49" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E49" s="103" t="e">
+      <c r="C49" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D49" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C48</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F49" s="103" t="e">
+      <c r="F49" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8091,17 +8097,17 @@
         <f t="shared" si="0"/>
         <v>47362</v>
       </c>
-      <c r="C50" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D50" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E50" s="103" t="e">
+      <c r="C50" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D50" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E50" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C49</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F50" s="103" t="e">
+      <c r="F50" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8111,17 +8117,17 @@
         <f t="shared" si="0"/>
         <v>47392</v>
       </c>
-      <c r="C51" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D51" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E51" s="103" t="e">
+      <c r="C51" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D51" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E51" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C50</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F51" s="103" t="e">
+      <c r="F51" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8131,17 +8137,17 @@
         <f t="shared" si="0"/>
         <v>47423</v>
       </c>
-      <c r="C52" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D52" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E52" s="103" t="e">
+      <c r="C52" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D52" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E52" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C51</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F52" s="103" t="e">
+      <c r="F52" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8151,17 +8157,17 @@
         <f t="shared" si="0"/>
         <v>47453</v>
       </c>
-      <c r="C53" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D53" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E53" s="103" t="e">
+      <c r="C53" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D53" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E53" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C52</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F53" s="103" t="e">
+      <c r="F53" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8171,17 +8177,17 @@
         <f t="shared" si="0"/>
         <v>47484</v>
       </c>
-      <c r="C54" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D54" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E54" s="103" t="e">
+      <c r="C54" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D54" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E54" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C53</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F54" s="103" t="e">
+      <c r="F54" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8191,17 +8197,17 @@
         <f t="shared" si="0"/>
         <v>47515</v>
       </c>
-      <c r="C55" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D55" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E55" s="103" t="e">
+      <c r="C55" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E55" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C54</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F55" s="103" t="e">
+      <c r="F55" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8211,17 +8217,17 @@
         <f t="shared" si="0"/>
         <v>47543</v>
       </c>
-      <c r="C56" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D56" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E56" s="103" t="e">
+      <c r="C56" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D56" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E56" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C55</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F56" s="103" t="e">
+      <c r="F56" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8231,17 +8237,17 @@
         <f t="shared" si="0"/>
         <v>47574</v>
       </c>
-      <c r="C57" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D57" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E57" s="103" t="e">
+      <c r="C57" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D57" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E57" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C56</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F57" s="103" t="e">
+      <c r="F57" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8251,17 +8257,17 @@
         <f t="shared" si="0"/>
         <v>47604</v>
       </c>
-      <c r="C58" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D58" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58" s="103" t="e">
+      <c r="C58" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D58" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C57</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F58" s="103" t="e">
+      <c r="F58" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8271,17 +8277,17 @@
         <f t="shared" si="0"/>
         <v>47635</v>
       </c>
-      <c r="C59" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D59" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E59" s="103" t="e">
+      <c r="C59" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D59" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E59" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C58</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F59" s="103" t="e">
+      <c r="F59" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8291,17 +8297,17 @@
         <f t="shared" si="0"/>
         <v>47665</v>
       </c>
-      <c r="C60" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D60" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E60" s="103" t="e">
+      <c r="C60" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E60" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C59</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F60" s="103" t="e">
+      <c r="F60" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8311,17 +8317,17 @@
         <f t="shared" si="0"/>
         <v>47696</v>
       </c>
-      <c r="C61" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D61" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E61" s="103" t="e">
+      <c r="C61" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D61" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E61" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F61" s="103" t="e">
+      <c r="F61" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8331,17 +8337,17 @@
         <f t="shared" si="0"/>
         <v>47727</v>
       </c>
-      <c r="C62" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D62" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E62" s="103" t="e">
+      <c r="C62" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D62" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E62" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C61</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F62" s="103" t="e">
+      <c r="F62" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8351,17 +8357,17 @@
         <f t="shared" si="0"/>
         <v>47757</v>
       </c>
-      <c r="C63" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D63" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E63" s="103" t="e">
+      <c r="C63" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D63" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E63" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C62</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F63" s="103" t="e">
+      <c r="F63" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8371,17 +8377,17 @@
         <f t="shared" si="0"/>
         <v>47788</v>
       </c>
-      <c r="C64" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D64" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E64" s="103" t="e">
+      <c r="C64" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D64" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E64" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C63</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F64" s="103" t="e">
+      <c r="F64" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8391,17 +8397,17 @@
         <f t="shared" si="0"/>
         <v>47818</v>
       </c>
-      <c r="C65" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="D65" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="E65" s="103" t="e">
+      <c r="C65" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="D65" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E65" s="102" t="e">
         <f>Table9[[#This Row],[General Balance]]-C64</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F65" s="103" t="e">
+      <c r="F65" s="102" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8617,17 +8623,17 @@
     </row>
     <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="114" t="s">
+      <c r="C6" s="113" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="116"/>
-      <c r="H6" s="111" t="s">
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="115"/>
+      <c r="H6" s="110" t="s">
         <v>205</v>
       </c>
-      <c r="I6" s="112"/>
-      <c r="J6" s="113"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C7" s="63" t="s">
@@ -8688,10 +8694,10 @@
       <c r="I9" s="65">
         <v>37000000</v>
       </c>
-      <c r="J9" s="102" t="s">
+      <c r="J9" s="101" t="s">
         <v>271</v>
       </c>
-      <c r="K9" s="101"/>
+      <c r="K9" s="100"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C10" s="53" t="s">
@@ -8879,20 +8885,20 @@
       <c r="C28" s="60" t="s">
         <v>241</v>
       </c>
-      <c r="D28" s="117">
+      <c r="D28" s="116">
         <f>SUM(Table5[Incoming])-SUM(Table5[Outcoming])</f>
         <v>5419770</v>
       </c>
-      <c r="E28" s="118"/>
-      <c r="F28" s="119"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="118"/>
       <c r="H28" s="52" t="s">
         <v>241</v>
       </c>
-      <c r="I28" s="120">
+      <c r="I28" s="119">
         <f>SUM(Table6[Amount])</f>
         <v>47211609.670000002</v>
       </c>
-      <c r="J28" s="121"/>
+      <c r="J28" s="120"/>
       <c r="K28" s="40"/>
     </row>
     <row r="29" spans="3:14" x14ac:dyDescent="0.3">
@@ -8919,7 +8925,7 @@
   <dimension ref="E5:AE33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="45.6640625" bestFit="1" customWidth="1"/>
@@ -8943,10 +8949,10 @@
   </cols>
   <sheetData>
     <row r="5" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="AB5" s="122"/>
-      <c r="AC5" s="122"/>
-      <c r="AD5" s="122"/>
-      <c r="AE5" s="122"/>
+      <c r="AB5" s="121"/>
+      <c r="AC5" s="121"/>
+      <c r="AD5" s="121"/>
+      <c r="AE5" s="121"/>
     </row>
     <row r="8" spans="5:31" x14ac:dyDescent="0.3">
       <c r="E8" s="72" t="s">
@@ -9015,13 +9021,13 @@
       </c>
     </row>
     <row r="14" spans="5:31" ht="36.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E14" s="94" t="s">
+      <c r="E14" s="93" t="s">
         <v>264</v>
       </c>
-      <c r="F14" s="94" t="s">
+      <c r="F14" s="93" t="s">
         <v>262</v>
       </c>
-      <c r="G14" s="94" t="s">
+      <c r="G14" s="93" t="s">
         <v>263</v>
       </c>
     </row>
@@ -9041,31 +9047,31 @@
       </c>
     </row>
     <row r="17" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E17" s="91" t="s">
+      <c r="E17" s="90" t="s">
         <v>261</v>
       </c>
-      <c r="F17" s="93">
+      <c r="F17" s="92">
         <v>0.3</v>
       </c>
-      <c r="G17" s="92">
+      <c r="G17" s="91">
         <f>Tracker!$C$2*Portfolio!F17</f>
         <v>15000000</v>
       </c>
-      <c r="H17" s="98" t="s">
+      <c r="H17" s="97" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="18" spans="5:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="E18" s="95" t="s">
+      <c r="E18" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="96">
+      <c r="F18" s="95">
         <v>0.15</v>
       </c>
-      <c r="G18" s="97">
+      <c r="G18" s="96">
         <v>6000000</v>
       </c>
-      <c r="H18" s="99" t="s">
+      <c r="H18" s="98" t="s">
         <v>289</v>
       </c>
     </row>
@@ -9079,7 +9085,7 @@
       <c r="G19" s="48">
         <v>6000000</v>
       </c>
-      <c r="H19" s="100"/>
+      <c r="H19" s="99"/>
     </row>
     <row r="20" spans="5:15" x14ac:dyDescent="0.3">
       <c r="E20" s="40" t="s">
@@ -9092,23 +9098,23 @@
         <f>Tracker!$C$2*Portfolio!F20</f>
         <v>22000000</v>
       </c>
-      <c r="H20" s="100" t="s">
+      <c r="H20" s="99" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="21" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E21" s="95" t="s">
+      <c r="E21" s="94" t="s">
         <v>234</v>
       </c>
-      <c r="F21" s="96">
+      <c r="F21" s="95">
         <f>1-SUM(F17:F20)</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="G21" s="97">
+      <c r="G21" s="96">
         <f>Tracker!$C$2*Portfolio!F21</f>
         <v>500000.00000000047</v>
       </c>
-      <c r="H21" s="99" t="s">
+      <c r="H21" s="98" t="s">
         <v>290</v>
       </c>
     </row>
@@ -9163,7 +9169,7 @@
       <c r="I24" s="48">
         <v>3237.3</v>
       </c>
-      <c r="J24" s="88" t="s">
+      <c r="J24" s="102" t="s">
         <v>210</v>
       </c>
       <c r="K24" s="48">
@@ -9176,7 +9182,7 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N24" s="90" t="e">
+      <c r="N24" s="123" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
@@ -9198,7 +9204,7 @@
       <c r="I25" s="48">
         <v>3213.78</v>
       </c>
-      <c r="J25" s="88" t="s">
+      <c r="J25" s="102" t="s">
         <v>210</v>
       </c>
       <c r="K25" s="48">
@@ -9211,7 +9217,7 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N25" s="90" t="e">
+      <c r="N25" s="123" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
@@ -9221,244 +9227,248 @@
       <c r="E26" s="87" t="s">
         <v>210</v>
       </c>
-      <c r="F26" s="87" t="s">
-        <v>210</v>
+      <c r="F26" s="87">
+        <v>46226</v>
       </c>
       <c r="G26" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="88"/>
-      <c r="I26" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="J26" s="88" t="s">
-        <v>210</v>
-      </c>
-      <c r="K26" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="L26" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="M26" s="89" t="e">
+      <c r="H26" s="88">
+        <v>100</v>
+      </c>
+      <c r="I26" s="48">
+        <v>3237.3</v>
+      </c>
+      <c r="J26" s="102">
+        <v>3257.13</v>
+      </c>
+      <c r="K26" s="48">
+        <f>H26*I26</f>
+        <v>323730</v>
+      </c>
+      <c r="L26" s="48">
+        <f>H26*J26</f>
+        <v>325713</v>
+      </c>
+      <c r="M26" s="89">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N26" s="90" t="e">
+        <v>1983</v>
+      </c>
+      <c r="N26" s="123">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
-        <v>#VALUE!</v>
+        <v>0.6125474932814382</v>
       </c>
       <c r="O26" s="40"/>
     </row>
     <row r="27" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E27" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="F27" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="G27" s="91" t="s">
+      <c r="E27" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="F27" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="G27" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="H27" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="I27" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="J27" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="K27" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="L27" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="M27" s="91" t="e">
+      <c r="H27" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="I27" s="91" t="s">
+        <v>210</v>
+      </c>
+      <c r="J27" s="122" t="s">
+        <v>210</v>
+      </c>
+      <c r="K27" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="L27" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="M27" s="90" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N27" s="91" t="e">
+      <c r="N27" s="124" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O27" s="91"/>
+      <c r="O27" s="90"/>
     </row>
     <row r="28" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E28" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="F28" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="G28" s="91" t="s">
+      <c r="E28" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="F28" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="G28" s="90" t="s">
         <v>281</v>
       </c>
-      <c r="H28" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="I28" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="J28" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="K28" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="L28" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="M28" s="91" t="e">
+      <c r="H28" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="I28" s="91" t="s">
+        <v>210</v>
+      </c>
+      <c r="J28" s="122" t="s">
+        <v>210</v>
+      </c>
+      <c r="K28" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="L28" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="M28" s="90" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N28" s="91" t="e">
+      <c r="N28" s="124" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O28" s="91"/>
+      <c r="O28" s="90"/>
     </row>
     <row r="29" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E29" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="F29" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="G29" s="91" t="s">
+      <c r="E29" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="F29" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="G29" s="90" t="s">
         <v>282</v>
       </c>
-      <c r="H29" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="I29" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="J29" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="K29" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="L29" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="M29" s="91" t="e">
+      <c r="H29" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="I29" s="91" t="s">
+        <v>210</v>
+      </c>
+      <c r="J29" s="122" t="s">
+        <v>210</v>
+      </c>
+      <c r="K29" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="L29" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="M29" s="90" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N29" s="91" t="e">
+      <c r="N29" s="124" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="91"/>
+      <c r="O29" s="90"/>
     </row>
     <row r="30" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E30" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="F30" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="G30" s="91" t="s">
+      <c r="E30" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="F30" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="G30" s="90" t="s">
         <v>283</v>
       </c>
-      <c r="H30" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="I30" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="J30" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="K30" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="L30" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="M30" s="91" t="e">
+      <c r="H30" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="I30" s="91" t="s">
+        <v>210</v>
+      </c>
+      <c r="J30" s="122" t="s">
+        <v>210</v>
+      </c>
+      <c r="K30" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="L30" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="M30" s="90" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N30" s="91" t="e">
+      <c r="N30" s="124" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O30" s="91"/>
+      <c r="O30" s="90"/>
     </row>
     <row r="31" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E31" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="F31" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="G31" s="91" t="s">
+      <c r="E31" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="F31" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="G31" s="90" t="s">
         <v>284</v>
       </c>
-      <c r="H31" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="I31" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="J31" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="K31" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="L31" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="M31" s="91" t="e">
+      <c r="H31" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="I31" s="91" t="s">
+        <v>210</v>
+      </c>
+      <c r="J31" s="122" t="s">
+        <v>210</v>
+      </c>
+      <c r="K31" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="L31" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="M31" s="90" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N31" s="91" t="e">
+      <c r="N31" s="124" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O31" s="91"/>
+      <c r="O31" s="90"/>
     </row>
     <row r="32" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E32" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="F32" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="G32" s="91" t="s">
+      <c r="E32" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="F32" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="90" t="s">
         <v>285</v>
       </c>
-      <c r="H32" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="I32" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="J32" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="K32" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="L32" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="M32" s="91" t="e">
+      <c r="H32" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="I32" s="91" t="s">
+        <v>210</v>
+      </c>
+      <c r="J32" s="122" t="s">
+        <v>210</v>
+      </c>
+      <c r="K32" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="L32" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="M32" s="90" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N32" s="91" t="e">
+      <c r="N32" s="124" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O32" s="91"/>
+      <c r="O32" s="90"/>
     </row>
     <row r="33" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -9467,7 +9477,7 @@
     <mergeCell ref="AD5:AE5"/>
   </mergeCells>
   <conditionalFormatting sqref="F17:F21">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>SUM($F$17:$F$21)&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Management/Finantial Planning.xlsx
+++ b/Management/Finantial Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aciww-my.sharepoint.com/personal/daniel_lozanobarrero_aciworldwide_com/Documents/Documents/My-Notes/Management/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{9D2CB4AA-B5D0-4EF5-A36A-0DE75FD5CA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F355AD36-8492-4F75-B7A4-C61BD189AFFC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D432296-E4FE-41EB-A404-B51F2DD37755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{F8FCC151-5DC7-4472-A863-0C0A531A258D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F8FCC151-5DC7-4472-A863-0C0A531A258D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="303">
   <si>
     <t>Wellbeing Lifestyle</t>
   </si>
@@ -983,7 +984,7 @@
     <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
     <numFmt numFmtId="175" formatCode="mmmm\ yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1751,6 +1752,15 @@
     <xf numFmtId="172" fontId="4" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1790,15 +1800,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Check Cell" xfId="5" builtinId="23"/>
@@ -1810,21 +1811,10 @@
   </cellStyles>
   <dxfs count="80">
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1837,6 +1827,10 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="172" formatCode="#,##0.00\ [$COP]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1945,6 +1939,13 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2786,22 +2787,22 @@
                 <c:formatCode>mmmm\ yyyy</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>46113</c:v>
+                  <c:v>46143</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46143</c:v>
+                  <c:v>46174</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46174</c:v>
+                  <c:v>46204</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46204</c:v>
+                  <c:v>46235</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46235</c:v>
+                  <c:v>46266</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46266</c:v>
+                  <c:v>46296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2813,22 +2814,22 @@
                 <c:formatCode>[$COP]\ #,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>52790636.799999997</c:v>
+                  <c:v>55912013.149999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55912013.149999999</c:v>
+                  <c:v>61491091.960000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>61491091.960000001</c:v>
+                  <c:v>64900000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>64900000</c:v>
+                  <c:v>65265421.539999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65265421.539999999</c:v>
+                  <c:v>69506976.569999993</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>69506976.569999993</c:v>
+                  <c:v>74189383.569999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3050,7 +3051,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3058,6 +3058,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -3251,22 +3252,22 @@
                 <c:formatCode>mmmm\ yyyy</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>46113</c:v>
+                  <c:v>46143</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46143</c:v>
+                  <c:v>46174</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46174</c:v>
+                  <c:v>46204</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46204</c:v>
+                  <c:v>46235</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46235</c:v>
+                  <c:v>46266</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46266</c:v>
+                  <c:v>46296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3278,22 +3279,22 @@
                 <c:formatCode>[$COP]\ #,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1253541.980000007</c:v>
+                  <c:v>1398761.5899999989</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1398761.5899999989</c:v>
+                  <c:v>-1058940.870000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1058940.870000002</c:v>
+                  <c:v>1111229.9000000013</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1111229.9000000013</c:v>
+                  <c:v>1111029.9400000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1111029.9400000004</c:v>
+                  <c:v>171182.9114285782</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>171182.9114285782</c:v>
+                  <c:v>-162269.05999999959</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3515,7 +3516,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3523,6 +3523,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -4178,7 +4179,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4186,6 +4186,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6005,36 +6006,36 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}" name="Table7" displayName="Table7" ref="E8:G14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}" name="Table7" displayName="Table7" ref="E8:G14" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="E8:G14" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{05264107-3C50-4DC4-BA66-3C598C57D362}" name="Condition" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{4F494527-B966-4283-AC8D-DDFC53922A3A}" name="Action" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{A8687214-DFD3-4202-A740-25119BF98217}" name="% Adjusted" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{05264107-3C50-4DC4-BA66-3C598C57D362}" name="Condition" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{4F494527-B966-4283-AC8D-DDFC53922A3A}" name="Action" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{A8687214-DFD3-4202-A740-25119BF98217}" name="% Adjusted" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}" name="Table10" displayName="Table10" ref="E23:O32" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}" name="Table10" displayName="Table10" ref="E23:O32" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="E23:O32" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{EF8D02AC-323D-45AB-AE15-91832BDC7B4E}" name="Date Bought" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{712A0457-F103-4A5F-89A3-F38940B6301F}" name="Date Sold" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{8B72E438-7296-4BE9-B114-652C18C0973F}" name="Asset" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{C9EB17C7-CF17-4BB1-8390-4A0AA329B909}" name="Units" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{38A379BB-56A1-4C91-8A79-E09D76997328}" name="Price Buy" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{70D6BA55-3422-446B-A79B-9ED0B67E93BD}" name="Price Sell" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{D264BB00-77B0-482C-925B-C8BD072B81A0}" name="Total Invested (COP)" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{9369D078-2888-4CE1-919F-E9A0C05D615C}" name="Total Value" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{313DF1E8-730D-4C1D-BB28-A01F2D131415}" name="Gain/Loss (COP)" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{EF8D02AC-323D-45AB-AE15-91832BDC7B4E}" name="Date Bought" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{712A0457-F103-4A5F-89A3-F38940B6301F}" name="Date Sold" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{8B72E438-7296-4BE9-B114-652C18C0973F}" name="Asset" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{C9EB17C7-CF17-4BB1-8390-4A0AA329B909}" name="Units" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{38A379BB-56A1-4C91-8A79-E09D76997328}" name="Price Buy" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{70D6BA55-3422-446B-A79B-9ED0B67E93BD}" name="Price Sell" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{D264BB00-77B0-482C-925B-C8BD072B81A0}" name="Total Invested (COP)" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{9369D078-2888-4CE1-919F-E9A0C05D615C}" name="Total Value" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{313DF1E8-730D-4C1D-BB28-A01F2D131415}" name="Gain/Loss (COP)" dataDxfId="2">
       <calculatedColumnFormula>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{CD1E921A-1374-4429-89D9-1676BA8642FB}" name="% Return" dataDxfId="0" dataCellStyle="Percent">
+    <tableColumn id="10" xr3:uid="{CD1E921A-1374-4429-89D9-1676BA8642FB}" name="% Return" dataDxfId="1" dataCellStyle="Percent">
       <calculatedColumnFormula>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{36B25BAF-3792-45C1-AE34-3EDA3274070F}" name="Notes" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{36B25BAF-3792-45C1-AE34-3EDA3274070F}" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6148,15 +6149,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}" name="Table3" displayName="Table3" ref="E16:H21" totalsRowShown="0" headerRowDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}" name="Table3" displayName="Table3" ref="E16:H21" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="E16:H21" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{88178FBB-1C68-4443-9D29-711B96CC8F3C}" name="Investment Type" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{AF13EBFA-AD22-4799-B232-349084129FC2}" name="Percentage" dataDxfId="21" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{06249914-8982-4D40-BF2A-A24479258B7E}" name="Current Amount" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{88178FBB-1C68-4443-9D29-711B96CC8F3C}" name="Investment Type" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{AF13EBFA-AD22-4799-B232-349084129FC2}" name="Percentage" dataDxfId="20" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{06249914-8982-4D40-BF2A-A24479258B7E}" name="Current Amount" dataDxfId="19">
       <calculatedColumnFormula>Tracker!$C$2*Portfolio!F17</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BE746FA0-4394-410B-BFFB-E4580C3454EF}" name="Notes" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{BE746FA0-4394-410B-BFFB-E4580C3454EF}" name="Notes" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6481,23 +6482,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0D8A61-82F4-4CC6-B552-F68414C6EAB4}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:M1048575"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15">
       <c r="A1" s="16" t="s">
         <v>196</v>
       </c>
@@ -6505,7 +6506,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15">
       <c r="A2" s="16" t="s">
         <v>8</v>
       </c>
@@ -6514,8 +6515,8 @@
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="15" thickBot="1"/>
+    <row r="5" spans="1:13" ht="15.75" thickBot="1">
       <c r="C5" s="14" t="s">
         <v>266</v>
       </c>
@@ -6531,10 +6532,10 @@
         <v>1120968.5714285714</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13">
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15">
       <c r="C7" s="33" t="s">
         <v>214</v>
       </c>
@@ -6566,7 +6567,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13">
       <c r="C8" s="41" t="s">
         <v>5</v>
       </c>
@@ -6601,7 +6602,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13">
       <c r="C9" s="41" t="s">
         <v>202</v>
       </c>
@@ -6637,7 +6638,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15" thickBot="1">
       <c r="C10" s="67" t="s">
         <v>265</v>
       </c>
@@ -6668,7 +6669,7 @@
       <c r="L10" s="28"/>
       <c r="M10" s="40"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13">
       <c r="C11" s="83" t="s">
         <v>0</v>
       </c>
@@ -6704,7 +6705,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13">
       <c r="C12" s="78" t="s">
         <v>17</v>
       </c>
@@ -6739,7 +6740,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13">
       <c r="C13" s="80" t="s">
         <v>14</v>
       </c>
@@ -6774,7 +6775,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13">
       <c r="C14" s="82" t="s">
         <v>17</v>
       </c>
@@ -6810,7 +6811,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13">
       <c r="G15" s="41" t="s">
         <v>226</v>
       </c>
@@ -6835,7 +6836,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13">
       <c r="G16" s="41" t="s">
         <v>233</v>
       </c>
@@ -6856,7 +6857,7 @@
       <c r="L16" s="28"/>
       <c r="M16" s="40"/>
     </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:13">
       <c r="G17" s="42" t="s">
         <v>6</v>
       </c>
@@ -6880,7 +6881,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:13">
       <c r="G18" s="42" t="s">
         <v>15</v>
       </c>
@@ -6906,8 +6907,8 @@
         <v>231</v>
       </c>
     </row>
-    <row r="20" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:13" ht="15" thickBot="1"/>
+    <row r="21" spans="3:13" ht="15.75" thickBot="1">
       <c r="C21" s="14" t="s">
         <v>268</v>
       </c>
@@ -6916,8 +6917,8 @@
         <v>4412737.9414285719</v>
       </c>
     </row>
-    <row r="22" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:13" ht="15" thickBot="1"/>
+    <row r="23" spans="3:13" ht="15.75" thickBot="1">
       <c r="C23" s="4" t="str">
         <f>"Savings on " &amp; TEXT(B2, "dd.MM.yyyy")</f>
         <v>Savings on 21.12.2025</v>
@@ -6933,20 +6934,20 @@
         <v>470000</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:13">
       <c r="C24" s="27" t="s">
         <v>206</v>
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:13">
       <c r="D25" s="1"/>
       <c r="J25" s="1">
         <f>SUM(J9:J11)</f>
         <v>213800</v>
       </c>
     </row>
-    <row r="26" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:13" ht="15" thickBot="1">
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -6958,7 +6959,7 @@
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:13">
       <c r="C28" s="4" t="s">
         <v>63</v>
       </c>
@@ -6967,7 +6968,7 @@
         <v>3703.7037037037035</v>
       </c>
     </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:13">
       <c r="C29" s="4" t="s">
         <v>20</v>
       </c>
@@ -6976,10 +6977,10 @@
         <v>3194.8881789137376</v>
       </c>
     </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:13" ht="15">
       <c r="C31" s="15"/>
     </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:13" ht="15">
       <c r="C32" s="18" t="s">
         <v>197</v>
       </c>
@@ -6993,7 +6994,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:6" ht="15">
       <c r="C33" s="19" t="s">
         <v>198</v>
       </c>
@@ -7010,7 +7011,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:6" ht="15">
       <c r="C34" s="19" t="s">
         <v>199</v>
       </c>
@@ -7027,7 +7028,7 @@
         <v>46320</v>
       </c>
     </row>
-    <row r="1048575" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1048575" spans="1:1">
       <c r="A1048575" s="31">
         <v>46048</v>
       </c>
@@ -7046,19 +7047,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8712021-9BAC-49DD-9632-A9B86C4FE255}">
   <dimension ref="B1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.75" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:9" ht="15" thickBot="1"/>
+    <row r="2" spans="2:9" ht="15.75" thickBot="1">
       <c r="B2" s="105" t="s">
         <v>299</v>
       </c>
@@ -7066,7 +7067,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="15">
       <c r="B5" s="40" t="s">
         <v>291</v>
       </c>
@@ -7082,12 +7083,12 @@
       <c r="F5" s="40" t="s">
         <v>296</v>
       </c>
-      <c r="H5" s="109" t="s">
+      <c r="H5" s="112" t="s">
         <v>297</v>
       </c>
-      <c r="I5" s="109"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="112"/>
+    </row>
+    <row r="6" spans="2:9" ht="15">
       <c r="B6" s="87">
         <v>46023</v>
       </c>
@@ -7112,7 +7113,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9">
       <c r="B7" s="87">
         <f>EDATE(B6,1)</f>
         <v>46054</v>
@@ -7135,14 +7136,14 @@
       </c>
       <c r="H7" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="I7" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
-        <v>52790636.799999997</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+        <v>55912013.149999999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
       <c r="B8" s="87">
         <f t="shared" ref="B8:B65" si="0">EDATE(B7,1)</f>
         <v>46082</v>
@@ -7165,14 +7166,14 @@
       </c>
       <c r="H8" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="I8" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
-        <v>55912013.149999999</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+        <v>61491091.960000001</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
       <c r="B9" s="87">
         <f t="shared" si="0"/>
         <v>46113</v>
@@ -7195,14 +7196,14 @@
       </c>
       <c r="H9" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="I9" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
-        <v>61491091.960000001</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+        <v>64900000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
       <c r="B10" s="87">
         <f t="shared" si="0"/>
         <v>46143</v>
@@ -7225,14 +7226,14 @@
       </c>
       <c r="H10" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="I10" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
-        <v>64900000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+        <v>65265421.539999999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
       <c r="B11" s="87">
         <f t="shared" si="0"/>
         <v>46174</v>
@@ -7255,14 +7256,14 @@
       </c>
       <c r="H11" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="I11" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
-        <v>65265421.539999999</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+        <v>69506976.569999993</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
       <c r="B12" s="87">
         <f t="shared" si="0"/>
         <v>46204</v>
@@ -7285,14 +7286,14 @@
       </c>
       <c r="H12" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="I12" s="102">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
-        <v>69506976.569999993</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+        <v>74189383.569999993</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
       <c r="B13" s="87">
         <f t="shared" si="0"/>
         <v>46235</v>
@@ -7313,7 +7314,7 @@
         <v>1111029.9400000004</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" ht="15">
       <c r="B14" s="87">
         <f t="shared" si="0"/>
         <v>46266</v>
@@ -7333,29 +7334,30 @@
         <f>Main!D21-E14</f>
         <v>171182.9114285782</v>
       </c>
-      <c r="H14" s="109" t="s">
+      <c r="H14" s="112" t="s">
         <v>298</v>
       </c>
-      <c r="I14" s="109"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I14" s="112"/>
+    </row>
+    <row r="15" spans="2:9" ht="15">
       <c r="B15" s="87">
         <f t="shared" si="0"/>
         <v>46296</v>
       </c>
-      <c r="C15" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E15" s="102" t="e">
+      <c r="C15" s="102">
+        <f>C14+4682407</f>
+        <v>74189383.569999993</v>
+      </c>
+      <c r="D15" s="102">
+        <v>25255077.379999999</v>
+      </c>
+      <c r="E15" s="102">
         <f>Table9[[#This Row],[General Balance]]-C14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F15" s="102" t="e">
+        <v>4682407</v>
+      </c>
+      <c r="F15" s="102">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>-162269.05999999959</v>
       </c>
       <c r="H15" s="104" t="s">
         <v>291</v>
@@ -7364,7 +7366,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9">
       <c r="B16" s="87">
         <f t="shared" si="0"/>
         <v>46327</v>
@@ -7385,14 +7387,14 @@
       </c>
       <c r="H16" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="I16" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
-        <v>1253541.980000007</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+        <v>1398761.5899999989</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
       <c r="B17" s="87">
         <f t="shared" si="0"/>
         <v>46357</v>
@@ -7413,14 +7415,14 @@
       </c>
       <c r="H17" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="I17" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
-        <v>1398761.5899999989</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+        <v>-1058940.870000002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
       <c r="B18" s="87">
         <f t="shared" si="0"/>
         <v>46388</v>
@@ -7441,14 +7443,14 @@
       </c>
       <c r="H18" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="I18" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
-        <v>-1058940.870000002</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+        <v>1111229.9000000013</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
       <c r="B19" s="87">
         <f t="shared" si="0"/>
         <v>46419</v>
@@ -7469,14 +7471,14 @@
       </c>
       <c r="H19" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="I19" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
-        <v>1111229.9000000013</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+        <v>1111029.9400000004</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
       <c r="B20" s="87">
         <f t="shared" si="0"/>
         <v>46447</v>
@@ -7497,14 +7499,14 @@
       </c>
       <c r="H20" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="I20" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
-        <v>1111029.9400000004</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+        <v>171182.9114285782</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
       <c r="B21" s="87">
         <f t="shared" si="0"/>
         <v>46478</v>
@@ -7525,14 +7527,14 @@
       </c>
       <c r="H21" s="103">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="I21" s="102">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
-        <v>171182.9114285782</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+        <v>-162269.05999999959</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
       <c r="B22" s="87">
         <f t="shared" si="0"/>
         <v>46508</v>
@@ -7552,7 +7554,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9">
       <c r="B23" s="87">
         <f t="shared" si="0"/>
         <v>46539</v>
@@ -7572,7 +7574,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9">
       <c r="B24" s="87">
         <f t="shared" si="0"/>
         <v>46569</v>
@@ -7592,7 +7594,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9">
       <c r="B25" s="87">
         <f t="shared" si="0"/>
         <v>46600</v>
@@ -7612,7 +7614,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9">
       <c r="B26" s="87">
         <f t="shared" si="0"/>
         <v>46631</v>
@@ -7632,7 +7634,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9">
       <c r="B27" s="87">
         <f t="shared" si="0"/>
         <v>46661</v>
@@ -7652,7 +7654,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9">
       <c r="B28" s="87">
         <f t="shared" si="0"/>
         <v>46692</v>
@@ -7672,7 +7674,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9">
       <c r="B29" s="87">
         <f t="shared" si="0"/>
         <v>46722</v>
@@ -7692,7 +7694,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9">
       <c r="B30" s="87">
         <f t="shared" si="0"/>
         <v>46753</v>
@@ -7712,7 +7714,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9">
       <c r="B31" s="87">
         <f t="shared" si="0"/>
         <v>46784</v>
@@ -7732,7 +7734,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9">
       <c r="B32" s="87">
         <f t="shared" si="0"/>
         <v>46813</v>
@@ -7752,7 +7754,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6">
       <c r="B33" s="87">
         <f t="shared" si="0"/>
         <v>46844</v>
@@ -7772,7 +7774,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6">
       <c r="B34" s="87">
         <f t="shared" si="0"/>
         <v>46874</v>
@@ -7792,7 +7794,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6">
       <c r="B35" s="87">
         <f t="shared" si="0"/>
         <v>46905</v>
@@ -7812,7 +7814,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6">
       <c r="B36" s="87">
         <f t="shared" si="0"/>
         <v>46935</v>
@@ -7832,7 +7834,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6">
       <c r="B37" s="87">
         <f t="shared" si="0"/>
         <v>46966</v>
@@ -7852,7 +7854,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6">
       <c r="B38" s="87">
         <f t="shared" si="0"/>
         <v>46997</v>
@@ -7872,7 +7874,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6">
       <c r="B39" s="87">
         <f t="shared" si="0"/>
         <v>47027</v>
@@ -7892,7 +7894,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6">
       <c r="B40" s="87">
         <f t="shared" si="0"/>
         <v>47058</v>
@@ -7912,7 +7914,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6">
       <c r="B41" s="87">
         <f t="shared" si="0"/>
         <v>47088</v>
@@ -7932,7 +7934,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6">
       <c r="B42" s="87">
         <f t="shared" si="0"/>
         <v>47119</v>
@@ -7952,7 +7954,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6">
       <c r="B43" s="87">
         <f t="shared" si="0"/>
         <v>47150</v>
@@ -7972,7 +7974,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6">
       <c r="B44" s="87">
         <f t="shared" si="0"/>
         <v>47178</v>
@@ -7992,7 +7994,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6">
       <c r="B45" s="87">
         <f t="shared" si="0"/>
         <v>47209</v>
@@ -8012,7 +8014,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6">
       <c r="B46" s="87">
         <f t="shared" si="0"/>
         <v>47239</v>
@@ -8032,7 +8034,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6">
       <c r="B47" s="87">
         <f t="shared" si="0"/>
         <v>47270</v>
@@ -8052,7 +8054,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6">
       <c r="B48" s="87">
         <f t="shared" si="0"/>
         <v>47300</v>
@@ -8072,7 +8074,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6">
       <c r="B49" s="87">
         <f t="shared" si="0"/>
         <v>47331</v>
@@ -8092,7 +8094,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6">
       <c r="B50" s="87">
         <f t="shared" si="0"/>
         <v>47362</v>
@@ -8112,7 +8114,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6">
       <c r="B51" s="87">
         <f t="shared" si="0"/>
         <v>47392</v>
@@ -8132,7 +8134,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6">
       <c r="B52" s="87">
         <f t="shared" si="0"/>
         <v>47423</v>
@@ -8152,7 +8154,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6">
       <c r="B53" s="87">
         <f t="shared" si="0"/>
         <v>47453</v>
@@ -8172,7 +8174,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6">
       <c r="B54" s="87">
         <f t="shared" si="0"/>
         <v>47484</v>
@@ -8192,7 +8194,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6">
       <c r="B55" s="87">
         <f t="shared" si="0"/>
         <v>47515</v>
@@ -8212,7 +8214,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6">
       <c r="B56" s="87">
         <f t="shared" si="0"/>
         <v>47543</v>
@@ -8232,7 +8234,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6">
       <c r="B57" s="87">
         <f t="shared" si="0"/>
         <v>47574</v>
@@ -8252,7 +8254,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6">
       <c r="B58" s="87">
         <f t="shared" si="0"/>
         <v>47604</v>
@@ -8272,7 +8274,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6">
       <c r="B59" s="87">
         <f t="shared" si="0"/>
         <v>47635</v>
@@ -8292,7 +8294,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6">
       <c r="B60" s="87">
         <f t="shared" si="0"/>
         <v>47665</v>
@@ -8312,7 +8314,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6">
       <c r="B61" s="87">
         <f t="shared" si="0"/>
         <v>47696</v>
@@ -8332,7 +8334,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6">
       <c r="B62" s="87">
         <f t="shared" si="0"/>
         <v>47727</v>
@@ -8352,7 +8354,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6">
       <c r="B63" s="87">
         <f t="shared" si="0"/>
         <v>47757</v>
@@ -8372,7 +8374,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6">
       <c r="B64" s="87">
         <f t="shared" si="0"/>
         <v>47788</v>
@@ -8392,7 +8394,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6">
       <c r="B65" s="87">
         <f t="shared" si="0"/>
         <v>47818</v>
@@ -8432,19 +8434,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E074D57D-0BB2-4D51-BFA3-6687E8A03A91}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="C1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="27.21875" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.25" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.375" style="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:7">
       <c r="C1"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:7">
       <c r="C2" s="43" t="s">
         <v>212</v>
       </c>
@@ -8460,7 +8462,7 @@
         <v>10431799.635782748</v>
       </c>
     </row>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:7">
       <c r="C3" s="43" t="s">
         <v>218</v>
       </c>
@@ -8468,7 +8470,7 @@
         <v>490000</v>
       </c>
     </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:7">
       <c r="C4" s="45" t="s">
         <v>9</v>
       </c>
@@ -8477,7 +8479,7 @@
       </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:7">
       <c r="C5" s="43" t="s">
         <v>184</v>
       </c>
@@ -8486,7 +8488,7 @@
         <v>319488.81789137376</v>
       </c>
     </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:7">
       <c r="C6" s="43" t="s">
         <v>187</v>
       </c>
@@ -8494,7 +8496,7 @@
         <v>234220</v>
       </c>
     </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:7">
       <c r="C7" s="43" t="s">
         <v>229</v>
       </c>
@@ -8502,7 +8504,7 @@
         <v>14602</v>
       </c>
     </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:7">
       <c r="C8" s="43" t="s">
         <v>186</v>
       </c>
@@ -8510,7 +8512,7 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:7">
       <c r="C9" s="43" t="s">
         <v>185</v>
       </c>
@@ -8518,7 +8520,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:7">
       <c r="C10" s="45" t="s">
         <v>188</v>
       </c>
@@ -8527,7 +8529,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:7">
       <c r="C11" s="43" t="s">
         <v>194</v>
       </c>
@@ -8535,7 +8537,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:7">
       <c r="C12" s="43" t="s">
         <v>201</v>
       </c>
@@ -8543,7 +8545,7 @@
         <v>262000</v>
       </c>
     </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:7">
       <c r="C13" s="43" t="s">
         <v>207</v>
       </c>
@@ -8551,7 +8553,7 @@
         <v>204000</v>
       </c>
     </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:7">
       <c r="C14" s="43" t="s">
         <v>211</v>
       </c>
@@ -8559,7 +8561,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:7">
       <c r="C15" s="45" t="s">
         <v>213</v>
       </c>
@@ -8567,7 +8569,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:7">
       <c r="C16" s="43" t="s">
         <v>228</v>
       </c>
@@ -8575,7 +8577,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4">
       <c r="C17" s="43" t="s">
         <v>238</v>
       </c>
@@ -8592,23 +8594,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04D596E-F0F9-4062-A9AD-561789D52B52}">
   <dimension ref="B2:N29"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:12" ht="15" thickBot="1"/>
+    <row r="3" spans="2:12" ht="15.75" thickBot="1">
       <c r="B3" s="69" t="s">
         <v>193</v>
       </c>
@@ -8621,21 +8623,21 @@
       <c r="F3" s="26"/>
       <c r="L3" s="24"/>
     </row>
-    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="113" t="s">
+    <row r="5" spans="2:12" ht="15" thickBot="1"/>
+    <row r="6" spans="2:12" ht="15.75" thickBot="1">
+      <c r="C6" s="116" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="115"/>
-      <c r="H6" s="110" t="s">
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="H6" s="113" t="s">
         <v>205</v>
       </c>
-      <c r="I6" s="111"/>
-      <c r="J6" s="112"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="I6" s="114"/>
+      <c r="J6" s="115"/>
+    </row>
+    <row r="7" spans="2:12" ht="15">
       <c r="C7" s="63" t="s">
         <v>244</v>
       </c>
@@ -8658,7 +8660,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12">
       <c r="C8" s="53" t="s">
         <v>190</v>
       </c>
@@ -8678,7 +8680,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12">
       <c r="C9" s="53" t="s">
         <v>192</v>
       </c>
@@ -8699,7 +8701,7 @@
       </c>
       <c r="K9" s="100"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12">
       <c r="C10" s="53" t="s">
         <v>191</v>
       </c>
@@ -8712,7 +8714,7 @@
       <c r="I10" s="65"/>
       <c r="J10" s="66"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12">
       <c r="C11" s="53" t="s">
         <v>240</v>
       </c>
@@ -8725,7 +8727,7 @@
       <c r="I11" s="65"/>
       <c r="J11" s="66"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12">
       <c r="C12" s="53" t="s">
         <v>208</v>
       </c>
@@ -8738,7 +8740,7 @@
       <c r="I12" s="65"/>
       <c r="J12" s="66"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12">
       <c r="C13" s="53" t="s">
         <v>216</v>
       </c>
@@ -8751,7 +8753,7 @@
       <c r="I13" s="65"/>
       <c r="J13" s="66"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12">
       <c r="C14" s="53" t="s">
         <v>217</v>
       </c>
@@ -8764,7 +8766,7 @@
       <c r="I14" s="65"/>
       <c r="J14" s="66"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12">
       <c r="C15" s="53"/>
       <c r="D15" s="49"/>
       <c r="E15" s="49"/>
@@ -8773,7 +8775,7 @@
       <c r="I15" s="65"/>
       <c r="J15" s="66"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12">
       <c r="C16" s="53"/>
       <c r="D16" s="49"/>
       <c r="E16" s="49"/>
@@ -8782,7 +8784,7 @@
       <c r="I16" s="65"/>
       <c r="J16" s="66"/>
     </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:14">
       <c r="C17" s="53"/>
       <c r="D17" s="49"/>
       <c r="E17" s="49"/>
@@ -8791,7 +8793,7 @@
       <c r="I17" s="65"/>
       <c r="J17" s="66"/>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:14">
       <c r="C18" s="53"/>
       <c r="D18" s="49"/>
       <c r="E18" s="49"/>
@@ -8800,7 +8802,7 @@
       <c r="I18" s="65"/>
       <c r="J18" s="66"/>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:14">
       <c r="C19" s="53"/>
       <c r="D19" s="49"/>
       <c r="E19" s="49"/>
@@ -8809,7 +8811,7 @@
       <c r="I19" s="65"/>
       <c r="J19" s="66"/>
     </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:14">
       <c r="C20" s="53"/>
       <c r="D20" s="49"/>
       <c r="E20" s="49"/>
@@ -8818,7 +8820,7 @@
       <c r="I20" s="65"/>
       <c r="J20" s="66"/>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:14">
       <c r="C21" s="53"/>
       <c r="D21" s="49"/>
       <c r="E21" s="49"/>
@@ -8827,7 +8829,7 @@
       <c r="I21" s="65"/>
       <c r="J21" s="66"/>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:14">
       <c r="C22" s="53"/>
       <c r="D22" s="49"/>
       <c r="E22" s="49"/>
@@ -8836,7 +8838,7 @@
       <c r="I22" s="65"/>
       <c r="J22" s="66"/>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:14">
       <c r="C23" s="53"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
@@ -8845,7 +8847,7 @@
       <c r="I23" s="65"/>
       <c r="J23" s="66"/>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:14">
       <c r="C24" s="53"/>
       <c r="D24" s="49"/>
       <c r="E24" s="49"/>
@@ -8854,7 +8856,7 @@
       <c r="I24" s="65"/>
       <c r="J24" s="66"/>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:14">
       <c r="C25" s="41"/>
       <c r="D25" s="45"/>
       <c r="E25" s="49"/>
@@ -8863,7 +8865,7 @@
       <c r="I25" s="65"/>
       <c r="J25" s="66"/>
     </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:14">
       <c r="C26" s="41"/>
       <c r="D26" s="45"/>
       <c r="E26" s="49"/>
@@ -8872,7 +8874,7 @@
       <c r="I26" s="65"/>
       <c r="J26" s="66"/>
     </row>
-    <row r="27" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:14" ht="15" thickBot="1">
       <c r="C27" s="54"/>
       <c r="D27" s="50"/>
       <c r="E27" s="51"/>
@@ -8881,27 +8883,27 @@
       <c r="I27" s="65"/>
       <c r="J27" s="68"/>
     </row>
-    <row r="28" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:14" ht="15.75" thickBot="1">
       <c r="C28" s="60" t="s">
         <v>241</v>
       </c>
-      <c r="D28" s="116">
+      <c r="D28" s="119">
         <f>SUM(Table5[Incoming])-SUM(Table5[Outcoming])</f>
         <v>5419770</v>
       </c>
-      <c r="E28" s="117"/>
-      <c r="F28" s="118"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="121"/>
       <c r="H28" s="52" t="s">
         <v>241</v>
       </c>
-      <c r="I28" s="119">
+      <c r="I28" s="122">
         <f>SUM(Table6[Amount])</f>
         <v>47211609.670000002</v>
       </c>
-      <c r="J28" s="120"/>
+      <c r="J28" s="123"/>
       <c r="K28" s="40"/>
     </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:14">
       <c r="N29" s="61"/>
     </row>
   </sheetData>
@@ -8923,38 +8925,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45E7117-2FD0-43A7-B1BA-26C3C91B6B68}">
   <dimension ref="E5:AE33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="5" max="5" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.77734375" customWidth="1"/>
-    <col min="21" max="21" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" customWidth="1"/>
+    <col min="21" max="21" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.75" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="AB5" s="121"/>
-      <c r="AC5" s="121"/>
-      <c r="AD5" s="121"/>
-      <c r="AE5" s="121"/>
-    </row>
-    <row r="8" spans="5:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="5:31">
+      <c r="AB5" s="124"/>
+      <c r="AC5" s="124"/>
+      <c r="AD5" s="124"/>
+      <c r="AE5" s="124"/>
+    </row>
+    <row r="8" spans="5:31" ht="15">
       <c r="E8" s="72" t="s">
         <v>252</v>
       </c>
@@ -8965,7 +8967,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="5:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="5:31" ht="15">
       <c r="E9" s="72" t="s">
         <v>245</v>
       </c>
@@ -8976,7 +8978,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="5:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="5:31" ht="15">
       <c r="E10" s="72" t="s">
         <v>247</v>
       </c>
@@ -8987,7 +8989,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="11" spans="5:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="5:31" ht="15">
       <c r="E11" s="72" t="s">
         <v>248</v>
       </c>
@@ -8998,7 +9000,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="5:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="5:31" ht="15">
       <c r="E12" s="72" t="s">
         <v>250</v>
       </c>
@@ -9009,7 +9011,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="5:31" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="5:31" ht="29.25" thickBot="1">
       <c r="E13" s="72" t="s">
         <v>260</v>
       </c>
@@ -9020,7 +9022,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="14" spans="5:31" ht="36.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="5:31" ht="36.6" customHeight="1" thickTop="1" thickBot="1">
       <c r="E14" s="93" t="s">
         <v>264</v>
       </c>
@@ -9031,8 +9033,8 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="5:31" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="5:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="5:31" ht="15" thickTop="1"/>
+    <row r="16" spans="5:31" ht="15" thickBot="1">
       <c r="E16" s="40" t="s">
         <v>237</v>
       </c>
@@ -9046,7 +9048,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
       <c r="E17" s="90" t="s">
         <v>261</v>
       </c>
@@ -9061,7 +9063,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="18" spans="5:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:15" ht="15.75" thickTop="1">
       <c r="E18" s="94" t="s">
         <v>20</v>
       </c>
@@ -9075,7 +9077,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="19" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:15" ht="15">
       <c r="E19" s="40" t="s">
         <v>233</v>
       </c>
@@ -9087,7 +9089,7 @@
       </c>
       <c r="H19" s="99"/>
     </row>
-    <row r="20" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:15" ht="15">
       <c r="E20" s="40" t="s">
         <v>232</v>
       </c>
@@ -9102,7 +9104,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:15" ht="15">
       <c r="E21" s="94" t="s">
         <v>234</v>
       </c>
@@ -9118,7 +9120,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="23" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:15">
       <c r="E23" s="40" t="s">
         <v>272</v>
       </c>
@@ -9153,7 +9155,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="24" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:15">
       <c r="E24" s="87">
         <v>46219</v>
       </c>
@@ -9182,13 +9184,13 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N24" s="123" t="e">
+      <c r="N24" s="110" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
       <c r="O24" s="40"/>
     </row>
-    <row r="25" spans="5:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:15">
       <c r="E25" s="87">
         <v>46225</v>
       </c>
@@ -9217,13 +9219,13 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N25" s="123" t="e">
+      <c r="N25" s="110" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
       <c r="O25" s="40"/>
     </row>
-    <row r="26" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="5:15" ht="15" thickBot="1">
       <c r="E26" s="87" t="s">
         <v>210</v>
       </c>
@@ -9254,13 +9256,13 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>1983</v>
       </c>
-      <c r="N26" s="123">
+      <c r="N26" s="110">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>0.6125474932814382</v>
       </c>
       <c r="O26" s="40"/>
     </row>
-    <row r="27" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
       <c r="E27" s="90" t="s">
         <v>210</v>
       </c>
@@ -9276,7 +9278,7 @@
       <c r="I27" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="J27" s="122" t="s">
+      <c r="J27" s="109" t="s">
         <v>210</v>
       </c>
       <c r="K27" s="90" t="s">
@@ -9289,13 +9291,13 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N27" s="124" t="e">
+      <c r="N27" s="111" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
       <c r="O27" s="90"/>
     </row>
-    <row r="28" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
       <c r="E28" s="90" t="s">
         <v>210</v>
       </c>
@@ -9311,7 +9313,7 @@
       <c r="I28" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="J28" s="122" t="s">
+      <c r="J28" s="109" t="s">
         <v>210</v>
       </c>
       <c r="K28" s="90" t="s">
@@ -9324,13 +9326,13 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N28" s="124" t="e">
+      <c r="N28" s="111" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
       <c r="O28" s="90"/>
     </row>
-    <row r="29" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
       <c r="E29" s="90" t="s">
         <v>210</v>
       </c>
@@ -9346,7 +9348,7 @@
       <c r="I29" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="J29" s="122" t="s">
+      <c r="J29" s="109" t="s">
         <v>210</v>
       </c>
       <c r="K29" s="90" t="s">
@@ -9359,13 +9361,13 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N29" s="124" t="e">
+      <c r="N29" s="111" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
       <c r="O29" s="90"/>
     </row>
-    <row r="30" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
       <c r="E30" s="90" t="s">
         <v>210</v>
       </c>
@@ -9381,7 +9383,7 @@
       <c r="I30" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="J30" s="122" t="s">
+      <c r="J30" s="109" t="s">
         <v>210</v>
       </c>
       <c r="K30" s="90" t="s">
@@ -9394,13 +9396,13 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N30" s="124" t="e">
+      <c r="N30" s="111" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
       <c r="O30" s="90"/>
     </row>
-    <row r="31" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
       <c r="E31" s="90" t="s">
         <v>210</v>
       </c>
@@ -9416,7 +9418,7 @@
       <c r="I31" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="J31" s="122" t="s">
+      <c r="J31" s="109" t="s">
         <v>210</v>
       </c>
       <c r="K31" s="90" t="s">
@@ -9429,13 +9431,13 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N31" s="124" t="e">
+      <c r="N31" s="111" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
       <c r="O31" s="90"/>
     </row>
-    <row r="32" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
       <c r="E32" s="90" t="s">
         <v>210</v>
       </c>
@@ -9451,7 +9453,7 @@
       <c r="I32" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="J32" s="122" t="s">
+      <c r="J32" s="109" t="s">
         <v>210</v>
       </c>
       <c r="K32" s="90" t="s">
@@ -9464,20 +9466,20 @@
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N32" s="124" t="e">
+      <c r="N32" s="111" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
       <c r="O32" s="90"/>
     </row>
-    <row r="33" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" thickTop="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="AB5:AC5"/>
     <mergeCell ref="AD5:AE5"/>
   </mergeCells>
   <conditionalFormatting sqref="F17:F21">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>SUM($F$17:$F$21)&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9495,13 +9497,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C45E6B-F2EC-4DF6-9239-EC7E9397E406}">
   <dimension ref="A1:B167"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -9509,7 +9511,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -9517,7 +9519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -9525,7 +9527,7 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -9533,7 +9535,7 @@
         <v>2.0409E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -9541,7 +9543,7 @@
         <v>2.495E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -9549,7 +9551,7 @@
         <v>0.11405700000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -9557,7 +9559,7 @@
         <v>5.6099999999999998E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -9565,7 +9567,7 @@
         <v>0.28789500000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -9573,7 +9575,7 @@
         <v>0.47286800000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -9581,7 +9583,7 @@
         <v>4.37E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -9589,7 +9591,7 @@
         <v>5.6099999999999998E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -9597,7 +9599,7 @@
         <v>5.3600000000000002E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -9605,7 +9607,7 @@
         <v>5.2800000000000004E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -9613,7 +9615,7 @@
         <v>6.2699999999999995E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -9621,7 +9623,7 @@
         <v>3.8725999999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -9629,7 +9631,7 @@
         <v>5.2800000000000004E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -9637,7 +9639,7 @@
         <v>1.18E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -9645,7 +9647,7 @@
         <v>0.94235199999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -9653,7 +9655,7 @@
         <v>3.1300000000000002E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -9661,7 +9663,7 @@
         <v>3.9899999999999999E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -9669,7 +9671,7 @@
         <v>3.699E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -9677,7 +9679,7 @@
         <v>1.621E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -9685,7 +9687,7 @@
         <v>3.1300000000000002E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -9693,7 +9695,7 @@
         <v>2.9824E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -9701,7 +9703,7 @@
         <v>4.2009999999999999E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -9709,7 +9711,7 @@
         <v>9.6100000000000005E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -9717,7 +9719,7 @@
         <v>6.2699999999999995E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -9725,7 +9727,7 @@
         <v>4.35E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -9733,7 +9735,7 @@
         <v>0.71758900000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -9741,7 +9743,7 @@
         <v>2.5300000000000002E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>223</v>
       </c>
@@ -9749,7 +9751,7 @@
         <v>6.9999999999999999E-6</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -9757,7 +9759,7 @@
         <v>0.29166199999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>224</v>
       </c>
@@ -9765,7 +9767,7 @@
         <v>2.104E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -9773,7 +9775,7 @@
         <v>2.1099999999999999E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -9781,7 +9783,7 @@
         <v>0.14158200000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -9789,7 +9791,7 @@
         <v>7.5180000000000004E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -9797,7 +9799,7 @@
         <v>2.9779E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -9805,7 +9807,7 @@
         <v>6.5160000000000001E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -9813,7 +9815,7 @@
         <v>5.5674000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -9821,7 +9823,7 @@
         <v>2.019E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -9829,7 +9831,7 @@
         <v>1.8456E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -9837,7 +9839,7 @@
         <v>4.1771999999999997E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -9845,7 +9847,7 @@
         <v>1.5897999999999999E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -9853,7 +9855,7 @@
         <v>4.6990000000000001E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>62</v>
       </c>
@@ -9861,7 +9863,7 @@
         <v>5.0786999999999999E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>63</v>
       </c>
@@ -9869,7 +9871,7 @@
         <v>2.7E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>64</v>
       </c>
@@ -9877,7 +9879,7 @@
         <v>6.8900000000000005E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -9885,7 +9887,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -9893,7 +9895,7 @@
         <v>2.019E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>67</v>
       </c>
@@ -9901,7 +9903,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>68</v>
       </c>
@@ -9909,7 +9911,7 @@
         <v>8.1599999999999999E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -9917,7 +9919,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>70</v>
       </c>
@@ -9925,7 +9927,7 @@
         <v>3.5209999999999998E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>71</v>
       </c>
@@ -9933,7 +9935,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -9941,7 +9943,7 @@
         <v>2.3699000000000001E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>73</v>
       </c>
@@ -9949,7 +9951,7 @@
         <v>2.7476530000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -9957,7 +9959,7 @@
         <v>2.3990000000000001E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -9965,7 +9967,7 @@
         <v>6.5502000000000005E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>76</v>
       </c>
@@ -9973,7 +9975,7 @@
         <v>2.454E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>77</v>
       </c>
@@ -9981,7 +9983,7 @@
         <v>8.4259999999999995E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>78</v>
       </c>
@@ -9989,7 +9991,7 @@
         <v>2.0349999999999999E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>79</v>
       </c>
@@ -9997,7 +9999,7 @@
         <v>4.0933999999999998E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -10005,7 +10007,7 @@
         <v>9.8497000000000001E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>81</v>
       </c>
@@ -10013,7 +10015,7 @@
         <v>5.5844550000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>82</v>
       </c>
@@ -10021,7 +10023,7 @@
         <v>9.3599999999999998E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -10029,7 +10031,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>84</v>
       </c>
@@ -10037,7 +10039,7 @@
         <v>2.9824E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>85</v>
       </c>
@@ -10045,7 +10047,7 @@
         <v>0.41089199999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -10053,7 +10055,7 @@
         <v>445.14925399999998</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>87</v>
       </c>
@@ -10061,7 +10063,7 @@
         <v>3.8009000000000001E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>88</v>
       </c>
@@ -10069,7 +10071,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>89</v>
       </c>
@@ -10077,7 +10079,7 @@
         <v>4.9805000000000002E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -10085,7 +10087,7 @@
         <v>2.22E-4</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -10093,7 +10095,7 @@
         <v>5.0019000000000001E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -10101,7 +10103,7 @@
         <v>4.0545999999999999E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>93</v>
       </c>
@@ -10109,7 +10111,7 @@
         <v>2.7387999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -10117,7 +10119,7 @@
         <v>1.2652890000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>95</v>
       </c>
@@ -10125,7 +10127,7 @@
         <v>4.37E-4</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>96</v>
       </c>
@@ -10133,7 +10135,7 @@
         <v>0.13286400000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>97</v>
       </c>
@@ -10141,7 +10143,7 @@
         <v>0.428672</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>98</v>
       </c>
@@ -10149,7 +10151,7 @@
         <v>9.7E-5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>99</v>
       </c>
@@ -10157,7 +10159,7 @@
         <v>2.61E-4</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>100</v>
       </c>
@@ -10165,7 +10167,7 @@
         <v>0.145283</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>101</v>
       </c>
@@ -10173,7 +10175,7 @@
         <v>6.9917009999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>102</v>
       </c>
@@ -10181,7 +10183,7 @@
         <v>28.037489999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>103</v>
       </c>
@@ -10189,7 +10191,7 @@
         <v>0.102843</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2">
       <c r="A87" t="s">
         <v>104</v>
       </c>
@@ -10197,7 +10199,7 @@
         <v>5.6659000000000001E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
         <v>105</v>
       </c>
@@ -10205,7 +10207,7 @@
         <v>5.0530000000000002E-3</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2">
       <c r="A89" t="s">
         <v>106</v>
       </c>
@@ -10213,7 +10215,7 @@
         <v>1.9840000000000001E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2">
       <c r="A90" t="s">
         <v>107</v>
       </c>
@@ -10221,7 +10223,7 @@
         <v>2.9129999999999998E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2">
       <c r="A91" t="s">
         <v>108</v>
       </c>
@@ -10229,7 +10231,7 @@
         <v>5.4190000000000002E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
         <v>109</v>
       </c>
@@ -10237,7 +10239,7 @@
         <v>1.354023</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2">
       <c r="A93" t="s">
         <v>110</v>
       </c>
@@ -10245,7 +10247,7 @@
         <v>1.7075E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2">
       <c r="A94" t="s">
         <v>111</v>
       </c>
@@ -10253,7 +10255,7 @@
         <v>0.65837199999999996</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2">
       <c r="A95" t="s">
         <v>112</v>
       </c>
@@ -10261,7 +10263,7 @@
         <v>1.1309959999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2">
       <c r="A96" t="s">
         <v>113</v>
       </c>
@@ -10269,7 +10271,7 @@
         <v>2.5279999999999999E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2">
       <c r="A97" t="s">
         <v>114</v>
       </c>
@@ -10277,7 +10279,7 @@
         <v>1.2573000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2">
       <c r="A98" t="s">
         <v>115</v>
       </c>
@@ -10285,7 +10287,7 @@
         <v>1.4734000000000001E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2">
       <c r="A99" t="s">
         <v>116</v>
       </c>
@@ -10293,7 +10295,7 @@
         <v>4.8459999999999996E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2">
       <c r="A100" t="s">
         <v>117</v>
       </c>
@@ -10301,7 +10303,7 @@
         <v>0.54324700000000004</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2">
       <c r="A101" t="s">
         <v>118</v>
       </c>
@@ -10309,7 +10311,7 @@
         <v>5.3280000000000003E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2">
       <c r="A102" t="s">
         <v>119</v>
       </c>
@@ -10317,7 +10319,7 @@
         <v>1.2600000000000001E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2">
       <c r="A103" t="s">
         <v>120</v>
       </c>
@@ -10325,7 +10327,7 @@
         <v>1.9913E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2">
       <c r="A104" t="s">
         <v>121</v>
       </c>
@@ -10333,7 +10335,7 @@
         <v>5.0530000000000002E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2">
       <c r="A105" t="s">
         <v>122</v>
       </c>
@@ -10341,7 +10343,7 @@
         <v>0.42027999999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2">
       <c r="A106" t="s">
         <v>123</v>
       </c>
@@ -10349,7 +10351,7 @@
         <v>1.157E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2">
       <c r="A107" t="s">
         <v>124</v>
       </c>
@@ -10357,7 +10359,7 @@
         <v>2.9269999999999999E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2">
       <c r="A108" t="s">
         <v>125</v>
       </c>
@@ -10365,7 +10367,7 @@
         <v>4.7718000000000003E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2">
       <c r="A109" t="s">
         <v>126</v>
       </c>
@@ -10373,7 +10375,7 @@
         <v>5.2899999999999996E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2">
       <c r="A110" t="s">
         <v>127</v>
       </c>
@@ -10381,7 +10383,7 @@
         <v>1.2E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2">
       <c r="A111" t="s">
         <v>128</v>
       </c>
@@ -10389,7 +10391,7 @@
         <v>3.1300000000000002E-4</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2">
       <c r="A112" t="s">
         <v>129</v>
       </c>
@@ -10397,7 +10399,7 @@
         <v>1.0560000000000001E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2">
       <c r="A113" t="s">
         <v>130</v>
       </c>
@@ -10405,7 +10407,7 @@
         <v>1.3979999999999999E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2">
       <c r="A114" t="s">
         <v>131</v>
       </c>
@@ -10413,7 +10415,7 @@
         <v>1.9529999999999999E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2">
       <c r="A115" t="s">
         <v>132</v>
       </c>
@@ -10421,7 +10423,7 @@
         <v>8.7101999999999999E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2">
       <c r="A116" t="s">
         <v>133</v>
       </c>
@@ -10429,7 +10431,7 @@
         <v>1.1709999999999999E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2">
       <c r="A117" t="s">
         <v>134</v>
       </c>
@@ -10437,7 +10439,7 @@
         <v>1.862026</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2">
       <c r="A118" t="s">
         <v>135</v>
       </c>
@@ -10445,7 +10447,7 @@
         <v>1.14E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2">
       <c r="A119" t="s">
         <v>136</v>
       </c>
@@ -10453,7 +10455,7 @@
         <v>1.42E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2">
       <c r="A120" t="s">
         <v>137</v>
       </c>
@@ -10461,7 +10463,7 @@
         <v>3.1708E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2">
       <c r="A121" t="s">
         <v>138</v>
       </c>
@@ -10469,7 +10471,7 @@
         <v>2.7088999999999998E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2">
       <c r="A122" t="s">
         <v>139</v>
       </c>
@@ -10477,7 +10479,7 @@
         <v>0.462258</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2">
       <c r="A123" t="s">
         <v>140</v>
       </c>
@@ -10485,7 +10487,7 @@
         <v>1.175E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2">
       <c r="A124" t="s">
         <v>141</v>
       </c>
@@ -10493,7 +10495,7 @@
         <v>2.5110000000000002E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2">
       <c r="A125" t="s">
         <v>142</v>
       </c>
@@ -10501,7 +10503,7 @@
         <v>4.398E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2">
       <c r="A126" t="s">
         <v>143</v>
       </c>
@@ -10509,7 +10511,7 @@
         <v>0.14224300000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2">
       <c r="A127" t="s">
         <v>144</v>
       </c>
@@ -10517,7 +10519,7 @@
         <v>3.0019999999999999E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2">
       <c r="A128" t="s">
         <v>145</v>
       </c>
@@ -10525,7 +10527,7 @@
         <v>3.9899999999999999E-4</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2">
       <c r="A129" t="s">
         <v>146</v>
       </c>
@@ -10533,7 +10535,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2">
       <c r="A130" t="s">
         <v>147</v>
       </c>
@@ -10541,7 +10543,7 @@
         <v>7.9640000000000006E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2">
       <c r="A131" t="s">
         <v>148</v>
       </c>
@@ -10549,7 +10551,7 @@
         <v>7.9639519999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2">
       <c r="A132" t="s">
         <v>149</v>
       </c>
@@ -10557,7 +10559,7 @@
         <v>0.17905699999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2">
       <c r="A133" t="s">
         <v>150</v>
       </c>
@@ -10565,7 +10567,7 @@
         <v>1.1838E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2">
       <c r="A134" t="s">
         <v>151</v>
       </c>
@@ -10573,7 +10575,7 @@
         <v>1.8075760000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2">
       <c r="A135" t="s">
         <v>152</v>
       </c>
@@ -10581,7 +10583,7 @@
         <v>6.6169999999999996E-3</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2">
       <c r="A136" t="s">
         <v>153</v>
       </c>
@@ -10589,7 +10591,7 @@
         <v>3.8131999999999999E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2">
       <c r="A137" t="s">
         <v>154</v>
       </c>
@@ -10597,7 +10599,7 @@
         <v>5.0530000000000002E-3</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2">
       <c r="A138" t="s">
         <v>155</v>
       </c>
@@ -10605,7 +10607,7 @@
         <v>1.0385999999999999E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2">
       <c r="A139" t="s">
         <v>156</v>
       </c>
@@ -10613,7 +10615,7 @@
         <v>2.9870000000000001E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2">
       <c r="A140" t="s">
         <v>157</v>
       </c>
@@ -10621,7 +10623,7 @@
         <v>1.1329999999999999E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2">
       <c r="A141" t="s">
         <v>158</v>
       </c>
@@ -10629,7 +10631,7 @@
         <v>9.1100000000000003E-4</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -10637,7 +10639,7 @@
         <v>7.5500000000000003E-4</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2">
       <c r="A143" t="s">
         <v>160</v>
       </c>
@@ -10645,7 +10647,7 @@
         <v>1.5110999999999999E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2">
       <c r="A144" t="s">
         <v>161</v>
       </c>
@@ -10653,7 +10655,7 @@
         <v>2.1389999999999998E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2">
       <c r="A145" t="s">
         <v>162</v>
       </c>
@@ -10661,7 +10663,7 @@
         <v>4.37E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -10669,7 +10671,7 @@
         <v>9.9290000000000003E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2">
       <c r="A147" t="s">
         <v>164</v>
       </c>
@@ -10677,7 +10679,7 @@
         <v>0.82893899999999998</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2">
       <c r="A148" t="s">
         <v>165</v>
       </c>
@@ -10685,7 +10687,7 @@
         <v>1.3958999999999999E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2">
       <c r="A149" t="s">
         <v>166</v>
       </c>
@@ -10693,7 +10695,7 @@
         <v>1.1724760000000001</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2">
       <c r="A150" t="s">
         <v>20</v>
       </c>
@@ -10701,7 +10703,7 @@
         <v>3.1300000000000002E-4</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2">
       <c r="A151" t="s">
         <v>167</v>
       </c>
@@ -10709,7 +10711,7 @@
         <v>1.2659999999999999E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2">
       <c r="A152" t="s">
         <v>168</v>
       </c>
@@ -10717,7 +10719,7 @@
         <v>3.6983440000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2">
       <c r="A153" t="s">
         <v>169</v>
       </c>
@@ -10725,7 +10727,7 @@
         <v>0.25009500000000001</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2">
       <c r="A154" t="s">
         <v>170</v>
       </c>
@@ -10733,7 +10735,7 @@
         <v>8.1179109999999994</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2">
       <c r="A155" t="s">
         <v>171</v>
       </c>
@@ -10741,7 +10743,7 @@
         <v>3.7132999999999999E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2">
       <c r="A156" t="s">
         <v>172</v>
       </c>
@@ -10749,7 +10751,7 @@
         <v>8.4699999999999999E-4</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2">
       <c r="A157" t="s">
         <v>173</v>
       </c>
@@ -10757,7 +10759,7 @@
         <v>0.177152</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2">
       <c r="A158" t="s">
         <v>174</v>
       </c>
@@ -10765,7 +10767,7 @@
         <v>8.4599999999999996E-4</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2">
       <c r="A159" t="s">
         <v>175</v>
       </c>
@@ -10773,7 +10775,7 @@
         <v>5.6099999999999998E-4</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2">
       <c r="A160" t="s">
         <v>176</v>
       </c>
@@ -10781,7 +10783,7 @@
         <v>2.2900000000000001E-4</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2">
       <c r="A161" t="s">
         <v>177</v>
       </c>
@@ -10789,7 +10791,7 @@
         <v>0.177152</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2">
       <c r="A162" t="s">
         <v>178</v>
       </c>
@@ -10797,7 +10799,7 @@
         <v>3.2228E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2">
       <c r="A163" t="s">
         <v>179</v>
       </c>
@@ -10805,7 +10807,7 @@
         <v>7.4154999999999999E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2">
       <c r="A164" t="s">
         <v>180</v>
       </c>
@@ -10813,7 +10815,7 @@
         <v>5.0530000000000002E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2">
       <c r="A165" t="s">
         <v>181</v>
       </c>
@@ -10821,7 +10823,7 @@
         <v>5.9589999999999999E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2">
       <c r="A166" t="s">
         <v>225</v>
       </c>
@@ -10829,7 +10831,7 @@
         <v>8.3540000000000003E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2">
       <c r="A167" t="s">
         <v>182</v>
       </c>

--- a/Management/Finantial Planning.xlsx
+++ b/Management/Finantial Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D432296-E4FE-41EB-A404-B51F2DD37755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3468EE1-EAF2-41EE-A4EB-47E406BF02A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F8FCC151-5DC7-4472-A863-0C0A531A258D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{F8FCC151-5DC7-4472-A863-0C0A531A258D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="305">
   <si>
     <t>Wellbeing Lifestyle</t>
   </si>
@@ -747,12 +747,6 @@
     <t>Pedido Temu</t>
   </si>
   <si>
-    <t>Rappi: ? - Optimum Nutrition 5g 300g - 4? months</t>
-  </si>
-  <si>
-    <t>Rappi: ? - Bipro 3lb - 3.75 months</t>
-  </si>
-  <si>
     <t>CDTs</t>
   </si>
   <si>
@@ -964,13 +958,25 @@
   </si>
   <si>
     <t>Laptop Drive</t>
+  </si>
+  <si>
+    <t>Look 'My Stats'&gt;Supplements</t>
+  </si>
+  <si>
+    <t>Chaqueta Velez</t>
+  </si>
+  <si>
+    <t>Viaje Cali</t>
+  </si>
+  <si>
+    <t>Monthly Remaining</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="12">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_([$COP]\ * #,##0.00_);_([$COP]\ * \(#,##0.00\);_([$COP]\ * &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_([$COP]\ * #,##0_);_([$COP]\ * \(#,##0\);_([$COP]\ * &quot;-&quot;??_);_(@_)"/>
@@ -978,7 +984,6 @@
     <numFmt numFmtId="168" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
     <numFmt numFmtId="172" formatCode="#,##0.00\ [$COP]"/>
     <numFmt numFmtId="173" formatCode="\+\ #.##0\ \C\O\P;\-\ #.##0\ \C\O\P;0\ \C\O\P"/>
     <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
@@ -1502,7 +1507,7 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1553,7 +1558,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1800,6 +1804,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Check Cell" xfId="5" builtinId="23"/>
@@ -1810,6 +1821,17 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="80">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1939,13 +1961,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2483,9 +2498,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -5999,43 +6011,43 @@
     </tableColumn>
     <tableColumn id="5" xr3:uid="{10738E51-758B-45FB-9DD0-02C14BC2D40D}" name="After Benefits" dataDxfId="72"/>
     <tableColumn id="6" xr3:uid="{07D186C7-DB64-4AC7-BA70-8DC5B9E3A51B}" name="Pay Date (day)" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{8B8904EF-9CF0-47D9-8BCB-78EF6DD7F607}" name="Additional Information" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{8B8904EF-9CF0-47D9-8BCB-78EF6DD7F607}" name="Additional Information" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}" name="Table7" displayName="Table7" ref="E8:G14" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}" name="Table7" displayName="Table7" ref="E8:G14" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="E8:G14" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{05264107-3C50-4DC4-BA66-3C598C57D362}" name="Condition" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{4F494527-B966-4283-AC8D-DDFC53922A3A}" name="Action" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{A8687214-DFD3-4202-A740-25119BF98217}" name="% Adjusted" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{05264107-3C50-4DC4-BA66-3C598C57D362}" name="Condition" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{4F494527-B966-4283-AC8D-DDFC53922A3A}" name="Action" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{A8687214-DFD3-4202-A740-25119BF98217}" name="% Adjusted" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}" name="Table10" displayName="Table10" ref="E23:O32" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}" name="Table10" displayName="Table10" ref="E23:O32" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="E23:O32" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{EF8D02AC-323D-45AB-AE15-91832BDC7B4E}" name="Date Bought" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{712A0457-F103-4A5F-89A3-F38940B6301F}" name="Date Sold" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{8B72E438-7296-4BE9-B114-652C18C0973F}" name="Asset" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{C9EB17C7-CF17-4BB1-8390-4A0AA329B909}" name="Units" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{38A379BB-56A1-4C91-8A79-E09D76997328}" name="Price Buy" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{70D6BA55-3422-446B-A79B-9ED0B67E93BD}" name="Price Sell" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{D264BB00-77B0-482C-925B-C8BD072B81A0}" name="Total Invested (COP)" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{9369D078-2888-4CE1-919F-E9A0C05D615C}" name="Total Value" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{313DF1E8-730D-4C1D-BB28-A01F2D131415}" name="Gain/Loss (COP)" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{EF8D02AC-323D-45AB-AE15-91832BDC7B4E}" name="Date Bought" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{712A0457-F103-4A5F-89A3-F38940B6301F}" name="Date Sold" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{8B72E438-7296-4BE9-B114-652C18C0973F}" name="Asset" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{C9EB17C7-CF17-4BB1-8390-4A0AA329B909}" name="Units" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{38A379BB-56A1-4C91-8A79-E09D76997328}" name="Price Buy" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{70D6BA55-3422-446B-A79B-9ED0B67E93BD}" name="Price Sell" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{D264BB00-77B0-482C-925B-C8BD072B81A0}" name="Total Invested (COP)" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{9369D078-2888-4CE1-919F-E9A0C05D615C}" name="Total Value" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{313DF1E8-730D-4C1D-BB28-A01F2D131415}" name="Gain/Loss (COP)" dataDxfId="4">
       <calculatedColumnFormula>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{CD1E921A-1374-4429-89D9-1676BA8642FB}" name="% Return" dataDxfId="1" dataCellStyle="Percent">
+    <tableColumn id="10" xr3:uid="{CD1E921A-1374-4429-89D9-1676BA8642FB}" name="% Return" dataDxfId="3" dataCellStyle="Percent">
       <calculatedColumnFormula>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{36B25BAF-3792-45C1-AE34-3EDA3274070F}" name="Notes" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{36B25BAF-3792-45C1-AE34-3EDA3274070F}" name="Notes" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6053,17 +6065,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{66334954-402F-42CF-93F5-A72360F2D070}" name="Tabla4" displayName="Tabla4" ref="C32:F34" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68" tableBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{66334954-402F-42CF-93F5-A72360F2D070}" name="Tabla4" displayName="Tabla4" ref="C32:F34" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
   <autoFilter ref="C32:F34" xr:uid="{66334954-402F-42CF-93F5-A72360F2D070}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7008F60E-B49B-4429-A785-DABF540532D2}" name=" " dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{7AA8370E-90CC-4DED-878E-C49D41DF4160}" name="Goal" dataDxfId="65">
+    <tableColumn id="1" xr3:uid="{7008F60E-B49B-4429-A785-DABF540532D2}" name=" " dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{7AA8370E-90CC-4DED-878E-C49D41DF4160}" name="Goal" dataDxfId="66">
       <calculatedColumnFormula>24000*D27</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F5EB769A-6764-44FD-A678-979868FCC64D}" name="Time till Germany (from 05.08.2025) [months]" dataDxfId="64">
+    <tableColumn id="3" xr3:uid="{F5EB769A-6764-44FD-A678-979868FCC64D}" name="Time till Germany (from 05.08.2025) [months]" dataDxfId="65">
       <calculatedColumnFormula>_xlfn.CEILING.MATH((D33-$D$23-$D$5+'Another Expenses'!G2)/$D$21)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{458996D1-0FCE-433A-A2D6-31A1409ED603}" name="Expected Date" dataDxfId="63">
+    <tableColumn id="4" xr3:uid="{458996D1-0FCE-433A-A2D6-31A1409ED603}" name="Expected Date" dataDxfId="64">
       <calculatedColumnFormula>EDATE(DATE(YEAR($B$2), MONTH($B$2), $E$8),E33)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6072,92 +6084,92 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EE785617-0173-4EE0-B271-24F483A6FC5D}" name="Table8" displayName="Table8" ref="C7:E14" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" tableBorderDxfId="59" totalsRowBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EE785617-0173-4EE0-B271-24F483A6FC5D}" name="Table8" displayName="Table8" ref="C7:E14" totalsRowShown="0" headerRowDxfId="63" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60" totalsRowBorderDxfId="59">
   <autoFilter ref="C7:E14" xr:uid="{EE785617-0173-4EE0-B271-24F483A6FC5D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B8D1B94D-65F4-44AF-BB8A-B3944537254D}" name="Income" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{70B9C461-0699-4DD9-88DF-A4BC104B1E84}" name="Unit Cost" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{0F428774-E799-4A75-AF01-1FEB7C7BB60B}" name="Pay Date" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{B8D1B94D-65F4-44AF-BB8A-B3944537254D}" name="Income" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{70B9C461-0699-4DD9-88DF-A4BC104B1E84}" name="Unit Cost" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{0F428774-E799-4A75-AF01-1FEB7C7BB60B}" name="Pay Date" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{234B9209-31CF-4CB4-B91D-DB56E5076B02}" name="Table9" displayName="Table9" ref="B5:F65" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{234B9209-31CF-4CB4-B91D-DB56E5076B02}" name="Table9" displayName="Table9" ref="B5:F65" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="B5:F65" xr:uid="{234B9209-31CF-4CB4-B91D-DB56E5076B02}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{71E1B1C3-7B4F-4332-B720-63A44972040A}" name="Date" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{92837B89-3057-4978-9098-533DE8C88637}" name="General Balance" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{A4EBB52D-F610-40EB-8029-0CC1E5ACB00B}" name="Account Balance" dataDxfId="50">
+    <tableColumn id="1" xr3:uid="{71E1B1C3-7B4F-4332-B720-63A44972040A}" name="Date" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{92837B89-3057-4978-9098-533DE8C88637}" name="General Balance" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{A4EBB52D-F610-40EB-8029-0CC1E5ACB00B}" name="Account Balance" dataDxfId="51">
       <calculatedColumnFormula>RAND()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{198D9105-C07E-44D2-8F61-8F9CABBAD850}" name="Gain/Loss" dataDxfId="49">
+    <tableColumn id="3" xr3:uid="{198D9105-C07E-44D2-8F61-8F9CABBAD850}" name="Gain/Loss" dataDxfId="50">
       <calculatedColumnFormula>Table9[[#This Row],[Account Balance]]-D5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{4C793EB9-7B7D-4BF8-8BFC-64EEC368D854}" name="Difference from Expected Net" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{4C793EB9-7B7D-4BF8-8BFC-64EEC368D854}" name="Difference from Expected Net" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{1E999F4D-13BA-4961-9CC8-4DF65A7B1CEA}" name="Table11" displayName="Table11" ref="H6:I12" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{1E999F4D-13BA-4961-9CC8-4DF65A7B1CEA}" name="Table11" displayName="Table11" ref="H6:I12" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <autoFilter ref="H6:I12" xr:uid="{1E999F4D-13BA-4961-9CC8-4DF65A7B1CEA}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5E82BFD3-6D74-43F6-913D-96694AEF7A3E}" name="Date" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{710C1C2F-6F23-4153-86B6-2D191197A156}" name="General Balance" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{5E82BFD3-6D74-43F6-913D-96694AEF7A3E}" name="Date" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{710C1C2F-6F23-4153-86B6-2D191197A156}" name="General Balance" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3DBCF91F-3FBC-4548-AAE4-34CB784C3CED}" name="Table1113" displayName="Table1113" ref="H15:I21" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3DBCF91F-3FBC-4548-AAE4-34CB784C3CED}" name="Table1113" displayName="Table1113" ref="H15:I21" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
   <autoFilter ref="H15:I21" xr:uid="{3DBCF91F-3FBC-4548-AAE4-34CB784C3CED}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E16B0B05-832D-453D-BB01-1648C2BB6952}" name="Date" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{1165A24D-75E5-4E1D-A756-DA4346B52F4F}" name="Difference from Expected Net" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{E16B0B05-832D-453D-BB01-1648C2BB6952}" name="Date" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{1165A24D-75E5-4E1D-A756-DA4346B52F4F}" name="Difference from Expected Net" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BA8F843C-C6A6-4B02-9256-7DFE12B32092}" name="Table5" displayName="Table5" ref="C7:F27" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37" totalsRowBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BA8F843C-C6A6-4B02-9256-7DFE12B32092}" name="Table5" displayName="Table5" ref="C7:F27" totalsRowShown="0" headerRowDxfId="40" headerRowBorderDxfId="39" tableBorderDxfId="38" totalsRowBorderDxfId="37">
   <autoFilter ref="C7:F27" xr:uid="{BA8F843C-C6A6-4B02-9256-7DFE12B32092}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A7222D0C-F15D-4B37-8493-05007AD6DC97}" name="Description" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{9873BCE0-3AFD-4035-A4F4-DDE3995CE8FF}" name="Incoming" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{73BD4001-1956-4334-A204-BB3321930FA2}" name="Outcoming" dataDxfId="33" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{6189F130-2A64-446B-8A16-FBD00F7771AC}" name="Notes" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{A7222D0C-F15D-4B37-8493-05007AD6DC97}" name="Description" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{9873BCE0-3AFD-4035-A4F4-DDE3995CE8FF}" name="Incoming" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{73BD4001-1956-4334-A204-BB3321930FA2}" name="Outcoming" dataDxfId="34" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{6189F130-2A64-446B-8A16-FBD00F7771AC}" name="Notes" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F7CD279B-A932-4C0F-8D8F-D149C918CAA1}" name="Table6" displayName="Table6" ref="H7:J27" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28" totalsRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F7CD279B-A932-4C0F-8D8F-D149C918CAA1}" name="Table6" displayName="Table6" ref="H7:J27" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31" tableBorderDxfId="29" totalsRowBorderDxfId="28">
   <autoFilter ref="H7:J27" xr:uid="{F7CD279B-A932-4C0F-8D8F-D149C918CAA1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{516245D1-012B-4614-97CB-8E191CA93F41}" name="Name" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{41E5D36C-6A21-4BF1-972B-BA27C450EDE2}" name="Amount" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{8ADFD3E1-24FE-45CE-8A72-696379253170}" name="Notes" dataDxfId="24" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{516245D1-012B-4614-97CB-8E191CA93F41}" name="Name" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{41E5D36C-6A21-4BF1-972B-BA27C450EDE2}" name="Amount" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{8ADFD3E1-24FE-45CE-8A72-696379253170}" name="Notes" dataDxfId="25" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}" name="Table3" displayName="Table3" ref="E16:H21" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}" name="Table3" displayName="Table3" ref="E16:H21" totalsRowShown="0" headerRowDxfId="24">
   <autoFilter ref="E16:H21" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{88178FBB-1C68-4443-9D29-711B96CC8F3C}" name="Investment Type" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{AF13EBFA-AD22-4799-B232-349084129FC2}" name="Percentage" dataDxfId="20" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{06249914-8982-4D40-BF2A-A24479258B7E}" name="Current Amount" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{88178FBB-1C68-4443-9D29-711B96CC8F3C}" name="Investment Type" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{AF13EBFA-AD22-4799-B232-349084129FC2}" name="Percentage" dataDxfId="22" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{06249914-8982-4D40-BF2A-A24479258B7E}" name="Current Amount" dataDxfId="21">
       <calculatedColumnFormula>Tracker!$C$2*Portfolio!F17</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BE746FA0-4394-410B-BFFB-E4580C3454EF}" name="Notes" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{BE746FA0-4394-410B-BFFB-E4580C3454EF}" name="Notes" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6518,14 +6530,14 @@
     <row r="4" spans="1:13" ht="15" thickBot="1"/>
     <row r="5" spans="1:13" ht="15.75" thickBot="1">
       <c r="C5" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D5" s="17">
         <f>SUM(D8:D10)</f>
         <v>5533706.5128571428</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H5" s="13">
         <f>SUM(K8:K18)</f>
@@ -6563,22 +6575,22 @@
       <c r="L7" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="M7" s="39" t="s">
+      <c r="M7" s="38" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="77">
+      <c r="D8" s="76">
         <f>71254500/14</f>
         <v>5089607.1428571427</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="56">
         <v>25</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="40" t="s">
         <v>2</v>
       </c>
       <c r="H8" s="5">
@@ -6598,23 +6610,23 @@
       <c r="L8" s="28">
         <v>5</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="M8" s="125" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="76">
         <f>241890.11/3</f>
         <v>80630.036666666667</v>
       </c>
-      <c r="E9" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="G9" s="41" t="s">
-        <v>300</v>
+      <c r="E9" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>298</v>
       </c>
       <c r="H9" s="5">
         <v>3550</v>
@@ -6632,30 +6644,30 @@
       </c>
       <c r="L9" s="30">
         <f ca="1">A1048575+_xlfn.CEILING.MATH((TODAY()-A1048575)/21, 1)*21</f>
-        <v>46300</v>
-      </c>
-      <c r="M9" s="40" t="s">
+        <v>46321</v>
+      </c>
+      <c r="M9" s="125" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" thickBot="1">
-      <c r="C10" s="67" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" s="86">
+      <c r="C10" s="66" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="85">
         <f>1090408/3</f>
         <v>363469.33333333331</v>
       </c>
-      <c r="E10" s="86" t="s">
-        <v>270</v>
-      </c>
-      <c r="G10" s="41" t="s">
-        <v>302</v>
+      <c r="E10" s="85" t="s">
+        <v>268</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>300</v>
       </c>
       <c r="H10" s="5">
         <v>15000</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="106">
         <v>8</v>
       </c>
       <c r="J10" s="5">
@@ -6667,21 +6679,21 @@
         <v>120000</v>
       </c>
       <c r="L10" s="28"/>
-      <c r="M10" s="40"/>
+      <c r="M10" s="125"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="C11" s="83" t="s">
+      <c r="C11" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="84">
+      <c r="D11" s="83">
         <f>35*D29</f>
         <v>111821.08626198082</v>
       </c>
-      <c r="E11" s="85" t="s">
+      <c r="E11" s="84" t="s">
         <v>219</v>
       </c>
-      <c r="G11" s="41" t="s">
-        <v>301</v>
+      <c r="G11" s="40" t="s">
+        <v>299</v>
       </c>
       <c r="H11" s="5">
         <v>6400</v>
@@ -6701,22 +6713,22 @@
       <c r="L11" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="M11" s="40" t="s">
+      <c r="M11" s="125" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="C12" s="78" t="s">
+      <c r="C12" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="79">
+      <c r="D12" s="78">
         <f>35*D30</f>
         <v>0</v>
       </c>
-      <c r="E12" s="74" t="s">
-        <v>210</v>
-      </c>
-      <c r="G12" s="41" t="s">
+      <c r="E12" s="73" t="s">
+        <v>210</v>
+      </c>
+      <c r="G12" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H12" s="5">
@@ -6736,21 +6748,21 @@
       <c r="L12" s="28">
         <v>23</v>
       </c>
-      <c r="M12" s="40" t="s">
+      <c r="M12" s="125" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="80">
         <v>440000</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="74">
         <v>10</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="40" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="5">
@@ -6771,22 +6783,22 @@
       <c r="L13" s="28">
         <v>25</v>
       </c>
-      <c r="M13" s="40" t="s">
+      <c r="M13" s="125" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="C14" s="82" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="73">
+      <c r="C14" s="81" t="s">
+        <v>304</v>
+      </c>
+      <c r="D14" s="72">
         <f>D13-J17-J18</f>
-        <v>342833.33333333331</v>
-      </c>
-      <c r="E14" s="76" t="s">
-        <v>210</v>
-      </c>
-      <c r="G14" s="41" t="s">
+        <v>338676.4705882353</v>
+      </c>
+      <c r="E14" s="75" t="s">
+        <v>210</v>
+      </c>
+      <c r="G14" s="40" t="s">
         <v>4</v>
       </c>
       <c r="H14" s="5">
@@ -6807,12 +6819,12 @@
       <c r="L14" s="28">
         <v>25</v>
       </c>
-      <c r="M14" s="40" t="s">
+      <c r="M14" s="125" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="G15" s="41" t="s">
+      <c r="G15" s="40" t="s">
         <v>226</v>
       </c>
       <c r="H15" s="5">
@@ -6832,18 +6844,18 @@
       <c r="L15" s="28">
         <v>25</v>
       </c>
-      <c r="M15" s="40" t="s">
+      <c r="M15" s="125" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="G16" s="41" t="s">
-        <v>233</v>
+      <c r="G16" s="40" t="s">
+        <v>231</v>
       </c>
       <c r="H16" s="5">
         <v>30000</v>
       </c>
-      <c r="I16" s="108">
+      <c r="I16" s="107">
         <v>1</v>
       </c>
       <c r="J16" s="5">
@@ -6855,10 +6867,10 @@
         <v>30000</v>
       </c>
       <c r="L16" s="28"/>
-      <c r="M16" s="40"/>
+      <c r="M16" s="125"/>
     </row>
     <row r="17" spans="3:13">
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="41" t="s">
         <v>6</v>
       </c>
       <c r="H17" s="10">
@@ -6877,24 +6889,24 @@
       <c r="L17" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="M17" s="29" t="s">
-        <v>230</v>
+      <c r="M17" s="124" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="3:13">
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="41" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="10">
-        <v>205000</v>
-      </c>
-      <c r="I18" s="38">
-        <f>1/3.75</f>
-        <v>0.26666666666666666</v>
+        <v>250000</v>
+      </c>
+      <c r="I18" s="32">
+        <f>1/4.25</f>
+        <v>0.23529411764705882</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="3"/>
-        <v>54666.666666666664</v>
+        <v>58823.529411764706</v>
       </c>
       <c r="K18" s="11">
         <f>0</f>
@@ -6903,14 +6915,19 @@
       <c r="L18" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="M18" s="29" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="20" spans="3:13" ht="15" thickBot="1"/>
+      <c r="M18" s="124" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13">
+      <c r="M19" s="126"/>
+    </row>
+    <row r="20" spans="3:13" ht="15" thickBot="1">
+      <c r="J20" s="8"/>
+    </row>
     <row r="21" spans="3:13" ht="15.75" thickBot="1">
       <c r="C21" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D21" s="12">
         <f>D5-H5</f>
@@ -7060,1356 +7077,1356 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1"/>
     <row r="2" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B2" s="105" t="s">
-        <v>299</v>
-      </c>
-      <c r="C2" s="106">
+      <c r="B2" s="104" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" s="105">
         <v>50000000</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="15">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="D5" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="E5" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="H5" s="111" t="s">
         <v>295</v>
       </c>
-      <c r="D5" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>296</v>
-      </c>
-      <c r="H5" s="112" t="s">
-        <v>297</v>
-      </c>
-      <c r="I5" s="112"/>
+      <c r="I5" s="111"/>
     </row>
     <row r="6" spans="2:9" ht="15">
-      <c r="B6" s="87">
+      <c r="B6" s="86">
         <v>46023</v>
       </c>
-      <c r="C6" s="102">
+      <c r="C6" s="101">
         <f>27037512.04+15400000</f>
         <v>42437512.039999999</v>
       </c>
-      <c r="D6" s="102">
+      <c r="D6" s="101">
         <f>27037512.04</f>
         <v>27037512.039999999</v>
       </c>
-      <c r="E6" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="H6" s="104" t="s">
-        <v>291</v>
-      </c>
-      <c r="I6" s="104" t="s">
-        <v>295</v>
+      <c r="E6" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="H6" s="103" t="s">
+        <v>289</v>
+      </c>
+      <c r="I6" s="103" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="87">
+      <c r="B7" s="86">
         <f>EDATE(B6,1)</f>
         <v>46054</v>
       </c>
-      <c r="C7" s="102">
+      <c r="C7" s="101">
         <f>30821932.81+15400000</f>
         <v>46221932.810000002</v>
       </c>
-      <c r="D7" s="102">
+      <c r="D7" s="101">
         <f>30821932.81</f>
         <v>30821932.809999999</v>
       </c>
-      <c r="E7" s="102">
+      <c r="E7" s="101">
         <f>Table9[[#This Row],[General Balance]]-C6</f>
         <v>3784420.7700000033</v>
       </c>
-      <c r="F7" s="102">
+      <c r="F7" s="101">
         <f>4520137.94-E7</f>
         <v>735717.16999999713</v>
       </c>
-      <c r="H7" s="103">
+      <c r="H7" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
         <v>46143</v>
       </c>
-      <c r="I7" s="102">
+      <c r="I7" s="101">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
         <v>55912013.149999999</v>
       </c>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="87">
+      <c r="B8" s="86">
         <f t="shared" ref="B8:B65" si="0">EDATE(B7,1)</f>
         <v>46082</v>
       </c>
-      <c r="C8" s="102">
+      <c r="C8" s="101">
         <f>34124040.84+15400000</f>
         <v>49524040.840000004</v>
       </c>
-      <c r="D8" s="102">
+      <c r="D8" s="101">
         <f>34124040.84</f>
         <v>34124040.840000004</v>
       </c>
-      <c r="E8" s="102">
+      <c r="E8" s="101">
         <f>Table9[[#This Row],[General Balance]]-C7</f>
         <v>3302108.0300000012</v>
       </c>
-      <c r="F8" s="102">
+      <c r="F8" s="101">
         <f t="shared" ref="F8:F65" si="1">4520137.94-E8</f>
         <v>1218029.9099999992</v>
       </c>
-      <c r="H8" s="103">
+      <c r="H8" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
         <v>46174</v>
       </c>
-      <c r="I8" s="102">
+      <c r="I8" s="101">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
         <v>61491091.960000001</v>
       </c>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="87">
+      <c r="B9" s="86">
         <f t="shared" si="0"/>
         <v>46113</v>
       </c>
-      <c r="C9" s="102">
+      <c r="C9" s="101">
         <f>37390636.8+15400000</f>
         <v>52790636.799999997</v>
       </c>
-      <c r="D9" s="102">
+      <c r="D9" s="101">
         <f>37390636.8</f>
         <v>37390636.799999997</v>
       </c>
-      <c r="E9" s="102">
+      <c r="E9" s="101">
         <f>Table9[[#This Row],[General Balance]]-C8</f>
         <v>3266595.9599999934</v>
       </c>
-      <c r="F9" s="102">
+      <c r="F9" s="101">
         <f t="shared" si="1"/>
         <v>1253541.980000007</v>
       </c>
-      <c r="H9" s="103">
+      <c r="H9" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
         <v>46204</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="101">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
         <v>64900000</v>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="B10" s="87">
+      <c r="B10" s="86">
         <f t="shared" si="0"/>
         <v>46143</v>
       </c>
-      <c r="C10" s="102">
+      <c r="C10" s="101">
         <f>40512013.15+15400000</f>
         <v>55912013.149999999</v>
       </c>
-      <c r="D10" s="102">
+      <c r="D10" s="101">
         <f>40512013.15</f>
         <v>40512013.149999999</v>
       </c>
-      <c r="E10" s="102">
+      <c r="E10" s="101">
         <f>Table9[[#This Row],[General Balance]]-C9</f>
         <v>3121376.3500000015</v>
       </c>
-      <c r="F10" s="102">
+      <c r="F10" s="101">
         <f t="shared" si="1"/>
         <v>1398761.5899999989</v>
       </c>
-      <c r="H10" s="103">
+      <c r="H10" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
         <v>46235</v>
       </c>
-      <c r="I10" s="102">
+      <c r="I10" s="101">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
         <v>65265421.539999999</v>
       </c>
     </row>
     <row r="11" spans="2:9">
-      <c r="B11" s="87">
+      <c r="B11" s="86">
         <f t="shared" si="0"/>
         <v>46174</v>
       </c>
-      <c r="C11" s="102">
+      <c r="C11" s="101">
         <f>46091091.96+15400000</f>
         <v>61491091.960000001</v>
       </c>
-      <c r="D11" s="102">
+      <c r="D11" s="101">
         <f>46091091.96</f>
         <v>46091091.960000001</v>
       </c>
-      <c r="E11" s="102">
+      <c r="E11" s="101">
         <f>Table9[[#This Row],[General Balance]]-C10</f>
         <v>5579078.8100000024</v>
       </c>
-      <c r="F11" s="102">
+      <c r="F11" s="101">
         <f t="shared" si="1"/>
         <v>-1058940.870000002</v>
       </c>
-      <c r="H11" s="103">
+      <c r="H11" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
         <v>46266</v>
       </c>
-      <c r="I11" s="102">
+      <c r="I11" s="101">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
         <v>69506976.569999993</v>
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="87">
+      <c r="B12" s="86">
         <f t="shared" si="0"/>
         <v>46204</v>
       </c>
-      <c r="C12" s="102">
+      <c r="C12" s="101">
         <f>9500000+15400000+37000000+3000000</f>
         <v>64900000</v>
       </c>
-      <c r="D12" s="102">
+      <c r="D12" s="101">
         <f>9500000</f>
         <v>9500000</v>
       </c>
-      <c r="E12" s="102">
+      <c r="E12" s="101">
         <f>Table9[[#This Row],[General Balance]]-C11</f>
         <v>3408908.0399999991</v>
       </c>
-      <c r="F12" s="102">
+      <c r="F12" s="101">
         <f t="shared" si="1"/>
         <v>1111229.9000000013</v>
       </c>
-      <c r="H12" s="103">
+      <c r="H12" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
         <v>46296</v>
       </c>
-      <c r="I12" s="102">
+      <c r="I12" s="101">
         <f ca="1">INDEX(Table9[General Balance],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
         <v>74189383.569999993</v>
       </c>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="87">
+      <c r="B13" s="86">
         <f t="shared" si="0"/>
         <v>46235</v>
       </c>
-      <c r="C13" s="102">
+      <c r="C13" s="101">
         <f>Table9[[#This Row],[Account Balance]]+15400000+37000000+6000000</f>
         <v>65265421.539999999</v>
       </c>
-      <c r="D13" s="102">
+      <c r="D13" s="101">
         <v>6865421.54</v>
       </c>
-      <c r="E13" s="102">
+      <c r="E13" s="101">
         <f>4682407-350000-220000-57030-16500-160000-469769</f>
         <v>3409108</v>
       </c>
-      <c r="F13" s="102">
+      <c r="F13" s="101">
         <f t="shared" si="1"/>
         <v>1111029.9400000004</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="15">
-      <c r="B14" s="87">
+      <c r="B14" s="86">
         <f t="shared" si="0"/>
         <v>46266</v>
       </c>
-      <c r="C14" s="102">
+      <c r="C14" s="101">
         <f>C13+(Table9[[#This Row],[Account Balance]]-D13)+Main!D10+Main!D9</f>
         <v>69506976.569999993</v>
       </c>
-      <c r="D14" s="102">
+      <c r="D14" s="101">
         <v>10662877.199999999</v>
       </c>
-      <c r="E14" s="102">
+      <c r="E14" s="101">
         <f>Table9[[#This Row],[General Balance]]-C13</f>
         <v>4241555.0299999937</v>
       </c>
-      <c r="F14" s="102">
+      <c r="F14" s="101">
         <f>Main!D21-E14</f>
         <v>171182.9114285782</v>
       </c>
-      <c r="H14" s="112" t="s">
-        <v>298</v>
-      </c>
-      <c r="I14" s="112"/>
+      <c r="H14" s="111" t="s">
+        <v>296</v>
+      </c>
+      <c r="I14" s="111"/>
     </row>
     <row r="15" spans="2:9" ht="15">
-      <c r="B15" s="87">
+      <c r="B15" s="86">
         <f t="shared" si="0"/>
         <v>46296</v>
       </c>
-      <c r="C15" s="102">
+      <c r="C15" s="101">
         <f>C14+4682407</f>
         <v>74189383.569999993</v>
       </c>
-      <c r="D15" s="102">
+      <c r="D15" s="101">
         <v>25255077.379999999</v>
       </c>
-      <c r="E15" s="102">
+      <c r="E15" s="101">
         <f>Table9[[#This Row],[General Balance]]-C14</f>
         <v>4682407</v>
       </c>
-      <c r="F15" s="102">
+      <c r="F15" s="101">
         <f t="shared" si="1"/>
         <v>-162269.05999999959</v>
       </c>
-      <c r="H15" s="104" t="s">
-        <v>291</v>
-      </c>
-      <c r="I15" s="104" t="s">
-        <v>296</v>
+      <c r="H15" s="103" t="s">
+        <v>289</v>
+      </c>
+      <c r="I15" s="103" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="87">
+      <c r="B16" s="86">
         <f t="shared" si="0"/>
         <v>46327</v>
       </c>
-      <c r="C16" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D16" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" s="102" t="e">
+      <c r="C16" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E16" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F16" s="102" t="e">
+      <c r="F16" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H16" s="103">
+      <c r="H16" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
         <v>46143</v>
       </c>
-      <c r="I16" s="102">
+      <c r="I16" s="101">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-6)+1,Table9[Date],1))</f>
         <v>1398761.5899999989</v>
       </c>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="87">
+      <c r="B17" s="86">
         <f t="shared" si="0"/>
         <v>46357</v>
       </c>
-      <c r="C17" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D17" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E17" s="102" t="e">
+      <c r="C17" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C16</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F17" s="102" t="e">
+      <c r="F17" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H17" s="103">
+      <c r="H17" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
         <v>46174</v>
       </c>
-      <c r="I17" s="102">
+      <c r="I17" s="101">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-5)+1,Table9[Date],1))</f>
         <v>-1058940.870000002</v>
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="87">
+      <c r="B18" s="86">
         <f t="shared" si="0"/>
         <v>46388</v>
       </c>
-      <c r="C18" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="102" t="e">
+      <c r="C18" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C17</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F18" s="102" t="e">
+      <c r="F18" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H18" s="103">
+      <c r="H18" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
         <v>46204</v>
       </c>
-      <c r="I18" s="102">
+      <c r="I18" s="101">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-4)+1,Table9[Date],1))</f>
         <v>1111229.9000000013</v>
       </c>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="87">
+      <c r="B19" s="86">
         <f t="shared" si="0"/>
         <v>46419</v>
       </c>
-      <c r="C19" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D19" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="102" t="e">
+      <c r="C19" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C18</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F19" s="102" t="e">
+      <c r="F19" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H19" s="103">
+      <c r="H19" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
         <v>46235</v>
       </c>
-      <c r="I19" s="102">
+      <c r="I19" s="101">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-3)+1,Table9[Date],1))</f>
         <v>1111029.9400000004</v>
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="87">
+      <c r="B20" s="86">
         <f t="shared" si="0"/>
         <v>46447</v>
       </c>
-      <c r="C20" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D20" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="102" t="e">
+      <c r="C20" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C19</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F20" s="102" t="e">
+      <c r="F20" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H20" s="103">
+      <c r="H20" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
         <v>46266</v>
       </c>
-      <c r="I20" s="102">
+      <c r="I20" s="101">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
         <v>171182.9114285782</v>
       </c>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="87">
+      <c r="B21" s="86">
         <f t="shared" si="0"/>
         <v>46478</v>
       </c>
-      <c r="C21" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D21" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="102" t="e">
+      <c r="C21" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D21" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C20</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F21" s="102" t="e">
+      <c r="F21" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="103">
+      <c r="H21" s="102">
         <f ca="1">INDEX(Table9[Date],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
         <v>46296</v>
       </c>
-      <c r="I21" s="102">
+      <c r="I21" s="101">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-1)+1,Table9[Date],1))</f>
         <v>-162269.05999999959</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="87">
+      <c r="B22" s="86">
         <f t="shared" si="0"/>
         <v>46508</v>
       </c>
-      <c r="C22" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D22" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E22" s="102" t="e">
+      <c r="C22" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E22" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C21</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F22" s="102" t="e">
+      <c r="F22" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="87">
+      <c r="B23" s="86">
         <f t="shared" si="0"/>
         <v>46539</v>
       </c>
-      <c r="C23" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D23" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E23" s="102" t="e">
+      <c r="C23" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D23" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E23" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F23" s="102" t="e">
+      <c r="F23" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="87">
+      <c r="B24" s="86">
         <f t="shared" si="0"/>
         <v>46569</v>
       </c>
-      <c r="C24" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D24" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="102" t="e">
+      <c r="C24" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D24" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F24" s="102" t="e">
+      <c r="F24" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="87">
+      <c r="B25" s="86">
         <f t="shared" si="0"/>
         <v>46600</v>
       </c>
-      <c r="C25" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D25" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E25" s="102" t="e">
+      <c r="C25" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D25" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E25" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C24</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F25" s="102" t="e">
+      <c r="F25" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="87">
+      <c r="B26" s="86">
         <f t="shared" si="0"/>
         <v>46631</v>
       </c>
-      <c r="C26" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D26" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E26" s="102" t="e">
+      <c r="C26" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D26" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E26" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C25</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="102" t="e">
+      <c r="F26" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="87">
+      <c r="B27" s="86">
         <f t="shared" si="0"/>
         <v>46661</v>
       </c>
-      <c r="C27" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E27" s="102" t="e">
+      <c r="C27" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D27" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E27" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C26</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F27" s="102" t="e">
+      <c r="F27" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="87">
+      <c r="B28" s="86">
         <f t="shared" si="0"/>
         <v>46692</v>
       </c>
-      <c r="C28" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D28" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E28" s="102" t="e">
+      <c r="C28" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D28" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F28" s="102" t="e">
+      <c r="F28" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="87">
+      <c r="B29" s="86">
         <f t="shared" si="0"/>
         <v>46722</v>
       </c>
-      <c r="C29" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D29" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E29" s="102" t="e">
+      <c r="C29" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D29" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E29" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C28</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F29" s="102" t="e">
+      <c r="F29" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="87">
+      <c r="B30" s="86">
         <f t="shared" si="0"/>
         <v>46753</v>
       </c>
-      <c r="C30" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D30" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E30" s="102" t="e">
+      <c r="C30" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E30" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F30" s="102" t="e">
+      <c r="F30" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="87">
+      <c r="B31" s="86">
         <f t="shared" si="0"/>
         <v>46784</v>
       </c>
-      <c r="C31" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D31" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E31" s="102" t="e">
+      <c r="C31" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D31" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F31" s="102" t="e">
+      <c r="F31" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="87">
+      <c r="B32" s="86">
         <f t="shared" si="0"/>
         <v>46813</v>
       </c>
-      <c r="C32" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D32" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E32" s="102" t="e">
+      <c r="C32" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C31</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="102" t="e">
+      <c r="F32" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="87">
+      <c r="B33" s="86">
         <f t="shared" si="0"/>
         <v>46844</v>
       </c>
-      <c r="C33" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D33" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E33" s="102" t="e">
+      <c r="C33" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D33" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E33" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C32</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F33" s="102" t="e">
+      <c r="F33" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="87">
+      <c r="B34" s="86">
         <f t="shared" si="0"/>
         <v>46874</v>
       </c>
-      <c r="C34" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D34" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E34" s="102" t="e">
+      <c r="C34" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E34" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C33</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F34" s="102" t="e">
+      <c r="F34" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="87">
+      <c r="B35" s="86">
         <f t="shared" si="0"/>
         <v>46905</v>
       </c>
-      <c r="C35" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D35" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E35" s="102" t="e">
+      <c r="C35" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C34</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F35" s="102" t="e">
+      <c r="F35" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="87">
+      <c r="B36" s="86">
         <f t="shared" si="0"/>
         <v>46935</v>
       </c>
-      <c r="C36" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D36" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E36" s="102" t="e">
+      <c r="C36" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D36" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E36" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C35</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F36" s="102" t="e">
+      <c r="F36" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="37" spans="2:6">
-      <c r="B37" s="87">
+      <c r="B37" s="86">
         <f t="shared" si="0"/>
         <v>46966</v>
       </c>
-      <c r="C37" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D37" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E37" s="102" t="e">
+      <c r="C37" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D37" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E37" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C36</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F37" s="102" t="e">
+      <c r="F37" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="87">
+      <c r="B38" s="86">
         <f t="shared" si="0"/>
         <v>46997</v>
       </c>
-      <c r="C38" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D38" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E38" s="102" t="e">
+      <c r="C38" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E38" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C37</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F38" s="102" t="e">
+      <c r="F38" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="87">
+      <c r="B39" s="86">
         <f t="shared" si="0"/>
         <v>47027</v>
       </c>
-      <c r="C39" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D39" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E39" s="102" t="e">
+      <c r="C39" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D39" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E39" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C38</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F39" s="102" t="e">
+      <c r="F39" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="87">
+      <c r="B40" s="86">
         <f t="shared" si="0"/>
         <v>47058</v>
       </c>
-      <c r="C40" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D40" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E40" s="102" t="e">
+      <c r="C40" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D40" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E40" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C39</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F40" s="102" t="e">
+      <c r="F40" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="87">
+      <c r="B41" s="86">
         <f t="shared" si="0"/>
         <v>47088</v>
       </c>
-      <c r="C41" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D41" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E41" s="102" t="e">
+      <c r="C41" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E41" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C40</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F41" s="102" t="e">
+      <c r="F41" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="42" spans="2:6">
-      <c r="B42" s="87">
+      <c r="B42" s="86">
         <f t="shared" si="0"/>
         <v>47119</v>
       </c>
-      <c r="C42" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D42" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E42" s="102" t="e">
+      <c r="C42" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D42" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E42" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C41</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F42" s="102" t="e">
+      <c r="F42" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="87">
+      <c r="B43" s="86">
         <f t="shared" si="0"/>
         <v>47150</v>
       </c>
-      <c r="C43" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D43" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E43" s="102" t="e">
+      <c r="C43" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E43" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C42</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F43" s="102" t="e">
+      <c r="F43" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="87">
+      <c r="B44" s="86">
         <f t="shared" si="0"/>
         <v>47178</v>
       </c>
-      <c r="C44" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D44" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E44" s="102" t="e">
+      <c r="C44" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D44" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E44" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C43</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F44" s="102" t="e">
+      <c r="F44" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="87">
+      <c r="B45" s="86">
         <f t="shared" si="0"/>
         <v>47209</v>
       </c>
-      <c r="C45" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D45" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E45" s="102" t="e">
+      <c r="C45" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D45" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E45" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C44</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F45" s="102" t="e">
+      <c r="F45" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="46" spans="2:6">
-      <c r="B46" s="87">
+      <c r="B46" s="86">
         <f t="shared" si="0"/>
         <v>47239</v>
       </c>
-      <c r="C46" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D46" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E46" s="102" t="e">
+      <c r="C46" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D46" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E46" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C45</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F46" s="102" t="e">
+      <c r="F46" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="87">
+      <c r="B47" s="86">
         <f t="shared" si="0"/>
         <v>47270</v>
       </c>
-      <c r="C47" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D47" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E47" s="102" t="e">
+      <c r="C47" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E47" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C46</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F47" s="102" t="e">
+      <c r="F47" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="48" spans="2:6">
-      <c r="B48" s="87">
+      <c r="B48" s="86">
         <f t="shared" si="0"/>
         <v>47300</v>
       </c>
-      <c r="C48" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D48" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E48" s="102" t="e">
+      <c r="C48" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D48" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E48" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C47</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F48" s="102" t="e">
+      <c r="F48" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="87">
+      <c r="B49" s="86">
         <f t="shared" si="0"/>
         <v>47331</v>
       </c>
-      <c r="C49" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D49" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E49" s="102" t="e">
+      <c r="C49" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D49" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C48</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F49" s="102" t="e">
+      <c r="F49" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="87">
+      <c r="B50" s="86">
         <f t="shared" si="0"/>
         <v>47362</v>
       </c>
-      <c r="C50" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D50" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E50" s="102" t="e">
+      <c r="C50" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D50" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E50" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C49</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F50" s="102" t="e">
+      <c r="F50" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="87">
+      <c r="B51" s="86">
         <f t="shared" si="0"/>
         <v>47392</v>
       </c>
-      <c r="C51" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D51" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E51" s="102" t="e">
+      <c r="C51" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D51" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E51" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C50</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F51" s="102" t="e">
+      <c r="F51" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="87">
+      <c r="B52" s="86">
         <f t="shared" si="0"/>
         <v>47423</v>
       </c>
-      <c r="C52" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D52" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E52" s="102" t="e">
+      <c r="C52" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D52" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E52" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C51</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F52" s="102" t="e">
+      <c r="F52" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="87">
+      <c r="B53" s="86">
         <f t="shared" si="0"/>
         <v>47453</v>
       </c>
-      <c r="C53" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D53" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E53" s="102" t="e">
+      <c r="C53" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D53" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E53" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C52</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F53" s="102" t="e">
+      <c r="F53" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="87">
+      <c r="B54" s="86">
         <f t="shared" si="0"/>
         <v>47484</v>
       </c>
-      <c r="C54" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D54" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E54" s="102" t="e">
+      <c r="C54" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D54" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E54" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C53</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F54" s="102" t="e">
+      <c r="F54" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="87">
+      <c r="B55" s="86">
         <f t="shared" si="0"/>
         <v>47515</v>
       </c>
-      <c r="C55" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D55" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E55" s="102" t="e">
+      <c r="C55" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E55" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C54</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F55" s="102" t="e">
+      <c r="F55" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="56" spans="2:6">
-      <c r="B56" s="87">
+      <c r="B56" s="86">
         <f t="shared" si="0"/>
         <v>47543</v>
       </c>
-      <c r="C56" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D56" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E56" s="102" t="e">
+      <c r="C56" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D56" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E56" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C55</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F56" s="102" t="e">
+      <c r="F56" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="87">
+      <c r="B57" s="86">
         <f t="shared" si="0"/>
         <v>47574</v>
       </c>
-      <c r="C57" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D57" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E57" s="102" t="e">
+      <c r="C57" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D57" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E57" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C56</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F57" s="102" t="e">
+      <c r="F57" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="87">
+      <c r="B58" s="86">
         <f t="shared" si="0"/>
         <v>47604</v>
       </c>
-      <c r="C58" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D58" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58" s="102" t="e">
+      <c r="C58" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D58" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C57</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F58" s="102" t="e">
+      <c r="F58" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="59" spans="2:6">
-      <c r="B59" s="87">
+      <c r="B59" s="86">
         <f t="shared" si="0"/>
         <v>47635</v>
       </c>
-      <c r="C59" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D59" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E59" s="102" t="e">
+      <c r="C59" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D59" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E59" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C58</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F59" s="102" t="e">
+      <c r="F59" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="60" spans="2:6">
-      <c r="B60" s="87">
+      <c r="B60" s="86">
         <f t="shared" si="0"/>
         <v>47665</v>
       </c>
-      <c r="C60" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D60" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E60" s="102" t="e">
+      <c r="C60" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E60" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C59</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F60" s="102" t="e">
+      <c r="F60" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="87">
+      <c r="B61" s="86">
         <f t="shared" si="0"/>
         <v>47696</v>
       </c>
-      <c r="C61" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D61" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E61" s="102" t="e">
+      <c r="C61" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D61" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E61" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F61" s="102" t="e">
+      <c r="F61" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="87">
+      <c r="B62" s="86">
         <f t="shared" si="0"/>
         <v>47727</v>
       </c>
-      <c r="C62" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D62" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E62" s="102" t="e">
+      <c r="C62" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D62" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E62" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C61</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F62" s="102" t="e">
+      <c r="F62" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="63" spans="2:6">
-      <c r="B63" s="87">
+      <c r="B63" s="86">
         <f t="shared" si="0"/>
         <v>47757</v>
       </c>
-      <c r="C63" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D63" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E63" s="102" t="e">
+      <c r="C63" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D63" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E63" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C62</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F63" s="102" t="e">
+      <c r="F63" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="87">
+      <c r="B64" s="86">
         <f t="shared" si="0"/>
         <v>47788</v>
       </c>
-      <c r="C64" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D64" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E64" s="102" t="e">
+      <c r="C64" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D64" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E64" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C63</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F64" s="102" t="e">
+      <c r="F64" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="65" spans="2:6">
-      <c r="B65" s="87">
+      <c r="B65" s="86">
         <f t="shared" si="0"/>
         <v>47818</v>
       </c>
-      <c r="C65" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="D65" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="E65" s="102" t="e">
+      <c r="C65" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="D65" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="E65" s="101" t="e">
         <f>Table9[[#This Row],[General Balance]]-C64</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F65" s="102" t="e">
+      <c r="F65" s="101" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -8433,11 +8450,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E074D57D-0BB2-4D51-BFA3-6687E8A03A91}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="C1:G17"/>
+  <dimension ref="C1:G19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="27.25" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.375" style="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.25" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.375" style="45" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -8447,10 +8464,10 @@
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="3:7">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="D2" s="44">
+      <c r="D2" s="43">
         <f>100*Main!D29</f>
         <v>319488.81789137376</v>
       </c>
@@ -8459,130 +8476,146 @@
       </c>
       <c r="G2" s="5">
         <f>SUM(D2:D29)</f>
-        <v>10431799.635782748</v>
+        <v>12031799.635782748</v>
       </c>
     </row>
     <row r="3" spans="3:7">
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="D3" s="44">
+      <c r="D3" s="43">
         <v>490000</v>
       </c>
     </row>
     <row r="4" spans="3:7">
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="45">
         <v>1788000</v>
       </c>
       <c r="G4" s="8"/>
     </row>
     <row r="5" spans="3:7">
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="43">
         <f>100*Main!D29</f>
         <v>319488.81789137376</v>
       </c>
     </row>
     <row r="6" spans="3:7">
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="43">
         <v>234220</v>
       </c>
     </row>
     <row r="7" spans="3:7">
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="43">
         <v>14602</v>
       </c>
     </row>
     <row r="8" spans="3:7">
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="43">
         <v>4500000</v>
       </c>
     </row>
     <row r="9" spans="3:7">
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="43">
         <v>100000</v>
       </c>
     </row>
     <row r="10" spans="3:7">
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="45">
         <f>650000+730000-500000</f>
         <v>880000</v>
       </c>
     </row>
     <row r="11" spans="3:7">
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="42" t="s">
         <v>194</v>
       </c>
-      <c r="D11" s="44">
+      <c r="D11" s="43">
         <v>200000</v>
       </c>
     </row>
     <row r="12" spans="3:7">
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="43">
         <v>262000</v>
       </c>
     </row>
     <row r="13" spans="3:7">
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="D13" s="44">
+      <c r="D13" s="43">
         <v>204000</v>
       </c>
     </row>
     <row r="14" spans="3:7">
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="43">
         <v>120000</v>
       </c>
     </row>
     <row r="15" spans="3:7">
-      <c r="C15" s="45" t="s">
+      <c r="C15" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="45" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="16" spans="3:7">
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="42" t="s">
         <v>228</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="43">
         <v>100000</v>
       </c>
     </row>
     <row r="17" spans="3:4">
-      <c r="C17" s="43" t="s">
-        <v>238</v>
-      </c>
-      <c r="D17" s="44">
+      <c r="C17" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="D17" s="43">
         <v>900000</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4">
+      <c r="C18" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="D18" s="45">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4">
+      <c r="C19" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" s="45">
+        <v>600000</v>
       </c>
     </row>
   </sheetData>
@@ -8611,10 +8644,10 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15" thickBot="1"/>
     <row r="3" spans="2:12" ht="15.75" thickBot="1">
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="70">
+      <c r="C3" s="69">
         <f>D28+I28</f>
         <v>52631379.670000002</v>
       </c>
@@ -8625,29 +8658,29 @@
     </row>
     <row r="5" spans="2:12" ht="15" thickBot="1"/>
     <row r="6" spans="2:12" ht="15.75" thickBot="1">
-      <c r="C6" s="116" t="s">
+      <c r="C6" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118"/>
-      <c r="H6" s="113" t="s">
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="117"/>
+      <c r="H6" s="112" t="s">
         <v>205</v>
       </c>
-      <c r="I6" s="114"/>
-      <c r="J6" s="115"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="2:12" ht="15">
-      <c r="C7" s="63" t="s">
-        <v>244</v>
-      </c>
-      <c r="D7" s="62" t="s">
+      <c r="C7" s="62" t="s">
         <v>242</v>
       </c>
-      <c r="E7" s="62" t="s">
-        <v>243</v>
-      </c>
-      <c r="F7" s="59" t="s">
+      <c r="D7" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="E7" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="F7" s="58" t="s">
         <v>203</v>
       </c>
       <c r="H7" s="33" t="s">
@@ -8656,255 +8689,255 @@
       <c r="I7" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="J7" s="64" t="s">
+      <c r="J7" s="63" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="48">
         <f>316170</f>
         <v>316170</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="55"/>
-      <c r="H8" s="41" t="s">
+      <c r="E8" s="48"/>
+      <c r="F8" s="54"/>
+      <c r="H8" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="I8" s="65">
+      <c r="I8" s="64">
         <v>10211609.67</v>
       </c>
-      <c r="J8" s="66" t="s">
-        <v>239</v>
+      <c r="J8" s="65" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="48">
         <f>500000-(730000+200000)+600000</f>
         <v>170000</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="56"/>
-      <c r="H9" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="I9" s="65">
+      <c r="E9" s="48"/>
+      <c r="F9" s="55"/>
+      <c r="H9" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="I9" s="64">
         <v>37000000</v>
       </c>
-      <c r="J9" s="101" t="s">
-        <v>271</v>
-      </c>
-      <c r="K9" s="100"/>
+      <c r="J9" s="100" t="s">
+        <v>269</v>
+      </c>
+      <c r="K9" s="99"/>
     </row>
     <row r="10" spans="2:12">
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="52" t="s">
         <v>191</v>
       </c>
-      <c r="D10" s="49">
+      <c r="D10" s="48">
         <v>5400000</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="56"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="66"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="55"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="65"/>
     </row>
     <row r="11" spans="2:12">
-      <c r="C11" s="53" t="s">
-        <v>240</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49">
+      <c r="C11" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48">
         <v>300000</v>
       </c>
-      <c r="F11" s="56"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="66"/>
+      <c r="F11" s="55"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="65"/>
     </row>
     <row r="12" spans="2:12">
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49">
+      <c r="D12" s="48"/>
+      <c r="E12" s="48">
         <v>100000</v>
       </c>
-      <c r="F12" s="56"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="66"/>
+      <c r="F12" s="55"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="2:12">
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49">
+      <c r="D13" s="48"/>
+      <c r="E13" s="48">
         <v>48000</v>
       </c>
-      <c r="F13" s="56"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="66"/>
+      <c r="F13" s="55"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="65"/>
     </row>
     <row r="14" spans="2:12">
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="52" t="s">
         <v>217</v>
       </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49">
+      <c r="D14" s="48"/>
+      <c r="E14" s="48">
         <v>18400</v>
       </c>
-      <c r="F14" s="56"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="66"/>
+      <c r="F14" s="55"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="65"/>
     </row>
     <row r="15" spans="2:12">
-      <c r="C15" s="53"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="56"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="66"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="55"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="65"/>
     </row>
     <row r="16" spans="2:12">
-      <c r="C16" s="53"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="56"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="66"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="55"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="65"/>
     </row>
     <row r="17" spans="3:14">
-      <c r="C17" s="53"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="56"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="66"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="55"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="65"/>
     </row>
     <row r="18" spans="3:14">
-      <c r="C18" s="53"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="56"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="66"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="55"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="65"/>
     </row>
     <row r="19" spans="3:14">
-      <c r="C19" s="53"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="56"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="66"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="55"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="65"/>
     </row>
     <row r="20" spans="3:14">
-      <c r="C20" s="53"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="56"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="66"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="55"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="65"/>
     </row>
     <row r="21" spans="3:14">
-      <c r="C21" s="53"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="56"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="66"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="55"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="65"/>
     </row>
     <row r="22" spans="3:14">
-      <c r="C22" s="53"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="56"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="66"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="55"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="65"/>
     </row>
     <row r="23" spans="3:14">
-      <c r="C23" s="53"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="56"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="66"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="55"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="65"/>
     </row>
     <row r="24" spans="3:14">
-      <c r="C24" s="53"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="56"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="66"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="55"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="65"/>
     </row>
     <row r="25" spans="3:14">
-      <c r="C25" s="41"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="57"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="66"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="56"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="65"/>
     </row>
     <row r="26" spans="3:14">
-      <c r="C26" s="41"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="57"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="66"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="56"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="65"/>
     </row>
     <row r="27" spans="3:14" ht="15" thickBot="1">
-      <c r="C27" s="54"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="58"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="68"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="57"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="67"/>
     </row>
     <row r="28" spans="3:14" ht="15.75" thickBot="1">
-      <c r="C28" s="60" t="s">
-        <v>241</v>
-      </c>
-      <c r="D28" s="119">
+      <c r="C28" s="59" t="s">
+        <v>239</v>
+      </c>
+      <c r="D28" s="118">
         <f>SUM(Table5[Incoming])-SUM(Table5[Outcoming])</f>
         <v>5419770</v>
       </c>
-      <c r="E28" s="120"/>
-      <c r="F28" s="121"/>
-      <c r="H28" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="I28" s="122">
+      <c r="E28" s="119"/>
+      <c r="F28" s="120"/>
+      <c r="H28" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="I28" s="121">
         <f>SUM(Table6[Amount])</f>
         <v>47211609.670000002</v>
       </c>
-      <c r="J28" s="123"/>
-      <c r="K28" s="40"/>
+      <c r="J28" s="122"/>
+      <c r="K28" s="39"/>
     </row>
     <row r="29" spans="3:14">
-      <c r="N29" s="61"/>
+      <c r="N29" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8951,526 +8984,526 @@
   </cols>
   <sheetData>
     <row r="5" spans="5:31">
-      <c r="AB5" s="124"/>
-      <c r="AC5" s="124"/>
-      <c r="AD5" s="124"/>
-      <c r="AE5" s="124"/>
+      <c r="AB5" s="123"/>
+      <c r="AC5" s="123"/>
+      <c r="AD5" s="123"/>
+      <c r="AE5" s="123"/>
     </row>
     <row r="8" spans="5:31" ht="15">
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="71" t="s">
+        <v>250</v>
+      </c>
+      <c r="F8" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="G8" s="71" t="s">
         <v>252</v>
       </c>
-      <c r="F8" s="72" t="s">
+    </row>
+    <row r="9" spans="5:31" ht="15">
+      <c r="E9" s="71" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="70" t="s">
+        <v>257</v>
+      </c>
+      <c r="G9" s="70" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="5:31" ht="15">
+      <c r="E10" s="71" t="s">
+        <v>245</v>
+      </c>
+      <c r="F10" s="70" t="s">
+        <v>255</v>
+      </c>
+      <c r="G10" s="70" t="s">
         <v>253</v>
       </c>
-      <c r="G8" s="72" t="s">
+    </row>
+    <row r="11" spans="5:31" ht="15">
+      <c r="E11" s="71" t="s">
+        <v>246</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>256</v>
+      </c>
+      <c r="G11" s="70" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="5:31" ht="15">
+      <c r="E12" s="71" t="s">
+        <v>248</v>
+      </c>
+      <c r="F12" s="70" t="s">
+        <v>255</v>
+      </c>
+      <c r="G12" s="70" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="5:31" ht="29.25" thickBot="1">
+      <c r="E13" s="71" t="s">
+        <v>258</v>
+      </c>
+      <c r="F13" s="70" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="9" spans="5:31" ht="15">
-      <c r="E9" s="72" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" s="71" t="s">
-        <v>259</v>
-      </c>
-      <c r="G9" s="71" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10" spans="5:31" ht="15">
-      <c r="E10" s="72" t="s">
-        <v>247</v>
-      </c>
-      <c r="F10" s="71" t="s">
-        <v>257</v>
-      </c>
-      <c r="G10" s="71" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="11" spans="5:31" ht="15">
-      <c r="E11" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="F11" s="71" t="s">
-        <v>258</v>
-      </c>
-      <c r="G11" s="71" t="s">
+      <c r="G13" s="70" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="5:31" ht="15">
-      <c r="E12" s="72" t="s">
-        <v>250</v>
-      </c>
-      <c r="F12" s="71" t="s">
-        <v>257</v>
-      </c>
-      <c r="G12" s="71" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="13" spans="5:31" ht="29.25" thickBot="1">
-      <c r="E13" s="72" t="s">
+    <row r="14" spans="5:31" ht="36.6" customHeight="1" thickTop="1" thickBot="1">
+      <c r="E14" s="92" t="s">
+        <v>262</v>
+      </c>
+      <c r="F14" s="92" t="s">
         <v>260</v>
       </c>
-      <c r="F13" s="71" t="s">
-        <v>256</v>
-      </c>
-      <c r="G13" s="71" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="14" spans="5:31" ht="36.6" customHeight="1" thickTop="1" thickBot="1">
-      <c r="E14" s="93" t="s">
-        <v>264</v>
-      </c>
-      <c r="F14" s="93" t="s">
-        <v>262</v>
-      </c>
-      <c r="G14" s="93" t="s">
-        <v>263</v>
+      <c r="G14" s="92" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="5:31" ht="15" thickTop="1"/>
     <row r="16" spans="5:31" ht="15" thickBot="1">
-      <c r="E16" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="F16" s="40" t="s">
+      <c r="E16" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="G16" s="40" t="s">
-        <v>236</v>
-      </c>
-      <c r="H16" s="40" t="s">
+      <c r="F16" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="H16" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="17" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
-      <c r="E17" s="90" t="s">
-        <v>261</v>
-      </c>
-      <c r="F17" s="92">
+      <c r="E17" s="89" t="s">
+        <v>259</v>
+      </c>
+      <c r="F17" s="91">
         <v>0.3</v>
       </c>
-      <c r="G17" s="91">
+      <c r="G17" s="90">
         <f>Tracker!$C$2*Portfolio!F17</f>
         <v>15000000</v>
       </c>
-      <c r="H17" s="97" t="s">
-        <v>288</v>
+      <c r="H17" s="96" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="5:15" ht="15.75" thickTop="1">
-      <c r="E18" s="94" t="s">
+      <c r="E18" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="94">
         <v>0.15</v>
       </c>
-      <c r="G18" s="96">
+      <c r="G18" s="95">
         <v>6000000</v>
       </c>
-      <c r="H18" s="98" t="s">
-        <v>289</v>
+      <c r="H18" s="97" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="5:15" ht="15">
-      <c r="E19" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="F19" s="47">
+      <c r="E19" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="F19" s="46">
         <v>0.1</v>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="47">
         <v>6000000</v>
       </c>
-      <c r="H19" s="99"/>
+      <c r="H19" s="98"/>
     </row>
     <row r="20" spans="5:15" ht="15">
-      <c r="E20" s="40" t="s">
-        <v>232</v>
-      </c>
-      <c r="F20" s="47">
+      <c r="E20" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="F20" s="46">
         <v>0.44</v>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="47">
         <f>Tracker!$C$2*Portfolio!F20</f>
         <v>22000000</v>
       </c>
-      <c r="H20" s="99" t="s">
-        <v>287</v>
+      <c r="H20" s="98" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="5:15" ht="15">
-      <c r="E21" s="94" t="s">
-        <v>234</v>
-      </c>
-      <c r="F21" s="95">
+      <c r="E21" s="93" t="s">
+        <v>232</v>
+      </c>
+      <c r="F21" s="94">
         <f>1-SUM(F17:F20)</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="G21" s="96">
+      <c r="G21" s="95">
         <f>Tracker!$C$2*Portfolio!F21</f>
         <v>500000.00000000047</v>
       </c>
-      <c r="H21" s="98" t="s">
-        <v>290</v>
+      <c r="H21" s="97" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="5:15">
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>271</v>
+      </c>
+      <c r="G23" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="H23" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="I23" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="J23" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="I23" s="40" t="s">
+      <c r="K23" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="J23" s="40" t="s">
+      <c r="L23" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="M23" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="K23" s="40" t="s">
+      <c r="N23" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="L23" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="M23" s="40" t="s">
-        <v>279</v>
-      </c>
-      <c r="N23" s="40" t="s">
-        <v>280</v>
-      </c>
-      <c r="O23" s="40" t="s">
+      <c r="O23" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="24" spans="5:15">
-      <c r="E24" s="87">
+      <c r="E24" s="86">
         <v>46219</v>
       </c>
-      <c r="F24" s="87" t="s">
-        <v>210</v>
-      </c>
-      <c r="G24" s="40" t="s">
+      <c r="F24" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="G24" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="H24" s="88">
+      <c r="H24" s="87">
         <v>926.69817440459997</v>
       </c>
-      <c r="I24" s="48">
+      <c r="I24" s="47">
         <v>3237.3</v>
       </c>
-      <c r="J24" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="K24" s="48">
+      <c r="J24" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="K24" s="47">
         <v>3000000</v>
       </c>
-      <c r="L24" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="M24" s="89" t="e">
+      <c r="L24" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="M24" s="88" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N24" s="110" t="e">
+      <c r="N24" s="109" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O24" s="40"/>
+      <c r="O24" s="39"/>
     </row>
     <row r="25" spans="5:15">
-      <c r="E25" s="87">
+      <c r="E25" s="86">
         <v>46225</v>
       </c>
-      <c r="F25" s="87" t="s">
-        <v>210</v>
-      </c>
-      <c r="G25" s="40" t="s">
+      <c r="F25" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="G25" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="88">
+      <c r="H25" s="87">
         <v>933.47</v>
       </c>
-      <c r="I25" s="48">
+      <c r="I25" s="47">
         <v>3213.78</v>
       </c>
-      <c r="J25" s="102" t="s">
-        <v>210</v>
-      </c>
-      <c r="K25" s="48">
+      <c r="J25" s="101" t="s">
+        <v>210</v>
+      </c>
+      <c r="K25" s="47">
         <v>3000000</v>
       </c>
-      <c r="L25" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="M25" s="89" t="e">
+      <c r="L25" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="M25" s="88" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N25" s="110" t="e">
+      <c r="N25" s="109" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O25" s="40"/>
+      <c r="O25" s="39"/>
     </row>
     <row r="26" spans="5:15" ht="15" thickBot="1">
-      <c r="E26" s="87" t="s">
-        <v>210</v>
-      </c>
-      <c r="F26" s="87">
+      <c r="E26" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="F26" s="86">
         <v>46226</v>
       </c>
-      <c r="G26" s="40" t="s">
+      <c r="G26" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="88">
+      <c r="H26" s="87">
         <v>100</v>
       </c>
-      <c r="I26" s="48">
+      <c r="I26" s="47">
         <v>3237.3</v>
       </c>
-      <c r="J26" s="102">
+      <c r="J26" s="101">
         <v>3257.13</v>
       </c>
-      <c r="K26" s="48">
+      <c r="K26" s="47">
         <f>H26*I26</f>
         <v>323730</v>
       </c>
-      <c r="L26" s="48">
+      <c r="L26" s="47">
         <f>H26*J26</f>
         <v>325713</v>
       </c>
-      <c r="M26" s="89">
+      <c r="M26" s="88">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>1983</v>
       </c>
-      <c r="N26" s="110">
+      <c r="N26" s="109">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>0.6125474932814382</v>
       </c>
-      <c r="O26" s="40"/>
+      <c r="O26" s="39"/>
     </row>
     <row r="27" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
-      <c r="E27" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="F27" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="G27" s="90" t="s">
+      <c r="E27" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="F27" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="G27" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="H27" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="I27" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="J27" s="109" t="s">
-        <v>210</v>
-      </c>
-      <c r="K27" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="L27" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="M27" s="90" t="e">
+      <c r="H27" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="I27" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="J27" s="108" t="s">
+        <v>210</v>
+      </c>
+      <c r="K27" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="L27" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="M27" s="89" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N27" s="111" t="e">
+      <c r="N27" s="110" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O27" s="90"/>
+      <c r="O27" s="89"/>
     </row>
     <row r="28" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
-      <c r="E28" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="F28" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="G28" s="90" t="s">
+      <c r="E28" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="F28" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="G28" s="89" t="s">
+        <v>279</v>
+      </c>
+      <c r="H28" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="I28" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="J28" s="108" t="s">
+        <v>210</v>
+      </c>
+      <c r="K28" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="L28" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="M28" s="89" t="e">
+        <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N28" s="110" t="e">
+        <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O28" s="89"/>
+    </row>
+    <row r="29" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+      <c r="E29" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="F29" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="G29" s="89" t="s">
+        <v>280</v>
+      </c>
+      <c r="H29" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="I29" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="J29" s="108" t="s">
+        <v>210</v>
+      </c>
+      <c r="K29" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="L29" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="M29" s="89" t="e">
+        <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N29" s="110" t="e">
+        <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O29" s="89"/>
+    </row>
+    <row r="30" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+      <c r="E30" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="F30" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="G30" s="89" t="s">
         <v>281</v>
       </c>
-      <c r="H28" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="I28" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="J28" s="109" t="s">
-        <v>210</v>
-      </c>
-      <c r="K28" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="L28" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="M28" s="90" t="e">
+      <c r="H30" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="I30" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="J30" s="108" t="s">
+        <v>210</v>
+      </c>
+      <c r="K30" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="L30" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="M30" s="89" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N28" s="111" t="e">
+      <c r="N30" s="110" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O28" s="90"/>
-    </row>
-    <row r="29" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
-      <c r="E29" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="F29" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="G29" s="90" t="s">
+      <c r="O30" s="89"/>
+    </row>
+    <row r="31" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+      <c r="E31" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="F31" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="G31" s="89" t="s">
         <v>282</v>
       </c>
-      <c r="H29" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="I29" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="J29" s="109" t="s">
-        <v>210</v>
-      </c>
-      <c r="K29" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="L29" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="M29" s="90" t="e">
+      <c r="H31" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="I31" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="J31" s="108" t="s">
+        <v>210</v>
+      </c>
+      <c r="K31" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="L31" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="M31" s="89" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N29" s="111" t="e">
+      <c r="N31" s="110" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="90"/>
-    </row>
-    <row r="30" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
-      <c r="E30" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="F30" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="G30" s="90" t="s">
+      <c r="O31" s="89"/>
+    </row>
+    <row r="32" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+      <c r="E32" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="F32" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="89" t="s">
         <v>283</v>
       </c>
-      <c r="H30" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="I30" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="J30" s="109" t="s">
-        <v>210</v>
-      </c>
-      <c r="K30" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="L30" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="M30" s="90" t="e">
+      <c r="H32" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="I32" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="J32" s="108" t="s">
+        <v>210</v>
+      </c>
+      <c r="K32" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="L32" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="M32" s="89" t="e">
         <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N30" s="111" t="e">
+      <c r="N32" s="110" t="e">
         <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O30" s="90"/>
-    </row>
-    <row r="31" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
-      <c r="E31" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="F31" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="G31" s="90" t="s">
-        <v>284</v>
-      </c>
-      <c r="H31" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="I31" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="J31" s="109" t="s">
-        <v>210</v>
-      </c>
-      <c r="K31" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="L31" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="M31" s="90" t="e">
-        <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N31" s="111" t="e">
-        <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O31" s="90"/>
-    </row>
-    <row r="32" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
-      <c r="E32" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="F32" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="G32" s="90" t="s">
-        <v>285</v>
-      </c>
-      <c r="H32" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="I32" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="J32" s="109" t="s">
-        <v>210</v>
-      </c>
-      <c r="K32" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="L32" s="90" t="s">
-        <v>210</v>
-      </c>
-      <c r="M32" s="90" t="e">
-        <f>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N32" s="111" t="e">
-        <f>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O32" s="90"/>
+      <c r="O32" s="89"/>
     </row>
     <row r="33" ht="15" thickTop="1"/>
   </sheetData>
@@ -9479,7 +9512,7 @@
     <mergeCell ref="AD5:AE5"/>
   </mergeCells>
   <conditionalFormatting sqref="F17:F21">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>SUM($F$17:$F$21)&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Management/Finantial Planning.xlsx
+++ b/Management/Finantial Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aciww-my.sharepoint.com/personal/daniel_lozanobarrero_aciworldwide_com/Documents/Documents/My-Notes/Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3468EE1-EAF2-41EE-A4EB-47E406BF02A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{E3468EE1-EAF2-41EE-A4EB-47E406BF02A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B63637E5-8527-445F-B700-C99C97A8DB8A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{F8FCC151-5DC7-4472-A863-0C0A531A258D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{F8FCC151-5DC7-4472-A863-0C0A531A258D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -864,9 +861,6 @@
     <t>The 16nd every 3 months</t>
   </si>
   <si>
-    <t>Cash out on 16.10.2026</t>
-  </si>
-  <si>
     <t>Date Bought</t>
   </si>
   <si>
@@ -970,6 +964,9 @@
   </si>
   <si>
     <t>Monthly Remaining</t>
+  </si>
+  <si>
+    <t>Cash out on 17.01.2027</t>
   </si>
 </sst>
 </file>
@@ -984,12 +981,12 @@
     <numFmt numFmtId="168" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="#,##0.00\ [$COP]"/>
-    <numFmt numFmtId="173" formatCode="\+\ #.##0\ \C\O\P;\-\ #.##0\ \C\O\P;0\ \C\O\P"/>
-    <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
-    <numFmt numFmtId="175" formatCode="mmmm\ yyyy"/>
+    <numFmt numFmtId="171" formatCode="#,##0.00\ [$COP]"/>
+    <numFmt numFmtId="172" formatCode="\+\ #.##0\ \C\O\P;\-\ #.##0\ \C\O\P;0\ \C\O\P"/>
+    <numFmt numFmtId="173" formatCode="[$COP]\ #,##0.00"/>
+    <numFmt numFmtId="174" formatCode="mmmm\ yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1507,7 +1504,7 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1585,7 +1582,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1706,13 +1703,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="26" xfId="5" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
@@ -1727,7 +1724,7 @@
     <xf numFmtId="9" fontId="8" fillId="13" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="13" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="13" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="26" xfId="5" applyFont="1" applyAlignment="1">
@@ -1743,20 +1740,20 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="4" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="4" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1765,9 +1762,13 @@
     <xf numFmtId="10" fontId="4" fillId="14" borderId="26" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1801,16 +1802,21 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Check Cell" xfId="5" builtinId="23"/>
@@ -1829,10 +1835,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1840,23 +1842,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="173" formatCode="\+\ #.##0\ \C\O\P;\-\ #.##0\ \C\O\P;0\ \C\O\P"/>
+      <numFmt numFmtId="172" formatCode="\+\ #.##0\ \C\O\P;\-\ #.##0\ \C\O\P;0\ \C\O\P"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="172" formatCode="#,##0.00\ [$COP]"/>
+      <numFmt numFmtId="171" formatCode="#,##0.00\ [$COP]"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="172" formatCode="#,##0.00\ [$COP]"/>
+      <numFmt numFmtId="171" formatCode="#,##0.00\ [$COP]"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
+      <numFmt numFmtId="173" formatCode="[$COP]\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="172" formatCode="#,##0.00\ [$COP]"/>
+      <numFmt numFmtId="171" formatCode="#,##0.00\ [$COP]"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1934,7 +1936,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="172" formatCode="#,##0.00\ [$COP]"/>
+      <numFmt numFmtId="171" formatCode="#,##0.00\ [$COP]"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1963,257 +1965,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="173" formatCode="[$COP]\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="175" formatCode="mmmm\ yyyy"/>
+      <numFmt numFmtId="174" formatCode="mmmm\ yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2226,11 +1982,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
+      <numFmt numFmtId="173" formatCode="[$COP]\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="175" formatCode="mmmm\ yyyy"/>
+      <numFmt numFmtId="174" formatCode="mmmm\ yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2254,7 +2010,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="174" formatCode="[$COP]\ #,##0.00"/>
+      <numFmt numFmtId="173" formatCode="[$COP]\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2500,6 +2256,10 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2620,6 +2380,252 @@
         <b/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3063,6 +3069,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3070,7 +3077,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -3303,7 +3309,7 @@
                   <c:v>1111029.9400000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>171182.9114285782</c:v>
+                  <c:v>156982.9114285782</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>-162269.05999999959</c:v>
@@ -3528,6 +3534,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3535,7 +3542,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -4191,6 +4197,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4198,7 +4205,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5984,10 +5990,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DatosExternos_1" connectionId="1" xr16:uid="{A1246213-22CC-41A1-BFB9-41CA85A97729}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="3">
@@ -6000,54 +6002,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D12B85FF-207C-4D5B-9D71-17F000E82BA2}" name="Tabla1" displayName="Tabla1" ref="G7:M18" totalsRowShown="0" headerRowDxfId="79" headerRowBorderDxfId="78" tableBorderDxfId="77" totalsRowBorderDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D12B85FF-207C-4D5B-9D71-17F000E82BA2}" name="Tabla1" displayName="Tabla1" ref="G7:M18" totalsRowShown="0" headerRowDxfId="63" headerRowBorderDxfId="62" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <autoFilter ref="G7:M18" xr:uid="{D12B85FF-207C-4D5B-9D71-17F000E82BA2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{2B7E95C1-DECA-4AEE-BDEF-3A0B4A1FF392}" name="Expense" dataDxfId="75"/>
-    <tableColumn id="2" xr3:uid="{3BF96C8D-03B0-41B0-B988-8791620F79BF}" name="Unit Cost" dataDxfId="74"/>
+    <tableColumn id="1" xr3:uid="{2B7E95C1-DECA-4AEE-BDEF-3A0B4A1FF392}" name="Expense" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{3BF96C8D-03B0-41B0-B988-8791620F79BF}" name="Unit Cost" dataDxfId="58"/>
     <tableColumn id="3" xr3:uid="{3065075C-2E97-4560-8473-35A37808B5F3}" name="Times/Month"/>
-    <tableColumn id="4" xr3:uid="{0E68B4B4-0092-46B6-9598-F0521EA5EC7E}" name="Total Cost" dataDxfId="73">
+    <tableColumn id="4" xr3:uid="{0E68B4B4-0092-46B6-9598-F0521EA5EC7E}" name="Total Cost" dataDxfId="57">
       <calculatedColumnFormula>H8*I8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{10738E51-758B-45FB-9DD0-02C14BC2D40D}" name="After Benefits" dataDxfId="72"/>
-    <tableColumn id="6" xr3:uid="{07D186C7-DB64-4AC7-BA70-8DC5B9E3A51B}" name="Pay Date (day)" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{8B8904EF-9CF0-47D9-8BCB-78EF6DD7F607}" name="Additional Information" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{10738E51-758B-45FB-9DD0-02C14BC2D40D}" name="After Benefits" dataDxfId="56"/>
+    <tableColumn id="6" xr3:uid="{07D186C7-DB64-4AC7-BA70-8DC5B9E3A51B}" name="Pay Date (day)" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{8B8904EF-9CF0-47D9-8BCB-78EF6DD7F607}" name="Additional Information" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}" name="Table7" displayName="Table7" ref="E8:G14" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}" name="Table7" displayName="Table7" ref="E8:G14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="E8:G14" xr:uid="{56BEBB7D-CF47-44B7-B205-1CF0E218C6CA}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{05264107-3C50-4DC4-BA66-3C598C57D362}" name="Condition" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{4F494527-B966-4283-AC8D-DDFC53922A3A}" name="Action" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{A8687214-DFD3-4202-A740-25119BF98217}" name="% Adjusted" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{05264107-3C50-4DC4-BA66-3C598C57D362}" name="Condition" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{4F494527-B966-4283-AC8D-DDFC53922A3A}" name="Action" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{A8687214-DFD3-4202-A740-25119BF98217}" name="% Adjusted" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}" name="Table10" displayName="Table10" ref="E23:O32" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}" name="Table10" displayName="Table10" ref="E23:O32" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="E23:O32" xr:uid="{73D22C32-1C4D-4F00-97CD-6D2B89C03A8F}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{EF8D02AC-323D-45AB-AE15-91832BDC7B4E}" name="Date Bought" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{712A0457-F103-4A5F-89A3-F38940B6301F}" name="Date Sold" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{8B72E438-7296-4BE9-B114-652C18C0973F}" name="Asset" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{C9EB17C7-CF17-4BB1-8390-4A0AA329B909}" name="Units" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{38A379BB-56A1-4C91-8A79-E09D76997328}" name="Price Buy" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{70D6BA55-3422-446B-A79B-9ED0B67E93BD}" name="Price Sell" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{D264BB00-77B0-482C-925B-C8BD072B81A0}" name="Total Invested (COP)" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{9369D078-2888-4CE1-919F-E9A0C05D615C}" name="Total Value" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{313DF1E8-730D-4C1D-BB28-A01F2D131415}" name="Gain/Loss (COP)" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{EF8D02AC-323D-45AB-AE15-91832BDC7B4E}" name="Date Bought" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{712A0457-F103-4A5F-89A3-F38940B6301F}" name="Date Sold" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{8B72E438-7296-4BE9-B114-652C18C0973F}" name="Asset" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C9EB17C7-CF17-4BB1-8390-4A0AA329B909}" name="Units" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{38A379BB-56A1-4C91-8A79-E09D76997328}" name="Price Buy" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{70D6BA55-3422-446B-A79B-9ED0B67E93BD}" name="Price Sell" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{D264BB00-77B0-482C-925B-C8BD072B81A0}" name="Total Invested (COP)" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{9369D078-2888-4CE1-919F-E9A0C05D615C}" name="Total Value" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{313DF1E8-730D-4C1D-BB28-A01F2D131415}" name="Gain/Loss (COP)" dataDxfId="3">
       <calculatedColumnFormula>Table10[[#This Row],[Total Value]]-Table10[[#This Row],[Total Invested (COP)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{CD1E921A-1374-4429-89D9-1676BA8642FB}" name="% Return" dataDxfId="3" dataCellStyle="Percent">
+    <tableColumn id="10" xr3:uid="{CD1E921A-1374-4429-89D9-1676BA8642FB}" name="% Return" dataDxfId="2" dataCellStyle="Percent">
       <calculatedColumnFormula>Table10[[#This Row],[Gain/Loss (COP)]]*100/Table10[[#This Row],[Total Invested (COP)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{36B25BAF-3792-45C1-AE34-3EDA3274070F}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{36B25BAF-3792-45C1-AE34-3EDA3274070F}" name="Notes" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6065,17 +6067,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{66334954-402F-42CF-93F5-A72360F2D070}" name="Tabla4" displayName="Tabla4" ref="C32:F34" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{66334954-402F-42CF-93F5-A72360F2D070}" name="Tabla4" displayName="Tabla4" ref="C32:F34" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52" tableBorderDxfId="51">
   <autoFilter ref="C32:F34" xr:uid="{66334954-402F-42CF-93F5-A72360F2D070}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7008F60E-B49B-4429-A785-DABF540532D2}" name=" " dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{7AA8370E-90CC-4DED-878E-C49D41DF4160}" name="Goal" dataDxfId="66">
+    <tableColumn id="1" xr3:uid="{7008F60E-B49B-4429-A785-DABF540532D2}" name=" " dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{7AA8370E-90CC-4DED-878E-C49D41DF4160}" name="Goal" dataDxfId="49">
       <calculatedColumnFormula>24000*D27</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F5EB769A-6764-44FD-A678-979868FCC64D}" name="Time till Germany (from 05.08.2025) [months]" dataDxfId="65">
+    <tableColumn id="3" xr3:uid="{F5EB769A-6764-44FD-A678-979868FCC64D}" name="Time till Germany (from 05.08.2025) [months]" dataDxfId="48">
       <calculatedColumnFormula>_xlfn.CEILING.MATH((D33-$D$23-$D$5+'Another Expenses'!G2)/$D$21)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{458996D1-0FCE-433A-A2D6-31A1409ED603}" name="Expected Date" dataDxfId="64">
+    <tableColumn id="4" xr3:uid="{458996D1-0FCE-433A-A2D6-31A1409ED603}" name="Expected Date" dataDxfId="47">
       <calculatedColumnFormula>EDATE(DATE(YEAR($B$2), MONTH($B$2), $E$8),E33)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6084,92 +6086,92 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EE785617-0173-4EE0-B271-24F483A6FC5D}" name="Table8" displayName="Table8" ref="C7:E14" totalsRowShown="0" headerRowDxfId="63" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60" totalsRowBorderDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EE785617-0173-4EE0-B271-24F483A6FC5D}" name="Table8" displayName="Table8" ref="C7:E14" totalsRowShown="0" headerRowDxfId="46" dataDxfId="44" headerRowBorderDxfId="45" tableBorderDxfId="43" totalsRowBorderDxfId="42">
   <autoFilter ref="C7:E14" xr:uid="{EE785617-0173-4EE0-B271-24F483A6FC5D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B8D1B94D-65F4-44AF-BB8A-B3944537254D}" name="Income" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{70B9C461-0699-4DD9-88DF-A4BC104B1E84}" name="Unit Cost" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{0F428774-E799-4A75-AF01-1FEB7C7BB60B}" name="Pay Date" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{B8D1B94D-65F4-44AF-BB8A-B3944537254D}" name="Income" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{70B9C461-0699-4DD9-88DF-A4BC104B1E84}" name="Unit Cost" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{0F428774-E799-4A75-AF01-1FEB7C7BB60B}" name="Pay Date" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{234B9209-31CF-4CB4-B91D-DB56E5076B02}" name="Table9" displayName="Table9" ref="B5:F65" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{234B9209-31CF-4CB4-B91D-DB56E5076B02}" name="Table9" displayName="Table9" ref="B5:F65" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="B5:F65" xr:uid="{234B9209-31CF-4CB4-B91D-DB56E5076B02}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{71E1B1C3-7B4F-4332-B720-63A44972040A}" name="Date" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{92837B89-3057-4978-9098-533DE8C88637}" name="General Balance" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{A4EBB52D-F610-40EB-8029-0CC1E5ACB00B}" name="Account Balance" dataDxfId="51">
+    <tableColumn id="1" xr3:uid="{71E1B1C3-7B4F-4332-B720-63A44972040A}" name="Date" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{92837B89-3057-4978-9098-533DE8C88637}" name="General Balance" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{A4EBB52D-F610-40EB-8029-0CC1E5ACB00B}" name="Account Balance" dataDxfId="34">
       <calculatedColumnFormula>RAND()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{198D9105-C07E-44D2-8F61-8F9CABBAD850}" name="Gain/Loss" dataDxfId="50">
+    <tableColumn id="3" xr3:uid="{198D9105-C07E-44D2-8F61-8F9CABBAD850}" name="Gain/Loss" dataDxfId="33">
       <calculatedColumnFormula>Table9[[#This Row],[Account Balance]]-D5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{4C793EB9-7B7D-4BF8-8BFC-64EEC368D854}" name="Difference from Expected Net" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{4C793EB9-7B7D-4BF8-8BFC-64EEC368D854}" name="Difference from Expected Net" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{1E999F4D-13BA-4961-9CC8-4DF65A7B1CEA}" name="Table11" displayName="Table11" ref="H6:I12" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{1E999F4D-13BA-4961-9CC8-4DF65A7B1CEA}" name="Table11" displayName="Table11" ref="H6:I12" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="H6:I12" xr:uid="{1E999F4D-13BA-4961-9CC8-4DF65A7B1CEA}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5E82BFD3-6D74-43F6-913D-96694AEF7A3E}" name="Date" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{710C1C2F-6F23-4153-86B6-2D191197A156}" name="General Balance" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{5E82BFD3-6D74-43F6-913D-96694AEF7A3E}" name="Date" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{710C1C2F-6F23-4153-86B6-2D191197A156}" name="General Balance" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3DBCF91F-3FBC-4548-AAE4-34CB784C3CED}" name="Table1113" displayName="Table1113" ref="H15:I21" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3DBCF91F-3FBC-4548-AAE4-34CB784C3CED}" name="Table1113" displayName="Table1113" ref="H15:I21" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="H15:I21" xr:uid="{3DBCF91F-3FBC-4548-AAE4-34CB784C3CED}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E16B0B05-832D-453D-BB01-1648C2BB6952}" name="Date" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{1165A24D-75E5-4E1D-A756-DA4346B52F4F}" name="Difference from Expected Net" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{E16B0B05-832D-453D-BB01-1648C2BB6952}" name="Date" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{1165A24D-75E5-4E1D-A756-DA4346B52F4F}" name="Difference from Expected Net" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BA8F843C-C6A6-4B02-9256-7DFE12B32092}" name="Table5" displayName="Table5" ref="C7:F27" totalsRowShown="0" headerRowDxfId="40" headerRowBorderDxfId="39" tableBorderDxfId="38" totalsRowBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BA8F843C-C6A6-4B02-9256-7DFE12B32092}" name="Table5" displayName="Table5" ref="C7:F27" totalsRowShown="0" headerRowDxfId="79" headerRowBorderDxfId="78" tableBorderDxfId="77" totalsRowBorderDxfId="76">
   <autoFilter ref="C7:F27" xr:uid="{BA8F843C-C6A6-4B02-9256-7DFE12B32092}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A7222D0C-F15D-4B37-8493-05007AD6DC97}" name="Description" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{9873BCE0-3AFD-4035-A4F4-DDE3995CE8FF}" name="Incoming" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{73BD4001-1956-4334-A204-BB3321930FA2}" name="Outcoming" dataDxfId="34" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{6189F130-2A64-446B-8A16-FBD00F7771AC}" name="Notes" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{A7222D0C-F15D-4B37-8493-05007AD6DC97}" name="Description" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{9873BCE0-3AFD-4035-A4F4-DDE3995CE8FF}" name="Incoming" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{73BD4001-1956-4334-A204-BB3321930FA2}" name="Outcoming" dataDxfId="73" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{6189F130-2A64-446B-8A16-FBD00F7771AC}" name="Notes" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F7CD279B-A932-4C0F-8D8F-D149C918CAA1}" name="Table6" displayName="Table6" ref="H7:J27" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F7CD279B-A932-4C0F-8D8F-D149C918CAA1}" name="Table6" displayName="Table6" ref="H7:J27" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" tableBorderDxfId="68" totalsRowBorderDxfId="67">
   <autoFilter ref="H7:J27" xr:uid="{F7CD279B-A932-4C0F-8D8F-D149C918CAA1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{516245D1-012B-4614-97CB-8E191CA93F41}" name="Name" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{41E5D36C-6A21-4BF1-972B-BA27C450EDE2}" name="Amount" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{8ADFD3E1-24FE-45CE-8A72-696379253170}" name="Notes" dataDxfId="25" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{516245D1-012B-4614-97CB-8E191CA93F41}" name="Name" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{41E5D36C-6A21-4BF1-972B-BA27C450EDE2}" name="Amount" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{8ADFD3E1-24FE-45CE-8A72-696379253170}" name="Notes" dataDxfId="64" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}" name="Table3" displayName="Table3" ref="E16:H21" totalsRowShown="0" headerRowDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}" name="Table3" displayName="Table3" ref="E16:H21" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="E16:H21" xr:uid="{36A5E943-B17C-4ECF-8BB7-30335A174A27}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{88178FBB-1C68-4443-9D29-711B96CC8F3C}" name="Investment Type" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{AF13EBFA-AD22-4799-B232-349084129FC2}" name="Percentage" dataDxfId="22" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{06249914-8982-4D40-BF2A-A24479258B7E}" name="Current Amount" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{88178FBB-1C68-4443-9D29-711B96CC8F3C}" name="Investment Type" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{AF13EBFA-AD22-4799-B232-349084129FC2}" name="Percentage" dataDxfId="21" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{06249914-8982-4D40-BF2A-A24479258B7E}" name="Current Amount" dataDxfId="20">
       <calculatedColumnFormula>Tracker!$C$2*Portfolio!F17</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BE746FA0-4394-410B-BFFB-E4580C3454EF}" name="Notes" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{BE746FA0-4394-410B-BFFB-E4580C3454EF}" name="Notes" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6494,23 +6496,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0D8A61-82F4-4CC6-B552-F68414C6EAB4}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:M1048575"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>196</v>
       </c>
@@ -6518,7 +6520,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>8</v>
       </c>
@@ -6527,8 +6529,8 @@
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1"/>
-    <row r="5" spans="1:13" ht="15.75" thickBot="1">
+    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="14" t="s">
         <v>264</v>
       </c>
@@ -6541,13 +6543,13 @@
       </c>
       <c r="H5" s="13">
         <f>SUM(K8:K18)</f>
-        <v>1120968.5714285714</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>1135168.5714285714</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:13" ht="15">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" s="33" t="s">
         <v>214</v>
       </c>
@@ -6579,7 +6581,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C8" s="40" t="s">
         <v>5</v>
       </c>
@@ -6610,11 +6612,11 @@
       <c r="L8" s="28">
         <v>5</v>
       </c>
-      <c r="M8" s="125" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="M8" s="112" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C9" s="40" t="s">
         <v>202</v>
       </c>
@@ -6626,31 +6628,31 @@
         <v>267</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H9" s="5">
         <v>3550</v>
       </c>
       <c r="I9" s="6">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="0"/>
-        <v>42600</v>
+        <v>56800</v>
       </c>
       <c r="K9" s="9">
         <f t="shared" ref="K9:K15" si="1">J9</f>
-        <v>42600</v>
+        <v>56800</v>
       </c>
       <c r="L9" s="30">
         <f ca="1">A1048575+_xlfn.CEILING.MATH((TODAY()-A1048575)/21, 1)*21</f>
         <v>46321</v>
       </c>
-      <c r="M9" s="125" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" thickBot="1">
+      <c r="M9" s="112" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="66" t="s">
         <v>263</v>
       </c>
@@ -6662,7 +6664,7 @@
         <v>268</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H10" s="5">
         <v>15000</v>
@@ -6679,9 +6681,9 @@
         <v>120000</v>
       </c>
       <c r="L10" s="28"/>
-      <c r="M10" s="125"/>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="M10" s="112"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C11" s="82" t="s">
         <v>0</v>
       </c>
@@ -6693,7 +6695,7 @@
         <v>219</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H11" s="5">
         <v>6400</v>
@@ -6713,11 +6715,11 @@
       <c r="L11" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="M11" s="125" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="M11" s="112" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C12" s="77" t="s">
         <v>17</v>
       </c>
@@ -6748,11 +6750,11 @@
       <c r="L12" s="28">
         <v>23</v>
       </c>
-      <c r="M12" s="125" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="M12" s="112" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C13" s="79" t="s">
         <v>14</v>
       </c>
@@ -6783,13 +6785,13 @@
       <c r="L13" s="28">
         <v>25</v>
       </c>
-      <c r="M13" s="125" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="M13" s="112" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C14" s="81" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D14" s="72">
         <f>D13-J17-J18</f>
@@ -6819,11 +6821,11 @@
       <c r="L14" s="28">
         <v>25</v>
       </c>
-      <c r="M14" s="125" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="M14" s="112" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G15" s="40" t="s">
         <v>226</v>
       </c>
@@ -6844,11 +6846,11 @@
       <c r="L15" s="28">
         <v>25</v>
       </c>
-      <c r="M15" s="125" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="M15" s="112" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G16" s="40" t="s">
         <v>231</v>
       </c>
@@ -6867,9 +6869,9 @@
         <v>30000</v>
       </c>
       <c r="L16" s="28"/>
-      <c r="M16" s="125"/>
-    </row>
-    <row r="17" spans="3:13">
+      <c r="M16" s="112"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
       <c r="G17" s="41" t="s">
         <v>6</v>
       </c>
@@ -6889,11 +6891,11 @@
       <c r="L17" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="M17" s="124" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13">
+      <c r="M17" s="111" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
       <c r="G18" s="41" t="s">
         <v>15</v>
       </c>
@@ -6915,27 +6917,27 @@
       <c r="L18" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="M18" s="124" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13">
-      <c r="M19" s="126"/>
-    </row>
-    <row r="20" spans="3:13" ht="15" thickBot="1">
+      <c r="M18" s="111" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M19" s="113"/>
+    </row>
+    <row r="20" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J20" s="8"/>
     </row>
-    <row r="21" spans="3:13" ht="15.75" thickBot="1">
+    <row r="21" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" s="14" t="s">
         <v>266</v>
       </c>
       <c r="D21" s="12">
         <f>D5-H5</f>
-        <v>4412737.9414285719</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" ht="15" thickBot="1"/>
-    <row r="23" spans="3:13" ht="15.75" thickBot="1">
+        <v>4398537.9414285719</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C23" s="4" t="str">
         <f>"Savings on " &amp; TEXT(B2, "dd.MM.yyyy")</f>
         <v>Savings on 21.12.2025</v>
@@ -6951,20 +6953,20 @@
         <v>470000</v>
       </c>
     </row>
-    <row r="24" spans="3:13">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C24" s="27" t="s">
         <v>206</v>
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="3:13">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D25" s="1"/>
       <c r="J25" s="1">
         <f>SUM(J9:J11)</f>
-        <v>213800</v>
-      </c>
-    </row>
-    <row r="26" spans="3:13" ht="15" thickBot="1">
+        <v>228000</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -6976,7 +6978,7 @@
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
     </row>
-    <row r="28" spans="3:13">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C28" s="4" t="s">
         <v>63</v>
       </c>
@@ -6985,7 +6987,7 @@
         <v>3703.7037037037035</v>
       </c>
     </row>
-    <row r="29" spans="3:13">
+    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C29" s="4" t="s">
         <v>20</v>
       </c>
@@ -6994,10 +6996,10 @@
         <v>3194.8881789137376</v>
       </c>
     </row>
-    <row r="31" spans="3:13" ht="15">
+    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C31" s="15"/>
     </row>
-    <row r="32" spans="3:13" ht="15">
+    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C32" s="18" t="s">
         <v>197</v>
       </c>
@@ -7011,7 +7013,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="15">
+    <row r="33" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C33" s="19" t="s">
         <v>198</v>
       </c>
@@ -7028,7 +7030,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="15">
+    <row r="34" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C34" s="19" t="s">
         <v>199</v>
       </c>
@@ -7045,7 +7047,7 @@
         <v>46320</v>
       </c>
     </row>
-    <row r="1048575" spans="1:1">
+    <row r="1048575" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1048575" s="31">
         <v>46048</v>
       </c>
@@ -7064,48 +7066,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8712021-9BAC-49DD-9632-A9B86C4FE255}">
   <dimension ref="B1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.75" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1"/>
-    <row r="2" spans="2:9" ht="15.75" thickBot="1">
+    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="104" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C2" s="105">
         <v>50000000</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="15">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C5" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="F5" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="D5" s="39" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>292</v>
-      </c>
-      <c r="F5" s="39" t="s">
+      <c r="H5" s="125" t="s">
         <v>294</v>
       </c>
-      <c r="H5" s="111" t="s">
-        <v>295</v>
-      </c>
-      <c r="I5" s="111"/>
-    </row>
-    <row r="6" spans="2:9" ht="15">
+      <c r="I5" s="125"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="86">
         <v>46023</v>
       </c>
@@ -7118,19 +7120,19 @@
         <v>27037512.039999999</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H6" s="103" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I6" s="103" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="86">
         <f>EDATE(B6,1)</f>
         <v>46054</v>
@@ -7160,7 +7162,7 @@
         <v>55912013.149999999</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="86">
         <f t="shared" ref="B8:B65" si="0">EDATE(B7,1)</f>
         <v>46082</v>
@@ -7190,7 +7192,7 @@
         <v>61491091.960000001</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="86">
         <f t="shared" si="0"/>
         <v>46113</v>
@@ -7220,7 +7222,7 @@
         <v>64900000</v>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="86">
         <f t="shared" si="0"/>
         <v>46143</v>
@@ -7250,7 +7252,7 @@
         <v>65265421.539999999</v>
       </c>
     </row>
-    <row r="11" spans="2:9">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="86">
         <f t="shared" si="0"/>
         <v>46174</v>
@@ -7280,7 +7282,7 @@
         <v>69506976.569999993</v>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="86">
         <f t="shared" si="0"/>
         <v>46204</v>
@@ -7310,7 +7312,7 @@
         <v>74189383.569999993</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" s="86">
         <f t="shared" si="0"/>
         <v>46235</v>
@@ -7331,7 +7333,7 @@
         <v>1111029.9400000004</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="15">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14" s="86">
         <f t="shared" si="0"/>
         <v>46266</v>
@@ -7349,14 +7351,14 @@
       </c>
       <c r="F14" s="101">
         <f>Main!D21-E14</f>
-        <v>171182.9114285782</v>
-      </c>
-      <c r="H14" s="111" t="s">
-        <v>296</v>
-      </c>
-      <c r="I14" s="111"/>
-    </row>
-    <row r="15" spans="2:9" ht="15">
+        <v>156982.9114285782</v>
+      </c>
+      <c r="H14" s="125" t="s">
+        <v>295</v>
+      </c>
+      <c r="I14" s="125"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="86">
         <f t="shared" si="0"/>
         <v>46296</v>
@@ -7377,13 +7379,13 @@
         <v>-162269.05999999959</v>
       </c>
       <c r="H15" s="103" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I15" s="103" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="86">
         <f t="shared" si="0"/>
         <v>46327</v>
@@ -7411,7 +7413,7 @@
         <v>1398761.5899999989</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="86">
         <f t="shared" si="0"/>
         <v>46357</v>
@@ -7439,7 +7441,7 @@
         <v>-1058940.870000002</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="86">
         <f t="shared" si="0"/>
         <v>46388</v>
@@ -7467,7 +7469,7 @@
         <v>1111229.9000000013</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="86">
         <f t="shared" si="0"/>
         <v>46419</v>
@@ -7495,7 +7497,7 @@
         <v>1111029.9400000004</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="86">
         <f t="shared" si="0"/>
         <v>46447</v>
@@ -7520,10 +7522,10 @@
       </c>
       <c r="I20" s="101">
         <f ca="1">INDEX(Table9[Difference from Expected Net],MATCH(EOMONTH(TODAY(),-2)+1,Table9[Date],1))</f>
-        <v>171182.9114285782</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9">
+        <v>156982.9114285782</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="86">
         <f t="shared" si="0"/>
         <v>46478</v>
@@ -7551,7 +7553,7 @@
         <v>-162269.05999999959</v>
       </c>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="86">
         <f t="shared" si="0"/>
         <v>46508</v>
@@ -7571,7 +7573,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="2:9">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="86">
         <f t="shared" si="0"/>
         <v>46539</v>
@@ -7591,7 +7593,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="2:9">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="86">
         <f t="shared" si="0"/>
         <v>46569</v>
@@ -7611,7 +7613,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="2:9">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="86">
         <f t="shared" si="0"/>
         <v>46600</v>
@@ -7631,7 +7633,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="2:9">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="86">
         <f t="shared" si="0"/>
         <v>46631</v>
@@ -7651,7 +7653,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="2:9">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="86">
         <f t="shared" si="0"/>
         <v>46661</v>
@@ -7671,7 +7673,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="2:9">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="86">
         <f t="shared" si="0"/>
         <v>46692</v>
@@ -7691,7 +7693,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="2:9">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="86">
         <f t="shared" si="0"/>
         <v>46722</v>
@@ -7711,7 +7713,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="2:9">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="86">
         <f t="shared" si="0"/>
         <v>46753</v>
@@ -7731,7 +7733,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="2:9">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="86">
         <f t="shared" si="0"/>
         <v>46784</v>
@@ -7751,7 +7753,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="2:9">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="86">
         <f t="shared" si="0"/>
         <v>46813</v>
@@ -7771,7 +7773,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="86">
         <f t="shared" si="0"/>
         <v>46844</v>
@@ -7791,7 +7793,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="86">
         <f t="shared" si="0"/>
         <v>46874</v>
@@ -7811,7 +7813,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="86">
         <f t="shared" si="0"/>
         <v>46905</v>
@@ -7831,7 +7833,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="86">
         <f t="shared" si="0"/>
         <v>46935</v>
@@ -7851,7 +7853,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="86">
         <f t="shared" si="0"/>
         <v>46966</v>
@@ -7871,7 +7873,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="86">
         <f t="shared" si="0"/>
         <v>46997</v>
@@ -7891,7 +7893,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="86">
         <f t="shared" si="0"/>
         <v>47027</v>
@@ -7911,7 +7913,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="86">
         <f t="shared" si="0"/>
         <v>47058</v>
@@ -7931,7 +7933,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="86">
         <f t="shared" si="0"/>
         <v>47088</v>
@@ -7951,7 +7953,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="42" spans="2:6">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="86">
         <f t="shared" si="0"/>
         <v>47119</v>
@@ -7971,7 +7973,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="86">
         <f t="shared" si="0"/>
         <v>47150</v>
@@ -7991,7 +7993,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="86">
         <f t="shared" si="0"/>
         <v>47178</v>
@@ -8011,7 +8013,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="86">
         <f t="shared" si="0"/>
         <v>47209</v>
@@ -8031,7 +8033,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="86">
         <f t="shared" si="0"/>
         <v>47239</v>
@@ -8051,7 +8053,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="47" spans="2:6">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="86">
         <f t="shared" si="0"/>
         <v>47270</v>
@@ -8071,7 +8073,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="86">
         <f t="shared" si="0"/>
         <v>47300</v>
@@ -8091,7 +8093,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="86">
         <f t="shared" si="0"/>
         <v>47331</v>
@@ -8111,7 +8113,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="86">
         <f t="shared" si="0"/>
         <v>47362</v>
@@ -8131,7 +8133,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="86">
         <f t="shared" si="0"/>
         <v>47392</v>
@@ -8151,7 +8153,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="86">
         <f t="shared" si="0"/>
         <v>47423</v>
@@ -8171,7 +8173,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="86">
         <f t="shared" si="0"/>
         <v>47453</v>
@@ -8191,7 +8193,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="86">
         <f t="shared" si="0"/>
         <v>47484</v>
@@ -8211,7 +8213,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="86">
         <f t="shared" si="0"/>
         <v>47515</v>
@@ -8231,7 +8233,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="86">
         <f t="shared" si="0"/>
         <v>47543</v>
@@ -8251,7 +8253,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="86">
         <f t="shared" si="0"/>
         <v>47574</v>
@@ -8271,7 +8273,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="86">
         <f t="shared" si="0"/>
         <v>47604</v>
@@ -8291,7 +8293,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="59" spans="2:6">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="86">
         <f t="shared" si="0"/>
         <v>47635</v>
@@ -8311,7 +8313,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="60" spans="2:6">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="86">
         <f t="shared" si="0"/>
         <v>47665</v>
@@ -8331,7 +8333,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B61" s="86">
         <f t="shared" si="0"/>
         <v>47696</v>
@@ -8351,7 +8353,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" s="86">
         <f t="shared" si="0"/>
         <v>47727</v>
@@ -8371,7 +8373,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="86">
         <f t="shared" si="0"/>
         <v>47757</v>
@@ -8391,7 +8393,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="86">
         <f t="shared" si="0"/>
         <v>47788</v>
@@ -8411,7 +8413,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" s="86">
         <f t="shared" si="0"/>
         <v>47818</v>
@@ -8451,19 +8453,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E074D57D-0BB2-4D51-BFA3-6687E8A03A91}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="C1:G19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="27.25" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.375" style="45" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.21875" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:7">
+    <row r="1" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="3:7">
+    <row r="2" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C2" s="42" t="s">
         <v>212</v>
       </c>
@@ -8479,7 +8481,7 @@
         <v>12031799.635782748</v>
       </c>
     </row>
-    <row r="3" spans="3:7">
+    <row r="3" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C3" s="42" t="s">
         <v>218</v>
       </c>
@@ -8487,7 +8489,7 @@
         <v>490000</v>
       </c>
     </row>
-    <row r="4" spans="3:7">
+    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C4" s="44" t="s">
         <v>9</v>
       </c>
@@ -8496,7 +8498,7 @@
       </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="3:7">
+    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C5" s="42" t="s">
         <v>184</v>
       </c>
@@ -8505,7 +8507,7 @@
         <v>319488.81789137376</v>
       </c>
     </row>
-    <row r="6" spans="3:7">
+    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C6" s="42" t="s">
         <v>187</v>
       </c>
@@ -8513,7 +8515,7 @@
         <v>234220</v>
       </c>
     </row>
-    <row r="7" spans="3:7">
+    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C7" s="42" t="s">
         <v>229</v>
       </c>
@@ -8521,7 +8523,7 @@
         <v>14602</v>
       </c>
     </row>
-    <row r="8" spans="3:7">
+    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C8" s="42" t="s">
         <v>186</v>
       </c>
@@ -8529,7 +8531,7 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="9" spans="3:7">
+    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C9" s="42" t="s">
         <v>185</v>
       </c>
@@ -8537,7 +8539,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="10" spans="3:7">
+    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C10" s="44" t="s">
         <v>188</v>
       </c>
@@ -8546,7 +8548,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="11" spans="3:7">
+    <row r="11" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C11" s="42" t="s">
         <v>194</v>
       </c>
@@ -8554,7 +8556,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="12" spans="3:7">
+    <row r="12" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C12" s="42" t="s">
         <v>201</v>
       </c>
@@ -8562,7 +8564,7 @@
         <v>262000</v>
       </c>
     </row>
-    <row r="13" spans="3:7">
+    <row r="13" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C13" s="42" t="s">
         <v>207</v>
       </c>
@@ -8570,7 +8572,7 @@
         <v>204000</v>
       </c>
     </row>
-    <row r="14" spans="3:7">
+    <row r="14" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C14" s="42" t="s">
         <v>211</v>
       </c>
@@ -8578,7 +8580,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="15" spans="3:7">
+    <row r="15" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C15" s="44" t="s">
         <v>213</v>
       </c>
@@ -8586,7 +8588,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="3:7">
+    <row r="16" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C16" s="42" t="s">
         <v>228</v>
       </c>
@@ -8594,7 +8596,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="17" spans="3:4">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17" s="42" t="s">
         <v>236</v>
       </c>
@@ -8602,17 +8604,17 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="18" spans="3:4">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C18" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D18" s="45">
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="3:4">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C19" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D19" s="45">
         <v>600000</v>
@@ -8627,23 +8629,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04D596E-F0F9-4062-A9AD-561789D52B52}">
   <dimension ref="B2:N29"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="25.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="8" max="8" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" thickBot="1"/>
-    <row r="3" spans="2:12" ht="15.75" thickBot="1">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="68" t="s">
         <v>193</v>
       </c>
@@ -8656,21 +8658,21 @@
       <c r="F3" s="26"/>
       <c r="L3" s="24"/>
     </row>
-    <row r="5" spans="2:12" ht="15" thickBot="1"/>
-    <row r="6" spans="2:12" ht="15.75" thickBot="1">
-      <c r="C6" s="115" t="s">
+    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117"/>
-      <c r="H6" s="112" t="s">
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="119"/>
+      <c r="H6" s="114" t="s">
         <v>205</v>
       </c>
-      <c r="I6" s="113"/>
-      <c r="J6" s="114"/>
-    </row>
-    <row r="7" spans="2:12" ht="15">
+      <c r="I6" s="115"/>
+      <c r="J6" s="116"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C7" s="62" t="s">
         <v>242</v>
       </c>
@@ -8693,7 +8695,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C8" s="52" t="s">
         <v>190</v>
       </c>
@@ -8703,17 +8705,17 @@
       </c>
       <c r="E8" s="48"/>
       <c r="F8" s="54"/>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="127" t="s">
         <v>202</v>
       </c>
-      <c r="I8" s="64">
+      <c r="I8" s="128">
         <v>10211609.67</v>
       </c>
-      <c r="J8" s="65" t="s">
+      <c r="J8" s="129" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="9" spans="2:12">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C9" s="52" t="s">
         <v>192</v>
       </c>
@@ -8730,11 +8732,11 @@
         <v>37000000</v>
       </c>
       <c r="J9" s="100" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="K9" s="99"/>
     </row>
-    <row r="10" spans="2:12">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C10" s="52" t="s">
         <v>191</v>
       </c>
@@ -8747,7 +8749,7 @@
       <c r="I10" s="64"/>
       <c r="J10" s="65"/>
     </row>
-    <row r="11" spans="2:12">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C11" s="52" t="s">
         <v>238</v>
       </c>
@@ -8760,7 +8762,7 @@
       <c r="I11" s="64"/>
       <c r="J11" s="65"/>
     </row>
-    <row r="12" spans="2:12">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C12" s="52" t="s">
         <v>208</v>
       </c>
@@ -8773,7 +8775,7 @@
       <c r="I12" s="64"/>
       <c r="J12" s="65"/>
     </row>
-    <row r="13" spans="2:12">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C13" s="52" t="s">
         <v>216</v>
       </c>
@@ -8786,7 +8788,7 @@
       <c r="I13" s="64"/>
       <c r="J13" s="65"/>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C14" s="52" t="s">
         <v>217</v>
       </c>
@@ -8799,7 +8801,7 @@
       <c r="I14" s="64"/>
       <c r="J14" s="65"/>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C15" s="52"/>
       <c r="D15" s="48"/>
       <c r="E15" s="48"/>
@@ -8808,7 +8810,7 @@
       <c r="I15" s="64"/>
       <c r="J15" s="65"/>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C16" s="52"/>
       <c r="D16" s="48"/>
       <c r="E16" s="48"/>
@@ -8817,7 +8819,7 @@
       <c r="I16" s="64"/>
       <c r="J16" s="65"/>
     </row>
-    <row r="17" spans="3:14">
+    <row r="17" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C17" s="52"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
@@ -8826,7 +8828,7 @@
       <c r="I17" s="64"/>
       <c r="J17" s="65"/>
     </row>
-    <row r="18" spans="3:14">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C18" s="52"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
@@ -8835,7 +8837,7 @@
       <c r="I18" s="64"/>
       <c r="J18" s="65"/>
     </row>
-    <row r="19" spans="3:14">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C19" s="52"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
@@ -8844,7 +8846,7 @@
       <c r="I19" s="64"/>
       <c r="J19" s="65"/>
     </row>
-    <row r="20" spans="3:14">
+    <row r="20" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C20" s="52"/>
       <c r="D20" s="48"/>
       <c r="E20" s="48"/>
@@ -8853,7 +8855,7 @@
       <c r="I20" s="64"/>
       <c r="J20" s="65"/>
     </row>
-    <row r="21" spans="3:14">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C21" s="52"/>
       <c r="D21" s="48"/>
       <c r="E21" s="48"/>
@@ -8862,7 +8864,7 @@
       <c r="I21" s="64"/>
       <c r="J21" s="65"/>
     </row>
-    <row r="22" spans="3:14">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C22" s="52"/>
       <c r="D22" s="48"/>
       <c r="E22" s="48"/>
@@ -8871,7 +8873,7 @@
       <c r="I22" s="64"/>
       <c r="J22" s="65"/>
     </row>
-    <row r="23" spans="3:14">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C23" s="52"/>
       <c r="D23" s="48"/>
       <c r="E23" s="48"/>
@@ -8880,7 +8882,7 @@
       <c r="I23" s="64"/>
       <c r="J23" s="65"/>
     </row>
-    <row r="24" spans="3:14">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C24" s="52"/>
       <c r="D24" s="48"/>
       <c r="E24" s="48"/>
@@ -8889,7 +8891,7 @@
       <c r="I24" s="64"/>
       <c r="J24" s="65"/>
     </row>
-    <row r="25" spans="3:14">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C25" s="40"/>
       <c r="D25" s="44"/>
       <c r="E25" s="48"/>
@@ -8898,7 +8900,7 @@
       <c r="I25" s="64"/>
       <c r="J25" s="65"/>
     </row>
-    <row r="26" spans="3:14">
+    <row r="26" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C26" s="40"/>
       <c r="D26" s="44"/>
       <c r="E26" s="48"/>
@@ -8907,7 +8909,7 @@
       <c r="I26" s="64"/>
       <c r="J26" s="65"/>
     </row>
-    <row r="27" spans="3:14" ht="15" thickBot="1">
+    <row r="27" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C27" s="53"/>
       <c r="D27" s="49"/>
       <c r="E27" s="50"/>
@@ -8916,27 +8918,27 @@
       <c r="I27" s="64"/>
       <c r="J27" s="67"/>
     </row>
-    <row r="28" spans="3:14" ht="15.75" thickBot="1">
+    <row r="28" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C28" s="59" t="s">
         <v>239</v>
       </c>
-      <c r="D28" s="118">
+      <c r="D28" s="120">
         <f>SUM(Table5[Incoming])-SUM(Table5[Outcoming])</f>
         <v>5419770</v>
       </c>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="122"/>
       <c r="H28" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="I28" s="121">
+      <c r="I28" s="123">
         <f>SUM(Table6[Amount])</f>
         <v>47211609.670000002</v>
       </c>
-      <c r="J28" s="122"/>
+      <c r="J28" s="124"/>
       <c r="K28" s="39"/>
     </row>
-    <row r="29" spans="3:14">
+    <row r="29" spans="3:14" x14ac:dyDescent="0.3">
       <c r="N29" s="60"/>
     </row>
   </sheetData>
@@ -8958,38 +8960,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45E7117-2FD0-43A7-B1BA-26C3C91B6B68}">
   <dimension ref="E5:AE33"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="26.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" customWidth="1"/>
-    <col min="21" max="21" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.75" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.77734375" customWidth="1"/>
+    <col min="21" max="21" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="5:31">
-      <c r="AB5" s="123"/>
-      <c r="AC5" s="123"/>
-      <c r="AD5" s="123"/>
-      <c r="AE5" s="123"/>
-    </row>
-    <row r="8" spans="5:31" ht="15">
+    <row r="5" spans="5:31" x14ac:dyDescent="0.3">
+      <c r="AB5" s="126"/>
+      <c r="AC5" s="126"/>
+      <c r="AD5" s="126"/>
+      <c r="AE5" s="126"/>
+    </row>
+    <row r="8" spans="5:31" x14ac:dyDescent="0.3">
       <c r="E8" s="71" t="s">
         <v>250</v>
       </c>
@@ -9000,7 +9002,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="5:31" ht="15">
+    <row r="9" spans="5:31" x14ac:dyDescent="0.3">
       <c r="E9" s="71" t="s">
         <v>243</v>
       </c>
@@ -9011,7 +9013,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="5:31" ht="15">
+    <row r="10" spans="5:31" x14ac:dyDescent="0.3">
       <c r="E10" s="71" t="s">
         <v>245</v>
       </c>
@@ -9022,7 +9024,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="11" spans="5:31" ht="15">
+    <row r="11" spans="5:31" x14ac:dyDescent="0.3">
       <c r="E11" s="71" t="s">
         <v>246</v>
       </c>
@@ -9033,7 +9035,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="5:31" ht="15">
+    <row r="12" spans="5:31" x14ac:dyDescent="0.3">
       <c r="E12" s="71" t="s">
         <v>248</v>
       </c>
@@ -9044,7 +9046,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="5:31" ht="29.25" thickBot="1">
+    <row r="13" spans="5:31" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E13" s="71" t="s">
         <v>258</v>
       </c>
@@ -9055,7 +9057,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="5:31" ht="36.6" customHeight="1" thickTop="1" thickBot="1">
+    <row r="14" spans="5:31" ht="36.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E14" s="92" t="s">
         <v>262</v>
       </c>
@@ -9066,8 +9068,8 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="5:31" ht="15" thickTop="1"/>
-    <row r="16" spans="5:31" ht="15" thickBot="1">
+    <row r="15" spans="5:31" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="5:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E16" s="39" t="s">
         <v>235</v>
       </c>
@@ -9081,7 +9083,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+    <row r="17" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E17" s="89" t="s">
         <v>259</v>
       </c>
@@ -9093,10 +9095,10 @@
         <v>15000000</v>
       </c>
       <c r="H17" s="96" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="18" spans="5:15" ht="15.75" thickTop="1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="18" spans="5:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="E18" s="93" t="s">
         <v>20</v>
       </c>
@@ -9107,10 +9109,10 @@
         <v>6000000</v>
       </c>
       <c r="H18" s="97" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="19" spans="5:15" ht="15">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="5:15" x14ac:dyDescent="0.3">
       <c r="E19" s="39" t="s">
         <v>231</v>
       </c>
@@ -9122,7 +9124,7 @@
       </c>
       <c r="H19" s="98"/>
     </row>
-    <row r="20" spans="5:15" ht="15">
+    <row r="20" spans="5:15" x14ac:dyDescent="0.3">
       <c r="E20" s="39" t="s">
         <v>230</v>
       </c>
@@ -9134,10 +9136,10 @@
         <v>22000000</v>
       </c>
       <c r="H20" s="98" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="21" spans="5:15" ht="15">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="5:15" x14ac:dyDescent="0.3">
       <c r="E21" s="93" t="s">
         <v>232</v>
       </c>
@@ -9150,45 +9152,45 @@
         <v>500000.00000000047</v>
       </c>
       <c r="H21" s="97" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="23" spans="5:15">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="23" spans="5:15" x14ac:dyDescent="0.3">
       <c r="E23" s="39" t="s">
+        <v>269</v>
+      </c>
+      <c r="F23" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="F23" s="39" t="s">
+      <c r="G23" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="G23" s="39" t="s">
+      <c r="H23" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="H23" s="39" t="s">
+      <c r="I23" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="I23" s="39" t="s">
+      <c r="J23" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="J23" s="39" t="s">
+      <c r="K23" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="K23" s="39" t="s">
+      <c r="L23" s="39" t="s">
+        <v>283</v>
+      </c>
+      <c r="M23" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="L23" s="39" t="s">
-        <v>284</v>
-      </c>
-      <c r="M23" s="39" t="s">
+      <c r="N23" s="39" t="s">
         <v>277</v>
-      </c>
-      <c r="N23" s="39" t="s">
-        <v>278</v>
       </c>
       <c r="O23" s="39" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="24" spans="5:15">
+    <row r="24" spans="5:15" x14ac:dyDescent="0.3">
       <c r="E24" s="86">
         <v>46219</v>
       </c>
@@ -9223,7 +9225,7 @@
       </c>
       <c r="O24" s="39"/>
     </row>
-    <row r="25" spans="5:15">
+    <row r="25" spans="5:15" x14ac:dyDescent="0.3">
       <c r="E25" s="86">
         <v>46225</v>
       </c>
@@ -9258,7 +9260,7 @@
       </c>
       <c r="O25" s="39"/>
     </row>
-    <row r="26" spans="5:15" ht="15" thickBot="1">
+    <row r="26" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E26" s="86" t="s">
         <v>210</v>
       </c>
@@ -9295,7 +9297,7 @@
       </c>
       <c r="O26" s="39"/>
     </row>
-    <row r="27" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+    <row r="27" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E27" s="89" t="s">
         <v>210</v>
       </c>
@@ -9330,7 +9332,7 @@
       </c>
       <c r="O27" s="89"/>
     </row>
-    <row r="28" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+    <row r="28" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E28" s="89" t="s">
         <v>210</v>
       </c>
@@ -9338,7 +9340,7 @@
         <v>210</v>
       </c>
       <c r="G28" s="89" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H28" s="89" t="s">
         <v>210</v>
@@ -9365,7 +9367,7 @@
       </c>
       <c r="O28" s="89"/>
     </row>
-    <row r="29" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+    <row r="29" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E29" s="89" t="s">
         <v>210</v>
       </c>
@@ -9373,7 +9375,7 @@
         <v>210</v>
       </c>
       <c r="G29" s="89" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H29" s="89" t="s">
         <v>210</v>
@@ -9400,7 +9402,7 @@
       </c>
       <c r="O29" s="89"/>
     </row>
-    <row r="30" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+    <row r="30" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E30" s="89" t="s">
         <v>210</v>
       </c>
@@ -9408,7 +9410,7 @@
         <v>210</v>
       </c>
       <c r="G30" s="89" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H30" s="89" t="s">
         <v>210</v>
@@ -9435,7 +9437,7 @@
       </c>
       <c r="O30" s="89"/>
     </row>
-    <row r="31" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+    <row r="31" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E31" s="89" t="s">
         <v>210</v>
       </c>
@@ -9443,7 +9445,7 @@
         <v>210</v>
       </c>
       <c r="G31" s="89" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H31" s="89" t="s">
         <v>210</v>
@@ -9470,7 +9472,7 @@
       </c>
       <c r="O31" s="89"/>
     </row>
-    <row r="32" spans="5:15" ht="16.5" thickTop="1" thickBot="1">
+    <row r="32" spans="5:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E32" s="89" t="s">
         <v>210</v>
       </c>
@@ -9478,7 +9480,7 @@
         <v>210</v>
       </c>
       <c r="G32" s="89" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H32" s="89" t="s">
         <v>210</v>
@@ -9505,7 +9507,7 @@
       </c>
       <c r="O32" s="89"/>
     </row>
-    <row r="33" ht="15" thickTop="1"/>
+    <row r="33" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="AB5:AC5"/>
@@ -9530,13 +9532,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C45E6B-F2EC-4DF6-9239-EC7E9397E406}">
   <dimension ref="A1:B167"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -9544,7 +9546,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -9552,7 +9554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -9560,7 +9562,7 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -9568,7 +9570,7 @@
         <v>2.0409E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -9576,7 +9578,7 @@
         <v>2.495E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -9584,7 +9586,7 @@
         <v>0.11405700000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -9592,7 +9594,7 @@
         <v>5.6099999999999998E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -9600,7 +9602,7 @@
         <v>0.28789500000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -9608,7 +9610,7 @@
         <v>0.47286800000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -9616,7 +9618,7 @@
         <v>4.37E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -9624,7 +9626,7 @@
         <v>5.6099999999999998E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -9632,7 +9634,7 @@
         <v>5.3600000000000002E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -9640,7 +9642,7 @@
         <v>5.2800000000000004E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -9648,7 +9650,7 @@
         <v>6.2699999999999995E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -9656,7 +9658,7 @@
         <v>3.8725999999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -9664,7 +9666,7 @@
         <v>5.2800000000000004E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -9672,7 +9674,7 @@
         <v>1.18E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -9680,7 +9682,7 @@
         <v>0.94235199999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -9688,7 +9690,7 @@
         <v>3.1300000000000002E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -9696,7 +9698,7 @@
         <v>3.9899999999999999E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -9704,7 +9706,7 @@
         <v>3.699E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -9712,7 +9714,7 @@
         <v>1.621E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -9720,7 +9722,7 @@
         <v>3.1300000000000002E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -9728,7 +9730,7 @@
         <v>2.9824E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -9736,7 +9738,7 @@
         <v>4.2009999999999999E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -9744,7 +9746,7 @@
         <v>9.6100000000000005E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -9752,7 +9754,7 @@
         <v>6.2699999999999995E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -9760,7 +9762,7 @@
         <v>4.35E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -9768,7 +9770,7 @@
         <v>0.71758900000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -9776,7 +9778,7 @@
         <v>2.5300000000000002E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>223</v>
       </c>
@@ -9784,7 +9786,7 @@
         <v>6.9999999999999999E-6</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -9792,7 +9794,7 @@
         <v>0.29166199999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>224</v>
       </c>
@@ -9800,7 +9802,7 @@
         <v>2.104E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -9808,7 +9810,7 @@
         <v>2.1099999999999999E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -9816,7 +9818,7 @@
         <v>0.14158200000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -9824,7 +9826,7 @@
         <v>7.5180000000000004E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -9832,7 +9834,7 @@
         <v>2.9779E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -9840,7 +9842,7 @@
         <v>6.5160000000000001E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -9848,7 +9850,7 @@
         <v>5.5674000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -9856,7 +9858,7 @@
         <v>2.019E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -9864,7 +9866,7 @@
         <v>1.8456E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -9872,7 +9874,7 @@
         <v>4.1771999999999997E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -9880,7 +9882,7 @@
         <v>1.5897999999999999E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -9888,7 +9890,7 @@
         <v>4.6990000000000001E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>62</v>
       </c>
@@ -9896,7 +9898,7 @@
         <v>5.0786999999999999E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>63</v>
       </c>
@@ -9904,7 +9906,7 @@
         <v>2.7E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>64</v>
       </c>
@@ -9912,7 +9914,7 @@
         <v>6.8900000000000005E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -9920,7 +9922,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -9928,7 +9930,7 @@
         <v>2.019E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>67</v>
       </c>
@@ -9936,7 +9938,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>68</v>
       </c>
@@ -9944,7 +9946,7 @@
         <v>8.1599999999999999E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -9952,7 +9954,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>70</v>
       </c>
@@ -9960,7 +9962,7 @@
         <v>3.5209999999999998E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>71</v>
       </c>
@@ -9968,7 +9970,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -9976,7 +9978,7 @@
         <v>2.3699000000000001E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>73</v>
       </c>
@@ -9984,7 +9986,7 @@
         <v>2.7476530000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -9992,7 +9994,7 @@
         <v>2.3990000000000001E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -10000,7 +10002,7 @@
         <v>6.5502000000000005E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>76</v>
       </c>
@@ -10008,7 +10010,7 @@
         <v>2.454E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>77</v>
       </c>
@@ -10016,7 +10018,7 @@
         <v>8.4259999999999995E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>78</v>
       </c>
@@ -10024,7 +10026,7 @@
         <v>2.0349999999999999E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>79</v>
       </c>
@@ -10032,7 +10034,7 @@
         <v>4.0933999999999998E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -10040,7 +10042,7 @@
         <v>9.8497000000000001E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>81</v>
       </c>
@@ -10048,7 +10050,7 @@
         <v>5.5844550000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>82</v>
       </c>
@@ -10056,7 +10058,7 @@
         <v>9.3599999999999998E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -10064,7 +10066,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>84</v>
       </c>
@@ -10072,7 +10074,7 @@
         <v>2.9824E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>85</v>
       </c>
@@ -10080,7 +10082,7 @@
         <v>0.41089199999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -10088,7 +10090,7 @@
         <v>445.14925399999998</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>87</v>
       </c>
@@ -10096,7 +10098,7 @@
         <v>3.8009000000000001E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>88</v>
       </c>
@@ -10104,7 +10106,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>89</v>
       </c>
@@ -10112,7 +10114,7 @@
         <v>4.9805000000000002E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -10120,7 +10122,7 @@
         <v>2.22E-4</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -10128,7 +10130,7 @@
         <v>5.0019000000000001E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -10136,7 +10138,7 @@
         <v>4.0545999999999999E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>93</v>
       </c>
@@ -10144,7 +10146,7 @@
         <v>2.7387999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -10152,7 +10154,7 @@
         <v>1.2652890000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>95</v>
       </c>
@@ -10160,7 +10162,7 @@
         <v>4.37E-4</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>96</v>
       </c>
@@ -10168,7 +10170,7 @@
         <v>0.13286400000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>97</v>
       </c>
@@ -10176,7 +10178,7 @@
         <v>0.428672</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>98</v>
       </c>
@@ -10184,7 +10186,7 @@
         <v>9.7E-5</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>99</v>
       </c>
@@ -10192,7 +10194,7 @@
         <v>2.61E-4</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>100</v>
       </c>
@@ -10200,7 +10202,7 @@
         <v>0.145283</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>101</v>
       </c>
@@ -10208,7 +10210,7 @@
         <v>6.9917009999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>102</v>
       </c>
@@ -10216,7 +10218,7 @@
         <v>28.037489999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>103</v>
       </c>
@@ -10224,7 +10226,7 @@
         <v>0.102843</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>104</v>
       </c>
@@ -10232,7 +10234,7 @@
         <v>5.6659000000000001E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>105</v>
       </c>
@@ -10240,7 +10242,7 @@
         <v>5.0530000000000002E-3</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>106</v>
       </c>
@@ -10248,7 +10250,7 @@
         <v>1.9840000000000001E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>107</v>
       </c>
@@ -10256,7 +10258,7 @@
         <v>2.9129999999999998E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>108</v>
       </c>
@@ -10264,7 +10266,7 @@
         <v>5.4190000000000002E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>109</v>
       </c>
@@ -10272,7 +10274,7 @@
         <v>1.354023</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>110</v>
       </c>
@@ -10280,7 +10282,7 @@
         <v>1.7075E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>111</v>
       </c>
@@ -10288,7 +10290,7 @@
         <v>0.65837199999999996</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>112</v>
       </c>
@@ -10296,7 +10298,7 @@
         <v>1.1309959999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>113</v>
       </c>
@@ -10304,7 +10306,7 @@
         <v>2.5279999999999999E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>114</v>
       </c>
@@ -10312,7 +10314,7 @@
         <v>1.2573000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>115</v>
       </c>
@@ -10320,7 +10322,7 @@
         <v>1.4734000000000001E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>116</v>
       </c>
@@ -10328,7 +10330,7 @@
         <v>4.8459999999999996E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>117</v>
       </c>
@@ -10336,7 +10338,7 @@
         <v>0.54324700000000004</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>118</v>
       </c>
@@ -10344,7 +10346,7 @@
         <v>5.3280000000000003E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>119</v>
       </c>
@@ -10352,7 +10354,7 @@
         <v>1.2600000000000001E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>120</v>
       </c>
@@ -10360,7 +10362,7 @@
         <v>1.9913E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>121</v>
       </c>
@@ -10368,7 +10370,7 @@
         <v>5.0530000000000002E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>122</v>
       </c>
@@ -10376,7 +10378,7 @@
         <v>0.42027999999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>123</v>
       </c>
@@ -10384,7 +10386,7 @@
         <v>1.157E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>124</v>
       </c>
@@ -10392,7 +10394,7 @@
         <v>2.9269999999999999E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>125</v>
       </c>
@@ -10400,7 +10402,7 @@
         <v>4.7718000000000003E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>126</v>
       </c>
@@ -10408,7 +10410,7 @@
         <v>5.2899999999999996E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>127</v>
       </c>
@@ -10416,7 +10418,7 @@
         <v>1.2E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>128</v>
       </c>
@@ -10424,7 +10426,7 @@
         <v>3.1300000000000002E-4</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>129</v>
       </c>
@@ -10432,7 +10434,7 @@
         <v>1.0560000000000001E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>130</v>
       </c>
@@ -10440,7 +10442,7 @@
         <v>1.3979999999999999E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>131</v>
       </c>
@@ -10448,7 +10450,7 @@
         <v>1.9529999999999999E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>132</v>
       </c>
@@ -10456,7 +10458,7 @@
         <v>8.7101999999999999E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>133</v>
       </c>
@@ -10464,7 +10466,7 @@
         <v>1.1709999999999999E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>134</v>
       </c>
@@ -10472,7 +10474,7 @@
         <v>1.862026</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>135</v>
       </c>
@@ -10480,7 +10482,7 @@
         <v>1.14E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>136</v>
       </c>
@@ -10488,7 +10490,7 @@
         <v>1.42E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>137</v>
       </c>
@@ -10496,7 +10498,7 @@
         <v>3.1708E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>138</v>
       </c>
@@ -10504,7 +10506,7 @@
         <v>2.7088999999999998E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>139</v>
       </c>
@@ -10512,7 +10514,7 @@
         <v>0.462258</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>140</v>
       </c>
@@ -10520,7 +10522,7 @@
         <v>1.175E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>141</v>
       </c>
@@ -10528,7 +10530,7 @@
         <v>2.5110000000000002E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>142</v>
       </c>
@@ -10536,7 +10538,7 @@
         <v>4.398E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>143</v>
       </c>
@@ -10544,7 +10546,7 @@
         <v>0.14224300000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>144</v>
       </c>
@@ -10552,7 +10554,7 @@
         <v>3.0019999999999999E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>145</v>
       </c>
@@ -10560,7 +10562,7 @@
         <v>3.9899999999999999E-4</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>146</v>
       </c>
@@ -10568,7 +10570,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>147</v>
       </c>
@@ -10576,7 +10578,7 @@
         <v>7.9640000000000006E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>148</v>
       </c>
@@ -10584,7 +10586,7 @@
         <v>7.9639519999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>149</v>
       </c>
@@ -10592,7 +10594,7 @@
         <v>0.17905699999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>150</v>
       </c>
@@ -10600,7 +10602,7 @@
         <v>1.1838E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>151</v>
       </c>
@@ -10608,7 +10610,7 @@
         <v>1.8075760000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>152</v>
       </c>
@@ -10616,7 +10618,7 @@
         <v>6.6169999999999996E-3</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>153</v>
       </c>
@@ -10624,7 +10626,7 @@
         <v>3.8131999999999999E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>154</v>
       </c>
@@ -10632,7 +10634,7 @@
         <v>5.0530000000000002E-3</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>155</v>
       </c>
@@ -10640,7 +10642,7 @@
         <v>1.0385999999999999E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>156</v>
       </c>
@@ -10648,7 +10650,7 @@
         <v>2.9870000000000001E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>157</v>
       </c>
@@ -10656,7 +10658,7 @@
         <v>1.1329999999999999E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>158</v>
       </c>
@@ -10664,7 +10666,7 @@
         <v>9.1100000000000003E-4</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -10672,7 +10674,7 @@
         <v>7.5500000000000003E-4</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>160</v>
       </c>
@@ -10680,7 +10682,7 @@
         <v>1.5110999999999999E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>161</v>
       </c>
@@ -10688,7 +10690,7 @@
         <v>2.1389999999999998E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>162</v>
       </c>
@@ -10696,7 +10698,7 @@
         <v>4.37E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -10704,7 +10706,7 @@
         <v>9.9290000000000003E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>164</v>
       </c>
@@ -10712,7 +10714,7 @@
         <v>0.82893899999999998</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>165</v>
       </c>
@@ -10720,7 +10722,7 @@
         <v>1.3958999999999999E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>166</v>
       </c>
@@ -10728,7 +10730,7 @@
         <v>1.1724760000000001</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>20</v>
       </c>
@@ -10736,7 +10738,7 @@
         <v>3.1300000000000002E-4</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>167</v>
       </c>
@@ -10744,7 +10746,7 @@
         <v>1.2659999999999999E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>168</v>
       </c>
@@ -10752,7 +10754,7 @@
         <v>3.6983440000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>169</v>
       </c>
@@ -10760,7 +10762,7 @@
         <v>0.25009500000000001</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>170</v>
       </c>
@@ -10768,7 +10770,7 @@
         <v>8.1179109999999994</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>171</v>
       </c>
@@ -10776,7 +10778,7 @@
         <v>3.7132999999999999E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>172</v>
       </c>
@@ -10784,7 +10786,7 @@
         <v>8.4699999999999999E-4</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>173</v>
       </c>
@@ -10792,7 +10794,7 @@
         <v>0.177152</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>174</v>
       </c>
@@ -10800,7 +10802,7 @@
         <v>8.4599999999999996E-4</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>175</v>
       </c>
@@ -10808,7 +10810,7 @@
         <v>5.6099999999999998E-4</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>176</v>
       </c>
@@ -10816,7 +10818,7 @@
         <v>2.2900000000000001E-4</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>177</v>
       </c>
@@ -10824,7 +10826,7 @@
         <v>0.177152</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>178</v>
       </c>
@@ -10832,7 +10834,7 @@
         <v>3.2228E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>179</v>
       </c>
@@ -10840,7 +10842,7 @@
         <v>7.4154999999999999E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>180</v>
       </c>
@@ -10848,7 +10850,7 @@
         <v>5.0530000000000002E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>181</v>
       </c>
@@ -10856,7 +10858,7 @@
         <v>5.9589999999999999E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>225</v>
       </c>
@@ -10864,7 +10866,7 @@
         <v>8.3540000000000003E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>182</v>
       </c>
